--- a/docs/reverse-tco-model-v1.xlsx
+++ b/docs/reverse-tco-model-v1.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Engine" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Results" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Validation" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="EngineRegression" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="329">
   <si>
     <t xml:space="preserve">Reverse TCO Tool v1 — Cloud AIaaS Spend to On-Prem NVIDIA Infrastructure</t>
   </si>
@@ -86,6 +87,12 @@
     <t xml:space="preserve">SOURCES: NVIDIA DGX TCO tool defaults (extracted Aug 2026); MLPerf-derived performance factors (see PerfFactors tab notes).</t>
   </si>
   <si>
+    <t xml:space="preserve">V2.0 WORKBOOK UPDATES (external audit response): harmonic workload blend in Engine!B10; lease view now shows lease + opex total; residual excludes professional services; EngineRegression sheet exercises the LIVE engine against a Test 1 fixture; fleet expansion under growth remains NOT modeled in the workbook (see Results warning) — the deployed web engine v2.0 models it dynamically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware registry note: only rows marked Priced?=YES are valid selections; placeholder rows produce nonsensical results and are guarded in the web app.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rate Card — all editable (blue). Effective date + source in column C.</t>
   </si>
   <si>
@@ -362,7 +369,7 @@
     <t xml:space="preserve">Monthly cloud AI spend ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Their approximate all-in monthly AI bill. Example default = NVIDIA Test 1.</t>
+    <t xml:space="preserve">Approximates NVIDIA Test 1 (~1% high; exact compute share would be 49.491%)</t>
   </si>
   <si>
     <t xml:space="preserve">Primary provider</t>
@@ -560,7 +567,7 @@
     <t xml:space="preserve">Generational factor (workload-weighted)</t>
   </si>
   <si>
-    <t xml:space="preserve">Training share x training PF + inference share x inference PF</t>
+    <t xml:space="preserve">v2.0: harmonic blend — workload shares are GPU-hour shares (audit P0-2)</t>
   </si>
   <si>
     <t xml:space="preserve">Net Performance Factor (NPF)</t>
@@ -701,13 +708,13 @@
     <t xml:space="preserve">STEP 6 — Financing (optional)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lease monthly, adjusted case ($/mo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capex x day-of factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lease monthly, floor case ($/mo)</t>
+    <t xml:space="preserve">Lease + opex, monthly total, adjusted ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2.0: lease payment + selected monthly opex (audit: lease view omitted opex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lease + opex, monthly total, floor ($/mo)</t>
   </si>
   <si>
     <t xml:space="preserve">STEP 7 (v1.2) — One-time costs &amp; residual</t>
@@ -722,7 +729,7 @@
     <t xml:space="preserve">Residual credit at horizon, adjusted ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems + storage capex only</t>
+    <t xml:space="preserve">v2.0: prof services excluded from residual basis (no resale value)</t>
   </si>
   <si>
     <t xml:space="preserve">Residual credit at horizon, floor ($)</t>
@@ -809,7 +816,7 @@
     <t xml:space="preserve">Years until growth exhausts headroom</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud egress + storage cost that disappears on-prem ($/mo)</t>
+    <t xml:space="preserve">Cloud storage + egress spend displaced by on-prem storage modeled above ($/mo)</t>
   </si>
   <si>
     <t xml:space="preserve">Simple payback, adjusted (months, capex + one-time vs current bill)</t>
@@ -818,6 +825,12 @@
     <t xml:space="preserve">Lease view, adjusted ($/mo, if factor entered)</t>
   </si>
   <si>
+    <t xml:space="preserve">⚠ WORKBOOK LIMITATION: fleet expansion under growth is NOT modeled here (web engine v2.0 models it). Headroom exhausted after (years):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals for horizons beyond that year understate on-prem cost; treat longer-horizon results as directional only.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Validation — reproduce NVIDIA DGX TCO tool Test 1 from this rate card</t>
   </si>
   <si>
@@ -885,13 +898,130 @@
   </si>
   <si>
     <t xml:space="preserve">All rows must read PASS before customer use. If a rate card value changes, expected values here describe the NVIDIA tool snapshot, not your new reality — they exist to prove the formula logic, not to freeze prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine Regression — NVIDIA Test 1 fixture (audit P0-3 response)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set the Inputs tab to the fixture below, then every check compares the LIVE Engine/Results cells (not shadow formulas) to expected values under the engine's documented conventions. Tolerance: MAX($1, 0.01%). Note: 'Other facility' expected is $3,111 (engine counts 1.0 storage rack for 1.0 PB) vs NVIDIA's $3,097 (0.75 racks) — a documented convention difference of $14/mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXTURE (set these on Inputs):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B4 Monthly spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B13 Compute share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B8 GPU class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B9 Training share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B10 OD share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B11 Storage PB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B12 Fast share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B14 Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B15 Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B16 Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B17 Utilization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B18 System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B21 Tier3 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B24-26 Factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0 / 1.0 / 1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs!B33-B37 Retrofit/Migr/Dual/N+1/Resid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 / 0 / 0 / 0 / 0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixture loaded?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check (live Engine/Results cell)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud GPU-hours/mo (Engine!B7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended rate $/instance-hr (Engine!B4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Performance Factor (Engine!B11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems required, adjusted (Engine!B18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems required, floor (Engine!B19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex compute+network (Engine!B31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex storage (Engine!B32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage support $/mo (Engine!B39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power $/mo (Engine!B35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other facility $/mo (Engine!B37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin $/mo (Engine!B38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected opex $/mo (Engine!B42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-time costs (Engine!B54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual credit (Engine!B55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-time expected = cloud exit egress only (1 PB × $0.05/GB = $50,000) since migration/dual-run are zeroed in the fixture.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -901,7 +1031,9 @@
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
     <numFmt numFmtId="171" formatCode="0.00\x"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="\$#,##0"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="174" formatCode="0.00\x"/>
+    <numFmt numFmtId="175" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1029,7 +1161,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1118,26 +1250,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1162,11 +1274,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1422,7 +1586,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1533,6 +1697,16 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1561,89 +1735,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>113.93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>68.36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>2.88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.05</v>
@@ -1652,18 +1826,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>189000</v>
@@ -1672,7 +1846,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>5000</v>
@@ -1681,29 +1855,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>8</v>
@@ -1712,23 +1886,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>25000</v>
@@ -1737,29 +1911,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>1200000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>100000</v>
@@ -1768,18 +1942,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>500000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>33333</v>
@@ -1788,7 +1962,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
@@ -1797,29 +1971,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>3000</v>
@@ -1828,7 +2002,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>2000</v>
@@ -1837,7 +2011,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
@@ -1846,7 +2020,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>189000</v>
@@ -1855,40 +2029,40 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>11387</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>730</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>0.04</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1920,47 +2094,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>8</v>
@@ -1987,15 +2161,15 @@
         <v>2</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>8</v>
@@ -2022,15 +2196,15 @@
         <v>2</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>8</v>
@@ -2057,15 +2231,15 @@
         <v>2</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>72</v>
@@ -2092,35 +2266,35 @@
         <v>1</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2149,32 +2323,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B3" s="14" t="n">
         <v>4.4</v>
@@ -2189,12 +2363,12 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>2.2</v>
@@ -2209,12 +2383,12 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>1.5</v>
@@ -2229,12 +2403,12 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>1</v>
@@ -2249,17 +2423,17 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2288,305 +2462,305 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>105079</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>0.25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B16" s="15" t="n">
         <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>0.85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B21" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>1.3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B26" s="20" t="n">
         <v>1.3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B30" s="19" t="n">
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="B33" s="24" t="n">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="23" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="B34" s="24" t="n">
+      <c r="C33" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="15" t="n">
         <v>100000</v>
       </c>
-      <c r="C34" s="23" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="B35" s="25" t="n">
+      <c r="C34" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="23" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="B36" s="25" t="n">
+      <c r="C35" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="23" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="B37" s="26" t="n">
+      <c r="C36" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="C37" s="23" t="s">
-        <v>164</v>
+      <c r="C37" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2615,49 +2789,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="B4" s="22" t="n">
         <f aca="false">(Inputs!$B$10*(RateCard!$B$4+RateCard!$B$6)+(1-Inputs!$B$10)*(RateCard!$B$5+RateCard!$B$7))*(1+RateCard!$B$15)</f>
         <v>71.24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="28" t="n">
+        <v>172</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
         <v>52539.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="29" t="n">
+        <v>174</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <f aca="false">B5/B4</f>
         <v>737.5</v>
       </c>
@@ -2665,77 +2839,77 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="29" t="n">
+        <v>175</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*RateCard!$B$16)</f>
         <v>5900</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B10" s="30" t="n">
-        <f aca="false">Inputs!$B$9*INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)*INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))</f>
-        <v>3.1</v>
+        <v>178</v>
+      </c>
+      <c r="B10" s="25" t="n">
+        <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
+        <v>2.83870967741935</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B11" s="30" t="n">
+        <v>180</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
-        <v>5.239</v>
+        <v>4.79741935483871</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B12" s="29" t="n">
+        <v>182</v>
+      </c>
+      <c r="B12" s="24" t="n">
         <f aca="false">B7/B11</f>
-        <v>1126.16911624356</v>
+        <v>1229.82786444325</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B13" s="29" t="n">
+        <v>183</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <f aca="false">B7</f>
         <v>5900</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B16" s="29" t="n">
+        <v>186</v>
+      </c>
+      <c r="B16" s="24" t="n">
         <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
         <v>8</v>
       </c>
@@ -2743,21 +2917,21 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B17" s="29" t="n">
+        <v>187</v>
+      </c>
+      <c r="B17" s="24" t="n">
         <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
         <v>4964</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="29" t="n">
+        <v>189</v>
+      </c>
+      <c r="B18" s="24" t="n">
         <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
         <v>1</v>
       </c>
@@ -2765,9 +2939,9 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B19" s="29" t="n">
+        <v>190</v>
+      </c>
+      <c r="B19" s="24" t="n">
         <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
         <v>2</v>
       </c>
@@ -2775,26 +2949,26 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B20" s="31" t="n">
+        <v>191</v>
+      </c>
+      <c r="B20" s="26" t="n">
         <f aca="false">1-B12/(B18*B17)</f>
-        <v>0.773132732424747</v>
+        <v>0.752250631659297</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B23" s="32" t="n">
+        <v>194</v>
+      </c>
+      <c r="B23" s="27" t="n">
         <f aca="false">Inputs!$B$11*Inputs!$B$12</f>
         <v>0.25</v>
       </c>
@@ -2802,9 +2976,9 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="32" t="n">
+        <v>195</v>
+      </c>
+      <c r="B24" s="27" t="n">
         <f aca="false">Inputs!$B$11*(1-Inputs!$B$12)</f>
         <v>0.75</v>
       </c>
@@ -2812,21 +2986,21 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B25" s="28" t="n">
+        <v>196</v>
+      </c>
+      <c r="B25" s="23" t="n">
         <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+Inputs!$B$11*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>52500</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B26" s="28" t="n">
+        <v>198</v>
+      </c>
+      <c r="B26" s="23" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
         <v>574.166666666667</v>
       </c>
@@ -2834,26 +3008,26 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B29" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="B29" s="23" t="n">
         <f aca="false">INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20</f>
         <v>744793</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B30" s="29" t="n">
+        <v>202</v>
+      </c>
+      <c r="B30" s="24" t="n">
         <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
         <v>1</v>
       </c>
@@ -2861,21 +3035,21 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B31" s="28" t="n">
+        <v>203</v>
+      </c>
+      <c r="B31" s="23" t="n">
         <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B32" s="28" t="n">
+        <v>205</v>
+      </c>
+      <c r="B32" s="23" t="n">
         <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
         <v>675000</v>
       </c>
@@ -2883,9 +3057,9 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B33" s="28" t="n">
+        <v>206</v>
+      </c>
+      <c r="B33" s="23" t="n">
         <f aca="false">B31+B32</f>
         <v>2034793</v>
       </c>
@@ -2893,9 +3067,9 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B34" s="32" t="n">
+        <v>207</v>
+      </c>
+      <c r="B34" s="27" t="n">
         <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
         <v>14.4</v>
       </c>
@@ -2903,21 +3077,21 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B35" s="28" t="n">
+        <v>208</v>
+      </c>
+      <c r="B35" s="23" t="n">
         <f aca="false">(B18*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16</f>
         <v>7320</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B36" s="32" t="n">
+        <v>210</v>
+      </c>
+      <c r="B36" s="27" t="n">
         <f aca="false">B30+Inputs!$B$11*RateCard!$B$27</f>
         <v>2</v>
       </c>
@@ -2925,45 +3099,45 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B37" s="28" t="n">
+        <v>211</v>
+      </c>
+      <c r="B37" s="23" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/36</f>
         <v>3111.11111111111</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B38" s="28" t="n">
+        <v>213</v>
+      </c>
+      <c r="B38" s="23" t="n">
         <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B39" s="28" t="n">
+        <v>214</v>
+      </c>
+      <c r="B39" s="23" t="n">
         <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
         <v>4166.64583333333</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B40" s="28" t="n">
+        <v>216</v>
+      </c>
+      <c r="B40" s="23" t="n">
         <f aca="false">B35+B37+B38+B39</f>
         <v>16172.7569444444</v>
       </c>
@@ -2971,21 +3145,21 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B41" s="28" t="n">
+        <v>217</v>
+      </c>
+      <c r="B41" s="23" t="n">
         <f aca="false">B18*RateCard!$B$33+B39</f>
         <v>15553.6458333333</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B42" s="28" t="n">
+        <v>219</v>
+      </c>
+      <c r="B42" s="23" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
         <v>16172.7569444444</v>
       </c>
@@ -2993,14 +3167,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B45" s="28" t="n">
+        <v>221</v>
+      </c>
+      <c r="B45" s="23" t="n">
         <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
         <v>2779586</v>
       </c>
@@ -3008,9 +3182,9 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B46" s="28" t="n">
+        <v>222</v>
+      </c>
+      <c r="B46" s="23" t="n">
         <f aca="false">(B19*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+Inputs!$B$11*RateCard!$B$27)/36+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
         <v>22067.7569444444</v>
       </c>
@@ -3018,9 +3192,9 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B47" s="28" t="n">
+        <v>223</v>
+      </c>
+      <c r="B47" s="23" t="n">
         <f aca="false">B19*RateCard!$B$33+B39</f>
         <v>26940.6458333333</v>
       </c>
@@ -3028,9 +3202,9 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B48" s="28" t="n">
+        <v>224</v>
+      </c>
+      <c r="B48" s="23" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
         <v>22067.7569444444</v>
       </c>
@@ -3038,69 +3212,69 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B51" s="28" t="str">
-        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29)</f>
+        <v>226</v>
+      </c>
+      <c r="B51" s="23" t="str">
+        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
         <v>not entered</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B52" s="28" t="str">
-        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29)</f>
+        <v>228</v>
+      </c>
+      <c r="B52" s="23" t="str">
+        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
         <v>not entered</v>
       </c>
       <c r="C52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="B54" s="33" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="23" t="n">
         <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+Inputs!$B$11*1000000*RateCard!$B$10</f>
         <v>360158</v>
       </c>
-      <c r="C54" s="23" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="B55" s="33" t="n">
-        <f aca="false">Inputs!$B$37*(B18*B29+B32)</f>
-        <v>212968.95</v>
-      </c>
-      <c r="C55" s="23" t="s">
+      <c r="C54" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="23" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B56" s="33" t="n">
-        <f aca="false">Inputs!$B$37*(B19*B29+B32)</f>
-        <v>324687.9</v>
-      </c>
-      <c r="C56" s="23"/>
+      <c r="B55" s="23" t="n">
+        <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20)+B32)</f>
+        <v>209218.95</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B56" s="23" t="n">
+        <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20)+B32)</f>
+        <v>317187.9</v>
+      </c>
+      <c r="C56" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3118,7 +3292,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -3127,332 +3301,346 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="28" t="n">
+        <v>243</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
         <v>1260948</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^1+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^1)</f>
         <v>1443785.46</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^2+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^2)</f>
         <v>1667036.3034</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="23" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^3+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^3)</f>
         <v>1940592.036786</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^4+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^4)</f>
         <v>2276808.56981994</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B7" s="28" t="n">
+        <v>244</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
         <v>194073.083333333</v>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^1</f>
         <v>201836.006666667</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^2</f>
         <v>209909.446933333</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^3</f>
         <v>218305.824810667</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^4</f>
         <v>227038.057803093</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B8" s="28" t="n">
+        <v>245</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
         <v>264813.083333333</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="23" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^1</f>
         <v>275405.606666667</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^2</f>
         <v>286421.830933333</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^3</f>
         <v>297878.704170667</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^4</f>
         <v>309793.852337493</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B12" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <f aca="false">SUM($B$6:B6)</f>
         <v>1260948</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="23" t="n">
         <f aca="false">SUM($B$6:D6)</f>
         <v>4371769.7634</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">SUM($B$6:F6)</f>
         <v>8589170.37000594</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B13" s="28" t="n">
+        <v>251</v>
+      </c>
+      <c r="B13" s="23" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)</f>
-        <v>2376055.13333333</v>
-      </c>
-      <c r="C13" s="28" t="n">
+        <v>2379805.13333333</v>
+      </c>
+      <c r="C13" s="23" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7)</f>
-        <v>2787800.58693333</v>
-      </c>
-      <c r="D13" s="28" t="n">
+        <v>2791550.58693333</v>
+      </c>
+      <c r="D13" s="23" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7)</f>
-        <v>3233144.46954709</v>
+        <v>3236894.46954709</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B14" s="28" t="n">
+        <v>252</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <f aca="false">B12-B13</f>
-        <v>-1115107.13333333</v>
-      </c>
-      <c r="C14" s="28" t="n">
+        <v>-1118857.13333333</v>
+      </c>
+      <c r="C14" s="23" t="n">
         <f aca="false">C12-C13</f>
-        <v>1583969.17646667</v>
-      </c>
-      <c r="D14" s="28" t="n">
+        <v>1580219.17646667</v>
+      </c>
+      <c r="D14" s="23" t="n">
         <f aca="false">D12-D13</f>
-        <v>5356025.90045885</v>
+        <v>5352275.90045885</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B15" s="31" t="n">
+        <v>253</v>
+      </c>
+      <c r="B15" s="26" t="n">
         <f aca="false">B14/B12</f>
-        <v>-0.884340300578084</v>
-      </c>
-      <c r="C15" s="31" t="n">
+        <v>-0.887314253508736</v>
+      </c>
+      <c r="C15" s="26" t="n">
         <f aca="false">C14/C12</f>
-        <v>0.362317610988459</v>
-      </c>
-      <c r="D15" s="31" t="n">
+        <v>0.361459834801022</v>
+      </c>
+      <c r="D15" s="26" t="n">
         <f aca="false">D14/D12</f>
-        <v>0.623578956957532</v>
+        <v>0.623142360657953</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B16" s="28" t="n">
+        <v>254</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)</f>
-        <v>3079869.18333333</v>
-      </c>
-      <c r="C16" s="28" t="n">
+        <v>3087369.18333333</v>
+      </c>
+      <c r="C16" s="23" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8)</f>
-        <v>3641696.62093333</v>
-      </c>
-      <c r="D16" s="28" t="n">
+        <v>3649196.62093333</v>
+      </c>
+      <c r="D16" s="23" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8)</f>
-        <v>4249369.17744149</v>
+        <v>4256869.17744149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B17" s="28" t="n">
+        <v>255</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">B12-B16</f>
-        <v>-1818921.18333333</v>
-      </c>
-      <c r="C17" s="28" t="n">
+        <v>-1826421.18333333</v>
+      </c>
+      <c r="C17" s="23" t="n">
         <f aca="false">C12-C16</f>
-        <v>730073.142466666</v>
-      </c>
-      <c r="D17" s="28" t="n">
+        <v>722573.142466666</v>
+      </c>
+      <c r="D17" s="23" t="n">
         <f aca="false">D12-D16</f>
-        <v>4339801.19256445</v>
+        <v>4332301.19256445</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B18" s="31" t="n">
+        <v>256</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <f aca="false">B17/B12</f>
-        <v>-1.4425029290132</v>
-      </c>
-      <c r="C18" s="31" t="n">
+        <v>-1.4484508348745</v>
+      </c>
+      <c r="C18" s="26" t="n">
         <f aca="false">C17/C12</f>
-        <v>0.166997161785317</v>
-      </c>
-      <c r="D18" s="31" t="n">
+        <v>0.165281609410444</v>
+      </c>
+      <c r="D18" s="26" t="n">
         <f aca="false">D17/D12</f>
-        <v>0.505264304422156</v>
+        <v>0.504391111822998</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B21" s="34" t="str">
+        <v>258</v>
+      </c>
+      <c r="B21" s="28" t="str">
         <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
         <v>1 / 2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B22" s="28" t="n">
+        <v>259</v>
+      </c>
+      <c r="B22" s="23" t="n">
         <f aca="false">Engine!$B$33</f>
         <v>2034793</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="31" t="n">
+        <v>260</v>
+      </c>
+      <c r="B23" s="26" t="n">
         <f aca="false">Engine!$B$20</f>
-        <v>0.773132732424747</v>
+        <v>0.752250631659297</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B24" s="32" t="n">
+        <v>261</v>
+      </c>
+      <c r="B24" s="27" t="n">
         <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14))</f>
-        <v>6.6476944913725</v>
+        <v>6.25309423974321</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" s="28" t="n">
+        <v>262</v>
+      </c>
+      <c r="B25" s="23" t="n">
         <f aca="false">Engine!$B$25</f>
         <v>52500</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B26" s="32" t="n">
+        <v>263</v>
+      </c>
+      <c r="B26" s="27" t="n">
         <f aca="false">(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42)</f>
         <v>26.9379395382105</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B27" s="28" t="str">
+        <v>264</v>
+      </c>
+      <c r="B27" s="23" t="str">
         <f aca="false">Engine!$B$51</f>
         <v>not entered</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B28" s="33" t="n">
+        <v>230</v>
+      </c>
+      <c r="B28" s="23" t="n">
         <f aca="false">Engine!$B$54</f>
         <v>360158</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B29" s="33" t="n">
+        <v>232</v>
+      </c>
+      <c r="B29" s="23" t="n">
         <f aca="false">Engine!$B$55</f>
-        <v>212968.95</v>
+        <v>209218.95</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B30" s="30" t="n">
+        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14))</f>
+        <v>6.25309423974321</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3480,33 +3668,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B5" s="29" t="n">
+        <v>273</v>
+      </c>
+      <c r="B5" s="24" t="n">
         <f aca="false">8*RateCard!$B$36</f>
         <v>5840</v>
       </c>
@@ -3520,9 +3708,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B6" s="28" t="n">
+        <v>274</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
         <v>52005.2</v>
       </c>
@@ -3536,9 +3724,9 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="28" t="n">
+        <v>275</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>52500</v>
       </c>
@@ -3552,9 +3740,9 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="28" t="n">
+        <v>276</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
         <v>574.166666666667</v>
       </c>
@@ -3568,9 +3756,9 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B9" s="28" t="n">
+        <v>277</v>
+      </c>
+      <c r="B9" s="23" t="n">
         <f aca="false">B6+B7+B8</f>
         <v>105079.366666667</v>
       </c>
@@ -3584,9 +3772,9 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" s="28" t="n">
+        <v>278</v>
+      </c>
+      <c r="B10" s="23" t="n">
         <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
@@ -3600,9 +3788,9 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="28" t="n">
+        <v>279</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
         <v>675000</v>
       </c>
@@ -3616,9 +3804,9 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" s="28" t="n">
+        <v>280</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
         <v>4166.64583333333</v>
       </c>
@@ -3632,9 +3820,9 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B13" s="28" t="n">
+        <v>281</v>
+      </c>
+      <c r="B13" s="23" t="n">
         <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
         <v>7320</v>
       </c>
@@ -3648,9 +3836,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B14" s="28" t="n">
+        <v>282</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
         <v>3097.22222222222</v>
       </c>
@@ -3664,9 +3852,9 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B15" s="28" t="n">
+        <v>283</v>
+      </c>
+      <c r="B15" s="23" t="n">
         <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
@@ -3680,9 +3868,9 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B16" s="28" t="n">
+        <v>284</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <f aca="false">B13+B14+B15</f>
         <v>11992.2222222222</v>
       </c>
@@ -3696,9 +3884,9 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B17" s="28" t="n">
+        <v>285</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">1*RateCard!$B$33</f>
         <v>11387</v>
       </c>
@@ -3712,9 +3900,9 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B18" s="28" t="n">
+        <v>286</v>
+      </c>
+      <c r="B18" s="23" t="n">
         <f aca="false">B10*0.0281</f>
         <v>38210.1833</v>
       </c>
@@ -3728,9 +3916,9 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B19" s="28" t="n">
+        <v>287</v>
+      </c>
+      <c r="B19" s="23" t="n">
         <f aca="false">B11*0.0281+B12</f>
         <v>23134.1458333333</v>
       </c>
@@ -3744,9 +3932,9 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B20" s="28" t="n">
+        <v>288</v>
+      </c>
+      <c r="B20" s="23" t="n">
         <f aca="false">B18+B19+B16</f>
         <v>73336.5513555556</v>
       </c>
@@ -3760,7 +3948,417 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="B5" s="32" t="n">
+        <v>105079</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="32" t="n">
+        <v>0.49491</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="B8" s="32" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="B11" s="32" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B12" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="32" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="B21" s="33" t="str">
+        <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0),"YES","NO — set fixture first")</f>
+        <v>NO — set fixture first</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="B24" s="35" t="n">
+        <f aca="false">Engine!$B$7</f>
+        <v>5900</v>
+      </c>
+      <c r="C24" s="36" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D24" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B24-C24)&lt;=MAX(1,0.0001*MAX(ABS(C24),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" s="37" t="n">
+        <f aca="false">Engine!$B$4</f>
+        <v>71.24</v>
+      </c>
+      <c r="C25" s="38" t="n">
+        <v>71.24</v>
+      </c>
+      <c r="D25" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B25-C25)&lt;=MAX(1,0.0001*MAX(ABS(C25),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B26" s="39" t="n">
+        <f aca="false">Engine!$B$11</f>
+        <v>4.79741935483871</v>
+      </c>
+      <c r="C26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B26-C26)&lt;=MAX(1,0.0001*MAX(ABS(C26),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" s="35" t="n">
+        <f aca="false">Engine!$B$18</f>
+        <v>1</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B27-C27)&lt;=MAX(1,0.0001*MAX(ABS(C27),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B28" s="35" t="n">
+        <f aca="false">Engine!$B$19</f>
+        <v>2</v>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B28-C28)&lt;=MAX(1,0.0001*MAX(ABS(C28),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B29" s="41" t="n">
+        <f aca="false">Engine!$B$31</f>
+        <v>1359793</v>
+      </c>
+      <c r="C29" s="42" t="n">
+        <v>1359793</v>
+      </c>
+      <c r="D29" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B29-C29)&lt;=MAX(1,0.0001*MAX(ABS(C29),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="B30" s="41" t="n">
+        <f aca="false">Engine!$B$32</f>
+        <v>675000</v>
+      </c>
+      <c r="C30" s="42" t="n">
+        <v>675000</v>
+      </c>
+      <c r="D30" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B30-C30)&lt;=MAX(1,0.0001*MAX(ABS(C30),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B31" s="41" t="n">
+        <f aca="false">Engine!$B$39</f>
+        <v>4166.64583333333</v>
+      </c>
+      <c r="C31" s="42" t="n">
+        <v>4167</v>
+      </c>
+      <c r="D31" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B31-C31)&lt;=MAX(1,0.0001*MAX(ABS(C31),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B32" s="41" t="n">
+        <f aca="false">Engine!$B$35</f>
+        <v>7320</v>
+      </c>
+      <c r="C32" s="42" t="n">
+        <v>7320</v>
+      </c>
+      <c r="D32" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B32-C32)&lt;=MAX(1,0.0001*MAX(ABS(C32),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B33" s="41" t="n">
+        <f aca="false">Engine!$B$37</f>
+        <v>3111.11111111111</v>
+      </c>
+      <c r="C33" s="42" t="n">
+        <v>3111</v>
+      </c>
+      <c r="D33" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B33-C33)&lt;=MAX(1,0.0001*MAX(ABS(C33),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="41" t="n">
+        <f aca="false">Engine!$B$38</f>
+        <v>1575</v>
+      </c>
+      <c r="C34" s="42" t="n">
+        <v>1575</v>
+      </c>
+      <c r="D34" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B34-C34)&lt;=MAX(1,0.0001*MAX(ABS(C34),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B35" s="41" t="n">
+        <f aca="false">Engine!$B$42</f>
+        <v>16172.7569444444</v>
+      </c>
+      <c r="C35" s="42" t="n">
+        <v>16173</v>
+      </c>
+      <c r="D35" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B35-C35)&lt;=MAX(1,0.0001*MAX(ABS(C35),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="B36" s="41" t="n">
+        <f aca="false">Engine!$B$54</f>
+        <v>360158</v>
+      </c>
+      <c r="C36" s="42" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D36" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B36-C36)&lt;=MAX(1,0.0001*MAX(ABS(C36),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B37" s="41" t="n">
+        <f aca="false">Engine!$B$55</f>
+        <v>209218.95</v>
+      </c>
+      <c r="C37" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="29" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B37-C37)&lt;=MAX(1,0.0001*MAX(ABS(C37),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reverse-tco-model-v1.xlsx
+++ b/docs/reverse-tco-model-v1.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="341">
   <si>
     <t xml:space="preserve">Reverse TCO Tool v1 — Cloud AIaaS Spend to On-Prem NVIDIA Infrastructure</t>
   </si>
@@ -93,6 +93,9 @@
     <t xml:space="preserve">Hardware registry note: only rows marked Priced?=YES are valid selections; placeholder rows produce nonsensical results and are guarded in the web app.</t>
   </si>
   <si>
+    <t xml:space="preserve">V2.1 (audit round 3): floor-case headroom/exhaustion computed separately and warning keys on the EARLIER exhaustion; payback shows no-crossover text instead of negative months; spend/storage reconciliation (Engine STEP 8 + Results row 32) flags storage inconsistent with the stated bill; unpriced hardware now hard-errors (NA error); residual also excludes the software suite; provider and lease-term fields labeled for scope; regression coverage extended.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rate Card — all editable (blue). Effective date + source in column C.</t>
   </si>
   <si>
@@ -378,7 +381,7 @@
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS / Azure / GCP / OCI / CoreWeave. v1 rate card is AWS-class; extend RateCard for others.</t>
+    <t xml:space="preserve">WORKBOOK: AWS rates only (web app routes all five providers). Selecting others here still computes AWS-class economics.</t>
   </si>
   <si>
     <t xml:space="preserve">TIER 2 — refine when known (defaults otherwise)</t>
@@ -495,7 +498,7 @@
     <t xml:space="preserve">Lease term (months)</t>
   </si>
   <si>
-    <t xml:space="preserve">Used only when a factor is entered</t>
+    <t xml:space="preserve">Informational only — not used in any workbook calculation (web/deploy-phase financing field)</t>
   </si>
   <si>
     <t xml:space="preserve">V1.2 — TRANSITION, FACILITY, RESILIENCE, RESIDUAL</t>
@@ -633,7 +636,7 @@
     <t xml:space="preserve">Per-system acquisition ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">System + SW suite + 3 fabrics + professional services</t>
+    <t xml:space="preserve">v2.1 guard: unpriced hardware (system cost &lt; $100K) deliberately returns an NA error (audit: hard error, not a note)</t>
   </si>
   <si>
     <t xml:space="preserve">Compute racks</t>
@@ -729,12 +732,24 @@
     <t xml:space="preserve">Residual credit at horizon, adjusted ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">v2.0: prof services excluded from residual basis (no resale value)</t>
+    <t xml:space="preserve">v2.1: residual basis excludes prof services AND software suite (subscription, non-transferable)</t>
   </si>
   <si>
     <t xml:space="preserve">Residual credit at horizon, floor ($)</t>
   </si>
   <si>
+    <t xml:space="preserve">STEP 8 — Spend/storage reconciliation (v2.1, audit round 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud storage+egress implied by entered PB ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-compute budget in stated bill ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconciliation status</t>
+  </si>
+  <si>
     <t xml:space="preserve">Results — Cloud vs. On-Prem</t>
   </si>
   <si>
@@ -810,10 +825,10 @@
     <t xml:space="preserve">Total capex, adjusted ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Growth headroom in year-1 fleet (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Years until growth exhausts headroom</t>
+    <t xml:space="preserve">Growth headroom in year-1 fleet (adjusted / floor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years until growth exhausts headroom (adjusted / floor)</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud storage + egress spend displaced by on-prem storage modeled above ($/mo)</t>
@@ -825,10 +840,13 @@
     <t xml:space="preserve">Lease view, adjusted ($/mo, if factor entered)</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ WORKBOOK LIMITATION: fleet expansion under growth is NOT modeled here (web engine v2.0 models it). Headroom exhausted after (years):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totals for horizons beyond that year understate on-prem cost; treat longer-horizon results as directional only.</t>
+    <t xml:space="preserve">⚠ WORKBOOK LIMITATION: fleet expansion under growth is NOT modeled here (web engine v2.x models it). Earliest exhaustion, either case (years):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals for horizons beyond the EARLIER of the two exhaustion years understate on-prem cost (the floor case usually exhausts first — audit round 3). Treat longer-horizon results as directional only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend/storage reconciliation</t>
   </si>
   <si>
     <t xml:space="preserve">Validation — reproduce NVIDIA DGX TCO tool Test 1 from this rate card</t>
@@ -1014,14 +1032,32 @@
     <t xml:space="preserve">Residual credit (Engine!B55)</t>
   </si>
   <si>
-    <t xml:space="preserve">One-time expected = cloud exit egress only (1 PB × $0.05/GB = $50,000) since migration/dual-run are zeroed in the fixture.</t>
+    <t xml:space="preserve">Cloud storage + egress $/mo (Engine!B25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud admin $/mo (Engine!B26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud monthly total (compute+storage+admin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equinix opex option $/mo (Engine!B41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lease view (blank factor → text) (Engine!B51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not entered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2.1: coverage extended to cloud storage/admin/total, Equinix option and lease text; fixture check now verifies GPU class, facility, system and provider.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -1031,9 +1067,6 @@
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
     <numFmt numFmtId="171" formatCode="0.00\x"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="174" formatCode="0.00\x"/>
-    <numFmt numFmtId="175" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1161,7 +1194,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1275,62 +1308,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1586,7 +1563,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1699,14 +1676,19 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1735,89 +1717,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>113.93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>68.36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>2.88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.05</v>
@@ -1826,18 +1808,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>189000</v>
@@ -1846,7 +1828,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>5000</v>
@@ -1855,29 +1837,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>8</v>
@@ -1886,23 +1868,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>25000</v>
@@ -1911,29 +1893,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>1200000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>100000</v>
@@ -1942,18 +1924,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>500000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>33333</v>
@@ -1962,7 +1944,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
@@ -1971,29 +1953,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>3000</v>
@@ -2002,7 +1984,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>2000</v>
@@ -2011,7 +1993,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
@@ -2020,7 +2002,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>189000</v>
@@ -2029,40 +2011,40 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>11387</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>730</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>0.04</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2094,47 +2076,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>8</v>
@@ -2161,15 +2143,15 @@
         <v>2</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>8</v>
@@ -2196,15 +2178,15 @@
         <v>2</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>8</v>
@@ -2231,15 +2213,15 @@
         <v>2</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>72</v>
@@ -2266,35 +2248,35 @@
         <v>1</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2323,32 +2305,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" s="14" t="n">
         <v>4.4</v>
@@ -2363,12 +2345,12 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>2.2</v>
@@ -2383,12 +2365,12 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>1.5</v>
@@ -2403,12 +2385,12 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>1</v>
@@ -2423,17 +2405,17 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2462,305 +2444,305 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>105079</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>0.25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" s="15" t="n">
         <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>0.85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>1.3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B26" s="20" t="n">
         <v>1.3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B30" s="19" t="n">
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B33" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B34" s="15" t="n">
         <v>100000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B35" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B36" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B37" s="17" t="n">
         <v>0.15</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2779,7 +2761,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
@@ -2789,47 +2771,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B4" s="22" t="n">
         <f aca="false">(Inputs!$B$10*(RateCard!$B$4+RateCard!$B$6)+(1-Inputs!$B$10)*(RateCard!$B$5+RateCard!$B$7))*(1+RateCard!$B$15)</f>
         <v>71.24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
         <v>52539.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">B5/B4</f>
@@ -2839,48 +2821,48 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*RateCard!$B$16)</f>
         <v>5900</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
         <v>2.83870967741935</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
         <v>4.79741935483871</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">B7/B11</f>
@@ -2890,24 +2872,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">B7</f>
         <v>5900</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -2917,19 +2899,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
         <v>4964</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" s="24" t="n">
         <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
@@ -2939,7 +2921,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B19" s="24" t="n">
         <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
@@ -2949,24 +2931,24 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B20" s="26" t="n">
         <f aca="false">1-B12/(B18*B17)</f>
         <v>0.752250631659297</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="27" t="n">
         <f aca="false">Inputs!$B$11*Inputs!$B$12</f>
@@ -2976,7 +2958,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" s="27" t="n">
         <f aca="false">Inputs!$B$11*(1-Inputs!$B$12)</f>
@@ -2986,19 +2968,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+Inputs!$B$11*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>52500</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B26" s="23" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -3008,24 +2990,24 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B29" s="23" t="n">
-        <f aca="false">INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20</f>
+        <f aca="false">IF(INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;100000,NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
         <v>744793</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B30" s="24" t="n">
         <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
@@ -3035,19 +3017,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B31" s="23" t="n">
         <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
@@ -3057,7 +3039,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B33" s="23" t="n">
         <f aca="false">B31+B32</f>
@@ -3067,7 +3049,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -3077,19 +3059,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B35" s="23" t="n">
         <f aca="false">(B18*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16</f>
         <v>7320</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B36" s="27" t="n">
         <f aca="false">B30+Inputs!$B$11*RateCard!$B$27</f>
@@ -3099,43 +3081,43 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B37" s="23" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/36</f>
         <v>3111.11111111111</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B38" s="23" t="n">
         <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B39" s="23" t="n">
         <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
         <v>4166.64583333333</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B40" s="23" t="n">
         <f aca="false">B35+B37+B38+B39</f>
@@ -3145,19 +3127,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B41" s="23" t="n">
         <f aca="false">B18*RateCard!$B$33+B39</f>
         <v>15553.6458333333</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B42" s="23" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
@@ -3167,12 +3149,12 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B45" s="23" t="n">
         <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
@@ -3182,7 +3164,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B46" s="23" t="n">
         <f aca="false">(B19*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+Inputs!$B$11*RateCard!$B$27)/36+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
@@ -3192,7 +3174,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">B19*RateCard!$B$33+B39</f>
@@ -3202,7 +3184,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B48" s="23" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
@@ -3212,24 +3194,24 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B51" s="23" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
         <v>not entered</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B52" s="23" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
@@ -3239,42 +3221,74 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B54" s="23" t="n">
         <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+Inputs!$B$11*1000000*RateCard!$B$10</f>
         <v>360158</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B55" s="23" t="n">
-        <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20)+B32)</f>
-        <v>209218.95</v>
+        <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
+        <v>187798.95</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B56" s="23" t="n">
-        <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20)+B32)</f>
-        <v>317187.9</v>
+        <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
+        <v>274347.9</v>
       </c>
       <c r="C56" s="3"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B58" s="23" t="n">
+        <f aca="false">Engine!$B$25</f>
+        <v>52500</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59" s="23" t="n">
+        <f aca="false">Inputs!$B$4*(1-Inputs!$B$13)</f>
+        <v>52539.5</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B60" s="4" t="str">
+        <f aca="false">IF(B58&gt;B59*1.02,"⚠ MISMATCH: entered storage implies $"&amp;TEXT(B58,"#,##0")&amp;"/mo but only $"&amp;TEXT(B59,"#,##0")&amp;"/mo of the stated bill is non-compute — reduce storage PB or raise the bill","OK — storage consistent with stated bill")</f>
+        <v>OK — storage consistent with stated bill</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3292,7 +3306,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -3301,40 +3315,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
@@ -3359,7 +3373,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
@@ -3384,7 +3398,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
@@ -3409,24 +3423,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM($B$6:B6)</f>
@@ -3443,114 +3457,114 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B13" s="23" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)</f>
-        <v>2379805.13333333</v>
+        <v>2401225.13333333</v>
       </c>
       <c r="C13" s="23" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7)</f>
-        <v>2791550.58693333</v>
+        <v>2812970.58693333</v>
       </c>
       <c r="D13" s="23" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7)</f>
-        <v>3236894.46954709</v>
+        <v>3258314.46954709</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B14" s="23" t="n">
         <f aca="false">B12-B13</f>
-        <v>-1118857.13333333</v>
+        <v>-1140277.13333333</v>
       </c>
       <c r="C14" s="23" t="n">
         <f aca="false">C12-C13</f>
-        <v>1580219.17646667</v>
+        <v>1558799.17646667</v>
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">D12-D13</f>
-        <v>5352275.90045885</v>
+        <v>5330855.90045885</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B14/B12</f>
-        <v>-0.887314253508736</v>
+        <v>-0.904301472648621</v>
       </c>
       <c r="C15" s="26" t="n">
         <f aca="false">C14/C12</f>
-        <v>0.361459834801022</v>
+        <v>0.356560217218384</v>
       </c>
       <c r="D15" s="26" t="n">
         <f aca="false">D14/D12</f>
-        <v>0.623142360657953</v>
+        <v>0.620648522594757</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)</f>
-        <v>3087369.18333333</v>
+        <v>3130209.18333333</v>
       </c>
       <c r="C16" s="23" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8)</f>
-        <v>3649196.62093333</v>
+        <v>3692036.62093333</v>
       </c>
       <c r="D16" s="23" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8)</f>
-        <v>4256869.17744149</v>
+        <v>4299709.17744149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">B12-B16</f>
-        <v>-1826421.18333333</v>
+        <v>-1869261.18333333</v>
       </c>
       <c r="C17" s="23" t="n">
         <f aca="false">C12-C16</f>
-        <v>722573.142466666</v>
+        <v>679733.142466666</v>
       </c>
       <c r="D17" s="23" t="n">
         <f aca="false">D12-D16</f>
-        <v>4332301.19256445</v>
+        <v>4289461.19256445</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B18" s="26" t="n">
         <f aca="false">B17/B12</f>
-        <v>-1.4484508348745</v>
+        <v>-1.48242527315427</v>
       </c>
       <c r="C18" s="26" t="n">
         <f aca="false">C17/C12</f>
-        <v>0.165281609410444</v>
+        <v>0.155482374245168</v>
       </c>
       <c r="D18" s="26" t="n">
         <f aca="false">D17/D12</f>
-        <v>0.504391111822998</v>
+        <v>0.499403435696605</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B21" s="28" t="str">
         <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
@@ -3559,7 +3573,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B22" s="23" t="n">
         <f aca="false">Engine!$B$33</f>
@@ -3568,25 +3582,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B23" s="26" t="n">
-        <f aca="false">Engine!$B$20</f>
-        <v>0.752250631659297</v>
+        <v>265</v>
+      </c>
+      <c r="B23" s="26" t="str">
+        <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/(Engine!$B$19*Engine!$B$17),"0.0%")</f>
+        <v>75.2% / 40.6%</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B24" s="27" t="n">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14))</f>
-        <v>6.25309423974321</v>
+        <v>266</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/(Engine!$B$19*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
+        <v>6.3 / 2.3</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">Engine!$B$25</f>
@@ -3595,16 +3609,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B26" s="27" t="n">
-        <f aca="false">(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42)</f>
+        <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"no crossover at current spend and assumptions",IF((Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42)&gt;60,"no crossover within modeled horizon (&gt;60 mo)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42)))</f>
         <v>26.9379395382105</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B27" s="23" t="str">
         <f aca="false">Engine!$B$51</f>
@@ -3613,7 +3627,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B28" s="23" t="n">
         <f aca="false">Engine!$B$54</f>
@@ -3622,25 +3636,34 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">Engine!$B$55</f>
-        <v>209218.95</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="B30" s="30" t="n">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14))</f>
-        <v>6.25309423974321</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>187798.95</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" s="27" t="n">
+        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/(Engine!$B$19*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
+        <v>2.3321610412924</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B32" s="1" t="str">
+        <f aca="false">Engine!$B$60</f>
+        <v>OK — storage consistent with stated bill</v>
       </c>
     </row>
   </sheetData>
@@ -3668,31 +3691,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B5" s="24" t="n">
         <f aca="false">8*RateCard!$B$36</f>
@@ -3708,7 +3731,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
@@ -3724,7 +3747,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
@@ -3740,7 +3763,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -3756,7 +3779,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B9" s="23" t="n">
         <f aca="false">B6+B7+B8</f>
@@ -3772,7 +3795,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
@@ -3788,7 +3811,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B11" s="23" t="n">
         <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
@@ -3804,7 +3827,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
@@ -3820,7 +3843,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B13" s="23" t="n">
         <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
@@ -3836,7 +3859,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B14" s="23" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
@@ -3852,7 +3875,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
@@ -3868,7 +3891,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">B13+B14+B15</f>
@@ -3884,7 +3907,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">1*RateCard!$B$33</f>
@@ -3900,7 +3923,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B18" s="23" t="n">
         <f aca="false">B10*0.0281</f>
@@ -3916,7 +3939,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B19" s="23" t="n">
         <f aca="false">B11*0.0281+B12</f>
@@ -3932,7 +3955,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B20" s="23" t="n">
         <f aca="false">B18+B19+B16</f>
@@ -3948,7 +3971,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3967,398 +3990,478 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="B5" s="32" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="13" t="n">
         <v>105079</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="B6" s="32" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="13" t="n">
         <v>0.49491</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="B8" s="32" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="32" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>298</v>
-      </c>
-      <c r="B10" s="32" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="B11" s="32" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" s="13" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="B12" s="32" t="n">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="B14" s="32" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="B15" s="32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="B17" s="32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>306</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>308</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" s="33" t="str">
-        <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0),"YES","NO — set fixture first")</f>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B21" s="28" t="str">
+        <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200/B300-class",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS"),"YES","NO — set fixture first")</f>
         <v>NO — set fixture first</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34" t="s">
-        <v>311</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B24" s="35" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B24" s="24" t="n">
         <f aca="false">Engine!$B$7</f>
         <v>5900</v>
       </c>
-      <c r="C24" s="36" t="n">
+      <c r="C24" s="11" t="n">
         <v>5840</v>
       </c>
-      <c r="D24" s="29" t="str">
+      <c r="D24" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B24-C24)&lt;=MAX(1,0.0001*MAX(ABS(C24),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B25" s="37" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" s="22" t="n">
         <f aca="false">Engine!$B$4</f>
         <v>71.24</v>
       </c>
-      <c r="C25" s="38" t="n">
+      <c r="C25" s="7" t="n">
         <v>71.24</v>
       </c>
-      <c r="D25" s="29" t="str">
+      <c r="D25" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B25-C25)&lt;=MAX(1,0.0001*MAX(ABS(C25),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B26" s="39" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B26" s="25" t="n">
         <f aca="false">Engine!$B$11</f>
         <v>4.79741935483871</v>
       </c>
-      <c r="C26" s="40" t="n">
+      <c r="C26" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="29" t="str">
+      <c r="D26" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B26-C26)&lt;=MAX(1,0.0001*MAX(ABS(C26),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>317</v>
-      </c>
-      <c r="B27" s="35" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B27" s="24" t="n">
         <f aca="false">Engine!$B$18</f>
         <v>1</v>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="29" t="str">
+      <c r="D27" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B27-C27)&lt;=MAX(1,0.0001*MAX(ABS(C27),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>318</v>
-      </c>
-      <c r="B28" s="35" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" s="24" t="n">
         <f aca="false">Engine!$B$19</f>
         <v>2</v>
       </c>
-      <c r="C28" s="36" t="n">
+      <c r="C28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="29" t="str">
+      <c r="D28" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B28-C28)&lt;=MAX(1,0.0001*MAX(ABS(C28),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>319</v>
-      </c>
-      <c r="B29" s="41" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B29" s="23" t="n">
         <f aca="false">Engine!$B$31</f>
         <v>1359793</v>
       </c>
-      <c r="C29" s="42" t="n">
+      <c r="C29" s="9" t="n">
         <v>1359793</v>
       </c>
-      <c r="D29" s="29" t="str">
+      <c r="D29" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B29-C29)&lt;=MAX(1,0.0001*MAX(ABS(C29),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>320</v>
-      </c>
-      <c r="B30" s="41" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B30" s="23" t="n">
         <f aca="false">Engine!$B$32</f>
         <v>675000</v>
       </c>
-      <c r="C30" s="42" t="n">
+      <c r="C30" s="9" t="n">
         <v>675000</v>
       </c>
-      <c r="D30" s="29" t="str">
+      <c r="D30" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B30-C30)&lt;=MAX(1,0.0001*MAX(ABS(C30),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>321</v>
-      </c>
-      <c r="B31" s="41" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B31" s="23" t="n">
         <f aca="false">Engine!$B$39</f>
         <v>4166.64583333333</v>
       </c>
-      <c r="C31" s="42" t="n">
+      <c r="C31" s="9" t="n">
         <v>4167</v>
       </c>
-      <c r="D31" s="29" t="str">
+      <c r="D31" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B31-C31)&lt;=MAX(1,0.0001*MAX(ABS(C31),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="B32" s="41" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B32" s="23" t="n">
         <f aca="false">Engine!$B$35</f>
         <v>7320</v>
       </c>
-      <c r="C32" s="42" t="n">
+      <c r="C32" s="9" t="n">
         <v>7320</v>
       </c>
-      <c r="D32" s="29" t="str">
+      <c r="D32" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B32-C32)&lt;=MAX(1,0.0001*MAX(ABS(C32),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>323</v>
-      </c>
-      <c r="B33" s="41" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B33" s="23" t="n">
         <f aca="false">Engine!$B$37</f>
         <v>3111.11111111111</v>
       </c>
-      <c r="C33" s="42" t="n">
+      <c r="C33" s="9" t="n">
         <v>3111</v>
       </c>
-      <c r="D33" s="29" t="str">
+      <c r="D33" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B33-C33)&lt;=MAX(1,0.0001*MAX(ABS(C33),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>324</v>
-      </c>
-      <c r="B34" s="41" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B34" s="23" t="n">
         <f aca="false">Engine!$B$38</f>
         <v>1575</v>
       </c>
-      <c r="C34" s="42" t="n">
+      <c r="C34" s="9" t="n">
         <v>1575</v>
       </c>
-      <c r="D34" s="29" t="str">
+      <c r="D34" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B34-C34)&lt;=MAX(1,0.0001*MAX(ABS(C34),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>325</v>
-      </c>
-      <c r="B35" s="41" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B35" s="23" t="n">
         <f aca="false">Engine!$B$42</f>
         <v>16172.7569444444</v>
       </c>
-      <c r="C35" s="42" t="n">
+      <c r="C35" s="9" t="n">
         <v>16173</v>
       </c>
-      <c r="D35" s="29" t="str">
+      <c r="D35" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B35-C35)&lt;=MAX(1,0.0001*MAX(ABS(C35),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>326</v>
-      </c>
-      <c r="B36" s="41" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B36" s="23" t="n">
         <f aca="false">Engine!$B$54</f>
         <v>360158</v>
       </c>
-      <c r="C36" s="42" t="n">
+      <c r="C36" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="D36" s="29" t="str">
+      <c r="D36" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B36-C36)&lt;=MAX(1,0.0001*MAX(ABS(C36),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="B37" s="41" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B37" s="23" t="n">
         <f aca="false">Engine!$B$55</f>
-        <v>209218.95</v>
-      </c>
-      <c r="C37" s="42" t="n">
+        <v>187798.95</v>
+      </c>
+      <c r="C37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="29" t="str">
+      <c r="D37" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B37-C37)&lt;=MAX(1,0.0001*MAX(ABS(C37),1)),"PASS","FAIL"))</f>
         <v>FIXTURE NOT LOADED</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>328</v>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B38" s="23" t="n">
+        <f aca="false">Engine!$B$25</f>
+        <v>52500</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>52500</v>
+      </c>
+      <c r="D38" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B38-C38)&lt;=MAX(1,0.0001*MAX(ABS(C38),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B39" s="23" t="n">
+        <f aca="false">Engine!$B$26</f>
+        <v>574.166666666667</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>574</v>
+      </c>
+      <c r="D39" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B39-C39)&lt;=MAX(1,0.0001*MAX(ABS(C39),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B40" s="23" t="n">
+        <f aca="false">Engine!$B$5+Engine!$B$25+Engine!$B$26</f>
+        <v>105613.666666667</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>105079</v>
+      </c>
+      <c r="D40" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B40-C40)&lt;=MAX(1,0.0001*MAX(ABS(C40),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B41" s="23" t="n">
+        <f aca="false">Engine!$B$41</f>
+        <v>15553.6458333333</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>15554</v>
+      </c>
+      <c r="D41" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B41-C41)&lt;=MAX(1,0.0001*MAX(ABS(C41),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B42" s="28" t="str">
+        <f aca="false">Engine!$B$51</f>
+        <v>not entered</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D42" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B42=C42,"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reverse-tco-model-v1.xlsx
+++ b/docs/reverse-tco-model-v1.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Results" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Validation" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="EngineRegression" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Crossover" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="349">
   <si>
     <t xml:space="preserve">Reverse TCO Tool v1 — Cloud AIaaS Spend to On-Prem NVIDIA Infrastructure</t>
   </si>
@@ -96,6 +97,12 @@
     <t xml:space="preserve">V2.1 (audit round 3): floor-case headroom/exhaustion computed separately and warning keys on the EARLIER exhaustion; payback shows no-crossover text instead of negative months; spend/storage reconciliation (Engine STEP 8 + Results row 32) flags storage inconsistent with the stated bill; unpriced hardware now hard-errors (NA error); residual also excludes the software suite; provider and lease-term fields labeled for scope; regression coverage extended.</t>
   </si>
   <si>
+    <t xml:space="preserve">SCOPE (v2.2): this workbook is the AUDITABLE REFERENCE IMPLEMENTATION for the core sizing and TCO formulas. The deployed web application extends it with dynamic fleet growth under demand, five-provider rate routing, capacity/unit-economics estimates and UI-level validation. True end-to-end parity requires the automated Excel↔JavaScript fixture suite (deploy-phase item).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROWTH CONVENTION (documented, both engines): cloud compute spend grows at the selected demand-growth rate; cloud non-compute spend and all on-prem opex grow at the 4%/yr ops rate. Crossover (Results!B26) is computed from cumulative monthly cash flows on the Crossover sheet; static payback is retained as a secondary metric only. Equinix bundle note: per-DGX rate covers system colocation; separate storage-rack colocation is not separately modeled (storage support is).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rate Card — all editable (blue). Effective date + source in column C.</t>
   </si>
   <si>
@@ -273,7 +280,7 @@
     <t xml:space="preserve">Mgmt fabric</t>
   </si>
   <si>
-    <t xml:space="preserve">kW avg</t>
+    <t xml:space="preserve">kW per system (avg)</t>
   </si>
   <si>
     <t xml:space="preserve">Sys/rack</t>
@@ -609,7 +616,7 @@
     <t xml:space="preserve">Growth headroom (adjusted case)</t>
   </si>
   <si>
-    <t xml:space="preserve">Idle capacity = free growth runway</t>
+    <t xml:space="preserve">v2.2: headroom uses PRODUCTIVE systems (total − N+1 spare); spare capacity is not growth capacity</t>
   </si>
   <si>
     <t xml:space="preserve">STEP 4 — Storage</t>
@@ -636,7 +643,7 @@
     <t xml:space="preserve">Per-system acquisition ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">v2.1 guard: unpriced hardware (system cost &lt; $100K) deliberately returns an NA error (audit: hard error, not a note)</t>
+    <t xml:space="preserve">v2.2 guard: requires Hardware Priced?=YES and GPU count &gt; 0; otherwise deliberate NA error</t>
   </si>
   <si>
     <t xml:space="preserve">Compute racks</t>
@@ -741,7 +748,7 @@
     <t xml:space="preserve">STEP 8 — Spend/storage reconciliation (v2.1, audit round 3)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud storage+egress implied by entered PB ($/mo)</t>
+    <t xml:space="preserve">Reconstructed non-compute (storage + egress + cloud admin) ($/mo)</t>
   </si>
   <si>
     <t xml:space="preserve">Non-compute budget in stated bill ($/mo)</t>
@@ -834,7 +841,7 @@
     <t xml:space="preserve">Cloud storage + egress spend displaced by on-prem storage modeled above ($/mo)</t>
   </si>
   <si>
-    <t xml:space="preserve">Simple payback, adjusted (months, capex + one-time vs current bill)</t>
+    <t xml:space="preserve">Crossover month (cumulative monthly cash flows, adjusted case)</t>
   </si>
   <si>
     <t xml:space="preserve">Lease view, adjusted ($/mo, if factor entered)</t>
@@ -849,6 +856,9 @@
     <t xml:space="preserve">Spend/storage reconciliation</t>
   </si>
   <si>
+    <t xml:space="preserve">Simple static payback, adjusted (months — SECONDARY metric only)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Validation — reproduce NVIDIA DGX TCO tool Test 1 from this rate card</t>
   </si>
   <si>
@@ -1051,6 +1061,21 @@
   </si>
   <si>
     <t xml:space="preserve">v2.1: coverage extended to cloud storage/admin/total, Equinix option and lease text; fixture check now verifies GPU class, facility, system and provider.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud cum ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-prem cum ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crossed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2.2: cumulative monthly cash flows (audit round 4). Cloud compute grows at demand rate, non-compute at 4%/yr, both stepped annually; on-prem = capex+one-time at month 1 + opex growing 4%/yr. Residual credit excluded (realized only at exit).</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1219,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1244,6 +1269,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1308,6 +1337,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1563,7 +1596,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1689,6 +1722,1076 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="n">
+        <f aca="false">(Engine!$B$5*(1+Inputs!$B$14)^INT((1-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((1-1)/12))</f>
+        <v>105613.666666667</v>
+      </c>
+      <c r="C2" s="30" t="n">
+        <f aca="false">Engine!$B$33+Engine!$B$54+(Engine!$B$42*1.04^INT((1-1)/12))</f>
+        <v>2411123.75694444</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <f aca="false">IF(B2&gt;=C2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="30" t="n">
+        <f aca="false">B2+(Engine!$B$5*(1+Inputs!$B$14)^INT((2-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((2-1)/12))</f>
+        <v>211227.333333333</v>
+      </c>
+      <c r="C3" s="30" t="n">
+        <f aca="false">C2+(Engine!$B$42*1.04^INT((2-1)/12))</f>
+        <v>2427296.51388889</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <f aca="false">IF(B3&gt;=C3,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="30" t="n">
+        <f aca="false">B3+(Engine!$B$5*(1+Inputs!$B$14)^INT((3-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((3-1)/12))</f>
+        <v>316841</v>
+      </c>
+      <c r="C4" s="30" t="n">
+        <f aca="false">C3+(Engine!$B$42*1.04^INT((3-1)/12))</f>
+        <v>2443469.27083333</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <f aca="false">IF(B4&gt;=C4,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="30" t="n">
+        <f aca="false">B4+(Engine!$B$5*(1+Inputs!$B$14)^INT((4-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((4-1)/12))</f>
+        <v>422454.666666667</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <f aca="false">C4+(Engine!$B$42*1.04^INT((4-1)/12))</f>
+        <v>2459642.02777778</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <f aca="false">IF(B5&gt;=C5,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="30" t="n">
+        <f aca="false">B5+(Engine!$B$5*(1+Inputs!$B$14)^INT((5-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((5-1)/12))</f>
+        <v>528068.333333333</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <f aca="false">C5+(Engine!$B$42*1.04^INT((5-1)/12))</f>
+        <v>2475814.78472222</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <f aca="false">IF(B6&gt;=C6,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="30" t="n">
+        <f aca="false">B6+(Engine!$B$5*(1+Inputs!$B$14)^INT((6-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((6-1)/12))</f>
+        <v>633682</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <f aca="false">C6+(Engine!$B$42*1.04^INT((6-1)/12))</f>
+        <v>2491987.54166667</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <f aca="false">IF(B7&gt;=C7,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="30" t="n">
+        <f aca="false">B7+(Engine!$B$5*(1+Inputs!$B$14)^INT((7-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((7-1)/12))</f>
+        <v>739295.666666667</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <f aca="false">C7+(Engine!$B$42*1.04^INT((7-1)/12))</f>
+        <v>2508160.29861111</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <f aca="false">IF(B8&gt;=C8,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="30" t="n">
+        <f aca="false">B8+(Engine!$B$5*(1+Inputs!$B$14)^INT((8-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((8-1)/12))</f>
+        <v>844909.333333333</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <f aca="false">C8+(Engine!$B$42*1.04^INT((8-1)/12))</f>
+        <v>2524333.05555556</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <f aca="false">IF(B9&gt;=C9,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="30" t="n">
+        <f aca="false">B9+(Engine!$B$5*(1+Inputs!$B$14)^INT((9-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((9-1)/12))</f>
+        <v>950523</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <f aca="false">C9+(Engine!$B$42*1.04^INT((9-1)/12))</f>
+        <v>2540505.8125</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <f aca="false">IF(B10&gt;=C10,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="30" t="n">
+        <f aca="false">B10+(Engine!$B$5*(1+Inputs!$B$14)^INT((10-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((10-1)/12))</f>
+        <v>1056136.66666667</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <f aca="false">C10+(Engine!$B$42*1.04^INT((10-1)/12))</f>
+        <v>2556678.56944445</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <f aca="false">IF(B11&gt;=C11,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="30" t="n">
+        <f aca="false">B11+(Engine!$B$5*(1+Inputs!$B$14)^INT((11-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((11-1)/12))</f>
+        <v>1161750.33333333</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <f aca="false">C11+(Engine!$B$42*1.04^INT((11-1)/12))</f>
+        <v>2572851.32638889</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <f aca="false">IF(B12&gt;=C12,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="30" t="n">
+        <f aca="false">B12+(Engine!$B$5*(1+Inputs!$B$14)^INT((12-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((12-1)/12))</f>
+        <v>1267364</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <f aca="false">C12+(Engine!$B$42*1.04^INT((12-1)/12))</f>
+        <v>2589024.08333333</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <f aca="false">IF(B13&gt;=C13,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="30" t="n">
+        <f aca="false">B13+(Engine!$B$5*(1+Inputs!$B$14)^INT((13-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((13-1)/12))</f>
+        <v>1388235.50833333</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <f aca="false">C13+(Engine!$B$42*1.04^INT((13-1)/12))</f>
+        <v>2605843.75055556</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <f aca="false">IF(B14&gt;=C14,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="30" t="n">
+        <f aca="false">B14+(Engine!$B$5*(1+Inputs!$B$14)^INT((14-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((14-1)/12))</f>
+        <v>1509107.01666667</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <f aca="false">C14+(Engine!$B$42*1.04^INT((14-1)/12))</f>
+        <v>2622663.41777778</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <f aca="false">IF(B15&gt;=C15,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="30" t="n">
+        <f aca="false">B15+(Engine!$B$5*(1+Inputs!$B$14)^INT((15-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((15-1)/12))</f>
+        <v>1629978.525</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <f aca="false">C15+(Engine!$B$42*1.04^INT((15-1)/12))</f>
+        <v>2639483.085</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <f aca="false">IF(B16&gt;=C16,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="30" t="n">
+        <f aca="false">B16+(Engine!$B$5*(1+Inputs!$B$14)^INT((16-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((16-1)/12))</f>
+        <v>1750850.03333333</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <f aca="false">C16+(Engine!$B$42*1.04^INT((16-1)/12))</f>
+        <v>2656302.75222222</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <f aca="false">IF(B17&gt;=C17,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="30" t="n">
+        <f aca="false">B17+(Engine!$B$5*(1+Inputs!$B$14)^INT((17-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((17-1)/12))</f>
+        <v>1871721.54166667</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <f aca="false">C17+(Engine!$B$42*1.04^INT((17-1)/12))</f>
+        <v>2673122.41944445</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <f aca="false">IF(B18&gt;=C18,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="30" t="n">
+        <f aca="false">B18+(Engine!$B$5*(1+Inputs!$B$14)^INT((18-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((18-1)/12))</f>
+        <v>1992593.05</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <f aca="false">C18+(Engine!$B$42*1.04^INT((18-1)/12))</f>
+        <v>2689942.08666667</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <f aca="false">IF(B19&gt;=C19,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="30" t="n">
+        <f aca="false">B19+(Engine!$B$5*(1+Inputs!$B$14)^INT((19-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((19-1)/12))</f>
+        <v>2113464.55833333</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <f aca="false">C19+(Engine!$B$42*1.04^INT((19-1)/12))</f>
+        <v>2706761.75388889</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <f aca="false">IF(B20&gt;=C20,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="30" t="n">
+        <f aca="false">B20+(Engine!$B$5*(1+Inputs!$B$14)^INT((20-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((20-1)/12))</f>
+        <v>2234336.06666667</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <f aca="false">C20+(Engine!$B$42*1.04^INT((20-1)/12))</f>
+        <v>2723581.42111111</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <f aca="false">IF(B21&gt;=C21,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="30" t="n">
+        <f aca="false">B21+(Engine!$B$5*(1+Inputs!$B$14)^INT((21-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((21-1)/12))</f>
+        <v>2355207.575</v>
+      </c>
+      <c r="C22" s="30" t="n">
+        <f aca="false">C21+(Engine!$B$42*1.04^INT((21-1)/12))</f>
+        <v>2740401.08833334</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <f aca="false">IF(B22&gt;=C22,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="30" t="n">
+        <f aca="false">B22+(Engine!$B$5*(1+Inputs!$B$14)^INT((22-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((22-1)/12))</f>
+        <v>2476079.08333333</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <f aca="false">C22+(Engine!$B$42*1.04^INT((22-1)/12))</f>
+        <v>2757220.75555556</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <f aca="false">IF(B23&gt;=C23,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="30" t="n">
+        <f aca="false">B23+(Engine!$B$5*(1+Inputs!$B$14)^INT((23-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((23-1)/12))</f>
+        <v>2596950.59166667</v>
+      </c>
+      <c r="C24" s="30" t="n">
+        <f aca="false">C23+(Engine!$B$42*1.04^INT((23-1)/12))</f>
+        <v>2774040.42277778</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <f aca="false">IF(B24&gt;=C24,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="30" t="n">
+        <f aca="false">B24+(Engine!$B$5*(1+Inputs!$B$14)^INT((24-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((24-1)/12))</f>
+        <v>2717822.1</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <f aca="false">C24+(Engine!$B$42*1.04^INT((24-1)/12))</f>
+        <v>2790860.09</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <f aca="false">IF(B25&gt;=C25,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="30" t="n">
+        <f aca="false">B25+(Engine!$B$5*(1+Inputs!$B$14)^INT((25-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((25-1)/12))</f>
+        <v>2857320.08741667</v>
+      </c>
+      <c r="C26" s="30" t="n">
+        <f aca="false">C25+(Engine!$B$42*1.04^INT((25-1)/12))</f>
+        <v>2808352.54391111</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <f aca="false">IF(B26&gt;=C26,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="30" t="n">
+        <f aca="false">B26+(Engine!$B$5*(1+Inputs!$B$14)^INT((26-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((26-1)/12))</f>
+        <v>2996818.07483333</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <f aca="false">C26+(Engine!$B$42*1.04^INT((26-1)/12))</f>
+        <v>2825844.99782222</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <f aca="false">IF(B27&gt;=C27,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="30" t="n">
+        <f aca="false">B27+(Engine!$B$5*(1+Inputs!$B$14)^INT((27-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((27-1)/12))</f>
+        <v>3136316.06225</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <f aca="false">C27+(Engine!$B$42*1.04^INT((27-1)/12))</f>
+        <v>2843337.45173334</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <f aca="false">IF(B28&gt;=C28,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="30" t="n">
+        <f aca="false">B28+(Engine!$B$5*(1+Inputs!$B$14)^INT((28-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((28-1)/12))</f>
+        <v>3275814.04966667</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <f aca="false">C28+(Engine!$B$42*1.04^INT((28-1)/12))</f>
+        <v>2860829.90564445</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <f aca="false">IF(B29&gt;=C29,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="30" t="n">
+        <f aca="false">B29+(Engine!$B$5*(1+Inputs!$B$14)^INT((29-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((29-1)/12))</f>
+        <v>3415312.03708333</v>
+      </c>
+      <c r="C30" s="30" t="n">
+        <f aca="false">C29+(Engine!$B$42*1.04^INT((29-1)/12))</f>
+        <v>2878322.35955556</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <f aca="false">IF(B30&gt;=C30,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="30" t="n">
+        <f aca="false">B30+(Engine!$B$5*(1+Inputs!$B$14)^INT((30-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((30-1)/12))</f>
+        <v>3554810.0245</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <f aca="false">C30+(Engine!$B$42*1.04^INT((30-1)/12))</f>
+        <v>2895814.81346667</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <f aca="false">IF(B31&gt;=C31,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="30" t="n">
+        <f aca="false">B31+(Engine!$B$5*(1+Inputs!$B$14)^INT((31-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((31-1)/12))</f>
+        <v>3694308.01191667</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <f aca="false">C31+(Engine!$B$42*1.04^INT((31-1)/12))</f>
+        <v>2913307.26737778</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <f aca="false">IF(B32&gt;=C32,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="30" t="n">
+        <f aca="false">B32+(Engine!$B$5*(1+Inputs!$B$14)^INT((32-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((32-1)/12))</f>
+        <v>3833805.99933333</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <f aca="false">C32+(Engine!$B$42*1.04^INT((32-1)/12))</f>
+        <v>2930799.72128889</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <f aca="false">IF(B33&gt;=C33,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="30" t="n">
+        <f aca="false">B33+(Engine!$B$5*(1+Inputs!$B$14)^INT((33-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((33-1)/12))</f>
+        <v>3973303.98675</v>
+      </c>
+      <c r="C34" s="30" t="n">
+        <f aca="false">C33+(Engine!$B$42*1.04^INT((33-1)/12))</f>
+        <v>2948292.1752</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <f aca="false">IF(B34&gt;=C34,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="30" t="n">
+        <f aca="false">B34+(Engine!$B$5*(1+Inputs!$B$14)^INT((34-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((34-1)/12))</f>
+        <v>4112801.97416666</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <f aca="false">C34+(Engine!$B$42*1.04^INT((34-1)/12))</f>
+        <v>2965784.62911111</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <f aca="false">IF(B35&gt;=C35,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="30" t="n">
+        <f aca="false">B35+(Engine!$B$5*(1+Inputs!$B$14)^INT((35-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((35-1)/12))</f>
+        <v>4252299.96158333</v>
+      </c>
+      <c r="C36" s="30" t="n">
+        <f aca="false">C35+(Engine!$B$42*1.04^INT((35-1)/12))</f>
+        <v>2983277.08302223</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <f aca="false">IF(B36&gt;=C36,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36+(Engine!$B$5*(1+Inputs!$B$14)^INT((36-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((36-1)/12))</f>
+        <v>4391797.949</v>
+      </c>
+      <c r="C37" s="30" t="n">
+        <f aca="false">C36+(Engine!$B$42*1.04^INT((36-1)/12))</f>
+        <v>3000769.53693334</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <f aca="false">IF(B37&gt;=C37,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="30" t="n">
+        <f aca="false">B37+(Engine!$B$5*(1+Inputs!$B$14)^INT((37-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((37-1)/12))</f>
+        <v>4554115.37935083</v>
+      </c>
+      <c r="C38" s="30" t="n">
+        <f aca="false">C37+(Engine!$B$42*1.04^INT((37-1)/12))</f>
+        <v>3018961.68900089</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <f aca="false">IF(B38&gt;=C38,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="30" t="n">
+        <f aca="false">B38+(Engine!$B$5*(1+Inputs!$B$14)^INT((38-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((38-1)/12))</f>
+        <v>4716432.80970167</v>
+      </c>
+      <c r="C39" s="30" t="n">
+        <f aca="false">C38+(Engine!$B$42*1.04^INT((38-1)/12))</f>
+        <v>3037153.84106845</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <f aca="false">IF(B39&gt;=C39,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">B39+(Engine!$B$5*(1+Inputs!$B$14)^INT((39-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((39-1)/12))</f>
+        <v>4878750.2400525</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">C39+(Engine!$B$42*1.04^INT((39-1)/12))</f>
+        <v>3055345.993136</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <f aca="false">IF(B40&gt;=C40,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B40+(Engine!$B$5*(1+Inputs!$B$14)^INT((40-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((40-1)/12))</f>
+        <v>5041067.67040333</v>
+      </c>
+      <c r="C41" s="30" t="n">
+        <f aca="false">C40+(Engine!$B$42*1.04^INT((40-1)/12))</f>
+        <v>3073538.14520356</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <f aca="false">IF(B41&gt;=C41,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="30" t="n">
+        <f aca="false">B41+(Engine!$B$5*(1+Inputs!$B$14)^INT((41-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((41-1)/12))</f>
+        <v>5203385.10075417</v>
+      </c>
+      <c r="C42" s="30" t="n">
+        <f aca="false">C41+(Engine!$B$42*1.04^INT((41-1)/12))</f>
+        <v>3091730.29727111</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <f aca="false">IF(B42&gt;=C42,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="30" t="n">
+        <f aca="false">B42+(Engine!$B$5*(1+Inputs!$B$14)^INT((42-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((42-1)/12))</f>
+        <v>5365702.531105</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <f aca="false">C42+(Engine!$B$42*1.04^INT((42-1)/12))</f>
+        <v>3109922.44933867</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <f aca="false">IF(B43&gt;=C43,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="30" t="n">
+        <f aca="false">B43+(Engine!$B$5*(1+Inputs!$B$14)^INT((43-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((43-1)/12))</f>
+        <v>5528019.96145583</v>
+      </c>
+      <c r="C44" s="30" t="n">
+        <f aca="false">C43+(Engine!$B$42*1.04^INT((43-1)/12))</f>
+        <v>3128114.60140623</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <f aca="false">IF(B44&gt;=C44,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="30" t="n">
+        <f aca="false">B44+(Engine!$B$5*(1+Inputs!$B$14)^INT((44-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((44-1)/12))</f>
+        <v>5690337.39180667</v>
+      </c>
+      <c r="C45" s="30" t="n">
+        <f aca="false">C44+(Engine!$B$42*1.04^INT((44-1)/12))</f>
+        <v>3146306.75347378</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <f aca="false">IF(B45&gt;=C45,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="30" t="n">
+        <f aca="false">B45+(Engine!$B$5*(1+Inputs!$B$14)^INT((45-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((45-1)/12))</f>
+        <v>5852654.8221575</v>
+      </c>
+      <c r="C46" s="30" t="n">
+        <f aca="false">C45+(Engine!$B$42*1.04^INT((45-1)/12))</f>
+        <v>3164498.90554134</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <f aca="false">IF(B46&gt;=C46,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="30" t="n">
+        <f aca="false">B46+(Engine!$B$5*(1+Inputs!$B$14)^INT((46-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((46-1)/12))</f>
+        <v>6014972.25250833</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <f aca="false">C46+(Engine!$B$42*1.04^INT((46-1)/12))</f>
+        <v>3182691.05760889</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <f aca="false">IF(B47&gt;=C47,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="30" t="n">
+        <f aca="false">B47+(Engine!$B$5*(1+Inputs!$B$14)^INT((47-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((47-1)/12))</f>
+        <v>6177289.68285917</v>
+      </c>
+      <c r="C48" s="30" t="n">
+        <f aca="false">C47+(Engine!$B$42*1.04^INT((47-1)/12))</f>
+        <v>3200883.20967645</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <f aca="false">IF(B48&gt;=C48,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="30" t="n">
+        <f aca="false">B48+(Engine!$B$5*(1+Inputs!$B$14)^INT((48-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((48-1)/12))</f>
+        <v>6339607.11321</v>
+      </c>
+      <c r="C49" s="30" t="n">
+        <f aca="false">C48+(Engine!$B$42*1.04^INT((48-1)/12))</f>
+        <v>3219075.361744</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <f aca="false">IF(B49&gt;=C49,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="30" t="n">
+        <f aca="false">B49+(Engine!$B$5*(1+Inputs!$B$14)^INT((49-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((49-1)/12))</f>
+        <v>6529966.64507174</v>
+      </c>
+      <c r="C50" s="30" t="n">
+        <f aca="false">C49+(Engine!$B$42*1.04^INT((49-1)/12))</f>
+        <v>3237995.19989426</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <f aca="false">IF(B50&gt;=C50,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="30" t="n">
+        <f aca="false">B50+(Engine!$B$5*(1+Inputs!$B$14)^INT((50-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((50-1)/12))</f>
+        <v>6720326.17693349</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <f aca="false">C50+(Engine!$B$42*1.04^INT((50-1)/12))</f>
+        <v>3256915.03804452</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <f aca="false">IF(B51&gt;=C51,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="30" t="n">
+        <f aca="false">B51+(Engine!$B$5*(1+Inputs!$B$14)^INT((51-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((51-1)/12))</f>
+        <v>6910685.70879523</v>
+      </c>
+      <c r="C52" s="30" t="n">
+        <f aca="false">C51+(Engine!$B$42*1.04^INT((51-1)/12))</f>
+        <v>3275834.87619478</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <f aca="false">IF(B52&gt;=C52,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="30" t="n">
+        <f aca="false">B52+(Engine!$B$5*(1+Inputs!$B$14)^INT((52-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((52-1)/12))</f>
+        <v>7101045.24065697</v>
+      </c>
+      <c r="C53" s="30" t="n">
+        <f aca="false">C52+(Engine!$B$42*1.04^INT((52-1)/12))</f>
+        <v>3294754.71434503</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <f aca="false">IF(B53&gt;=C53,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="30" t="n">
+        <f aca="false">B53+(Engine!$B$5*(1+Inputs!$B$14)^INT((53-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((53-1)/12))</f>
+        <v>7291404.77251871</v>
+      </c>
+      <c r="C54" s="30" t="n">
+        <f aca="false">C53+(Engine!$B$42*1.04^INT((53-1)/12))</f>
+        <v>3313674.55249529</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <f aca="false">IF(B54&gt;=C54,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="30" t="n">
+        <f aca="false">B54+(Engine!$B$5*(1+Inputs!$B$14)^INT((54-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((54-1)/12))</f>
+        <v>7481764.30438045</v>
+      </c>
+      <c r="C55" s="30" t="n">
+        <f aca="false">C54+(Engine!$B$42*1.04^INT((54-1)/12))</f>
+        <v>3332594.39064555</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <f aca="false">IF(B55&gt;=C55,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="30" t="n">
+        <f aca="false">B55+(Engine!$B$5*(1+Inputs!$B$14)^INT((55-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((55-1)/12))</f>
+        <v>7672123.8362422</v>
+      </c>
+      <c r="C56" s="30" t="n">
+        <f aca="false">C55+(Engine!$B$42*1.04^INT((55-1)/12))</f>
+        <v>3351514.22879581</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <f aca="false">IF(B56&gt;=C56,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="30" t="n">
+        <f aca="false">B56+(Engine!$B$5*(1+Inputs!$B$14)^INT((56-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((56-1)/12))</f>
+        <v>7862483.36810394</v>
+      </c>
+      <c r="C57" s="30" t="n">
+        <f aca="false">C56+(Engine!$B$42*1.04^INT((56-1)/12))</f>
+        <v>3370434.06694607</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <f aca="false">IF(B57&gt;=C57,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="30" t="n">
+        <f aca="false">B57+(Engine!$B$5*(1+Inputs!$B$14)^INT((57-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((57-1)/12))</f>
+        <v>8052842.89996568</v>
+      </c>
+      <c r="C58" s="30" t="n">
+        <f aca="false">C57+(Engine!$B$42*1.04^INT((57-1)/12))</f>
+        <v>3389353.90509632</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <f aca="false">IF(B58&gt;=C58,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="30" t="n">
+        <f aca="false">B58+(Engine!$B$5*(1+Inputs!$B$14)^INT((58-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((58-1)/12))</f>
+        <v>8243202.43182742</v>
+      </c>
+      <c r="C59" s="30" t="n">
+        <f aca="false">C58+(Engine!$B$42*1.04^INT((58-1)/12))</f>
+        <v>3408273.74324658</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <f aca="false">IF(B59&gt;=C59,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="30" t="n">
+        <f aca="false">B59+(Engine!$B$5*(1+Inputs!$B$14)^INT((59-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((59-1)/12))</f>
+        <v>8433561.96368916</v>
+      </c>
+      <c r="C60" s="30" t="n">
+        <f aca="false">C59+(Engine!$B$42*1.04^INT((59-1)/12))</f>
+        <v>3427193.58139684</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <f aca="false">IF(B60&gt;=C60,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="30" t="n">
+        <f aca="false">B60+(Engine!$B$5*(1+Inputs!$B$14)^INT((60-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((60-1)/12))</f>
+        <v>8623921.4955509</v>
+      </c>
+      <c r="C61" s="30" t="n">
+        <f aca="false">C60+(Engine!$B$42*1.04^INT((60-1)/12))</f>
+        <v>3446113.4195471</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <f aca="false">IF(B61&gt;=C61,1,0)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1717,89 +2820,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>113.93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>68.36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>2.88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.05</v>
@@ -1808,18 +2911,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>189000</v>
@@ -1828,7 +2931,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>5000</v>
@@ -1837,29 +2940,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>8</v>
@@ -1868,23 +2971,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>25000</v>
@@ -1893,29 +2996,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>1200000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>100000</v>
@@ -1924,18 +3027,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>500000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>33333</v>
@@ -1944,7 +3047,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
@@ -1953,29 +3056,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>3000</v>
@@ -1984,7 +3087,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>2000</v>
@@ -1993,7 +3096,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
@@ -2002,7 +3105,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>189000</v>
@@ -2011,40 +3114,40 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>11387</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>730</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>0.04</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2076,47 +3179,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>85</v>
+      <c r="A3" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>8</v>
@@ -2139,19 +3242,19 @@
       <c r="H3" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="I3" s="13" t="n">
+      <c r="I3" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>87</v>
+      <c r="J3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>88</v>
+      <c r="A4" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>8</v>
@@ -2172,21 +3275,21 @@
         <v>0</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I4" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>90</v>
+      <c r="J4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>91</v>
+      <c r="A5" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>8</v>
@@ -2207,21 +3310,21 @@
         <v>0</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>90</v>
+      <c r="J5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>92</v>
+      <c r="A6" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>72</v>
@@ -2242,41 +3345,41 @@
         <v>0</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="I6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>90</v>
+      <c r="J6" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>94</v>
+      <c r="A9" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>95</v>
+      <c r="A10" s="14" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>96</v>
+      <c r="A11" s="14" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>97</v>
+      <c r="A12" s="14" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2305,117 +3408,117 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C3" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2444,308 +3547,326 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="B4" s="16" t="n">
         <v>105079</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>118</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>95</v>
+        <v>121</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="B10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="18" t="n">
+        <v>127</v>
+      </c>
+      <c r="B11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="B12" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="B13" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="B14" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>136</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="15" t="n">
+        <v>138</v>
+      </c>
+      <c r="B16" s="16" t="n">
         <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="B17" s="18" t="n">
         <v>0.85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>85</v>
+        <v>142</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B21" s="19" t="n">
+        <v>145</v>
+      </c>
+      <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B24" s="20" t="n">
+        <v>148</v>
+      </c>
+      <c r="B24" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="B25" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B26" s="20" t="n">
+        <v>152</v>
+      </c>
+      <c r="B26" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B29" s="21"/>
+        <v>155</v>
+      </c>
+      <c r="B29" s="22"/>
       <c r="C29" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B30" s="19" t="n">
+        <v>157</v>
+      </c>
+      <c r="B30" s="20" t="n">
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B33" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="B33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B34" s="15" t="n">
+        <v>162</v>
+      </c>
+      <c r="B34" s="16" t="n">
         <v>100000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="19" t="n">
+        <v>164</v>
+      </c>
+      <c r="B35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" s="19" t="n">
+        <v>166</v>
+      </c>
+      <c r="B36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B37" s="17" t="n">
+        <v>168</v>
+      </c>
+      <c r="B37" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation allowBlank="true" error="Must be zero or positive" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4 B11 B16 B21 B33:B35" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Enter a fraction between 0 and 1" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B9:B10 B12:B14 B37" type="decimal">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Utilization must be between 0.05 and 1.0" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B17" type="decimal">
+      <formula1>0.05</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="0 = off, 1 = N+1" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B36" type="whole">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2771,49 +3892,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="22" t="n">
+        <v>173</v>
+      </c>
+      <c r="B4" s="23" t="n">
         <f aca="false">(Inputs!$B$10*(RateCard!$B$4+RateCard!$B$6)+(1-Inputs!$B$10)*(RateCard!$B$5+RateCard!$B$7))*(1+RateCard!$B$15)</f>
         <v>71.24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="23" t="n">
+        <v>175</v>
+      </c>
+      <c r="B5" s="24" t="n">
         <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
         <v>52539.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="24" t="n">
+        <v>177</v>
+      </c>
+      <c r="B6" s="25" t="n">
         <f aca="false">B5/B4</f>
         <v>737.5</v>
       </c>
@@ -2821,50 +3942,50 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="24" t="n">
+        <v>178</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*RateCard!$B$16)</f>
         <v>5900</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="25" t="n">
+        <v>181</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
         <v>2.83870967741935</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="25" t="n">
+        <v>183</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
         <v>4.79741935483871</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="24" t="n">
+        <v>185</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <f aca="false">B7/B11</f>
         <v>1229.82786444325</v>
       </c>
@@ -2872,26 +3993,26 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="24" t="n">
+        <v>186</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <f aca="false">B7</f>
         <v>5900</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" s="24" t="n">
+        <v>189</v>
+      </c>
+      <c r="B16" s="25" t="n">
         <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
         <v>8</v>
       </c>
@@ -2899,21 +4020,21 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B17" s="24" t="n">
+        <v>190</v>
+      </c>
+      <c r="B17" s="25" t="n">
         <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
         <v>4964</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="24" t="n">
+        <v>192</v>
+      </c>
+      <c r="B18" s="25" t="n">
         <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
         <v>1</v>
       </c>
@@ -2921,9 +4042,9 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="24" t="n">
+        <v>193</v>
+      </c>
+      <c r="B19" s="25" t="n">
         <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
         <v>2</v>
       </c>
@@ -2931,26 +4052,26 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B20" s="26" t="n">
-        <f aca="false">1-B12/(B18*B17)</f>
+        <v>194</v>
+      </c>
+      <c r="B20" s="27" t="n">
+        <f aca="false">1-B12/((B18-Inputs!$B$36)*B17)</f>
         <v>0.752250631659297</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B23" s="27" t="n">
+        <v>197</v>
+      </c>
+      <c r="B23" s="28" t="n">
         <f aca="false">Inputs!$B$11*Inputs!$B$12</f>
         <v>0.25</v>
       </c>
@@ -2958,9 +4079,9 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B24" s="27" t="n">
+        <v>198</v>
+      </c>
+      <c r="B24" s="28" t="n">
         <f aca="false">Inputs!$B$11*(1-Inputs!$B$12)</f>
         <v>0.75</v>
       </c>
@@ -2968,21 +4089,21 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" s="23" t="n">
+        <v>199</v>
+      </c>
+      <c r="B25" s="24" t="n">
         <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+Inputs!$B$11*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>52500</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B26" s="23" t="n">
+        <v>201</v>
+      </c>
+      <c r="B26" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
         <v>574.166666666667</v>
       </c>
@@ -2990,26 +4111,26 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B29" s="23" t="n">
-        <f aca="false">IF(INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;100000,NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
+        <v>203</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <f aca="false">IF(OR(INDEX(Hardware!$J$3:$J$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;&gt;"YES",INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))=0),NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
         <v>744793</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B30" s="24" t="n">
+        <v>205</v>
+      </c>
+      <c r="B30" s="25" t="n">
         <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
         <v>1</v>
       </c>
@@ -3017,21 +4138,21 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B31" s="23" t="n">
+        <v>206</v>
+      </c>
+      <c r="B31" s="24" t="n">
         <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B32" s="23" t="n">
+        <v>208</v>
+      </c>
+      <c r="B32" s="24" t="n">
         <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
         <v>675000</v>
       </c>
@@ -3039,9 +4160,9 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B33" s="23" t="n">
+        <v>209</v>
+      </c>
+      <c r="B33" s="24" t="n">
         <f aca="false">B31+B32</f>
         <v>2034793</v>
       </c>
@@ -3049,9 +4170,9 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B34" s="27" t="n">
+        <v>210</v>
+      </c>
+      <c r="B34" s="28" t="n">
         <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
         <v>14.4</v>
       </c>
@@ -3059,21 +4180,21 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B35" s="23" t="n">
+        <v>211</v>
+      </c>
+      <c r="B35" s="24" t="n">
         <f aca="false">(B18*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16</f>
         <v>7320</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B36" s="27" t="n">
+        <v>213</v>
+      </c>
+      <c r="B36" s="28" t="n">
         <f aca="false">B30+Inputs!$B$11*RateCard!$B$27</f>
         <v>2</v>
       </c>
@@ -3081,45 +4202,45 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B37" s="23" t="n">
+        <v>214</v>
+      </c>
+      <c r="B37" s="24" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/36</f>
         <v>3111.11111111111</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B38" s="23" t="n">
+        <v>216</v>
+      </c>
+      <c r="B38" s="24" t="n">
         <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B39" s="23" t="n">
+        <v>217</v>
+      </c>
+      <c r="B39" s="24" t="n">
         <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
         <v>4166.64583333333</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B40" s="23" t="n">
+        <v>219</v>
+      </c>
+      <c r="B40" s="24" t="n">
         <f aca="false">B35+B37+B38+B39</f>
         <v>16172.7569444444</v>
       </c>
@@ -3127,21 +4248,21 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B41" s="23" t="n">
+        <v>220</v>
+      </c>
+      <c r="B41" s="24" t="n">
         <f aca="false">B18*RateCard!$B$33+B39</f>
         <v>15553.6458333333</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B42" s="23" t="n">
+        <v>222</v>
+      </c>
+      <c r="B42" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
         <v>16172.7569444444</v>
       </c>
@@ -3149,14 +4270,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B45" s="23" t="n">
+        <v>224</v>
+      </c>
+      <c r="B45" s="24" t="n">
         <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
         <v>2779586</v>
       </c>
@@ -3164,9 +4285,9 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B46" s="23" t="n">
+        <v>225</v>
+      </c>
+      <c r="B46" s="24" t="n">
         <f aca="false">(B19*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+Inputs!$B$11*RateCard!$B$27)/36+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
         <v>22067.7569444444</v>
       </c>
@@ -3174,9 +4295,9 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B47" s="23" t="n">
+        <v>226</v>
+      </c>
+      <c r="B47" s="24" t="n">
         <f aca="false">B19*RateCard!$B$33+B39</f>
         <v>26940.6458333333</v>
       </c>
@@ -3184,9 +4305,9 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B48" s="23" t="n">
+        <v>227</v>
+      </c>
+      <c r="B48" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
         <v>22067.7569444444</v>
       </c>
@@ -3194,26 +4315,26 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B51" s="23" t="str">
+        <v>229</v>
+      </c>
+      <c r="B51" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
         <v>not entered</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B52" s="23" t="str">
+        <v>231</v>
+      </c>
+      <c r="B52" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
         <v>not entered</v>
       </c>
@@ -3221,38 +4342,38 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B54" s="23" t="n">
+        <v>233</v>
+      </c>
+      <c r="B54" s="24" t="n">
         <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+Inputs!$B$11*1000000*RateCard!$B$10</f>
         <v>360158</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B55" s="23" t="n">
+        <v>235</v>
+      </c>
+      <c r="B55" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
         <v>187798.95</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B56" s="23" t="n">
+        <v>237</v>
+      </c>
+      <c r="B56" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
         <v>274347.9</v>
       </c>
@@ -3260,34 +4381,34 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B58" s="23" t="n">
-        <f aca="false">Engine!$B$25</f>
-        <v>52500</v>
+        <v>239</v>
+      </c>
+      <c r="B58" s="24" t="n">
+        <f aca="false">Engine!$B$25+Engine!$B$26</f>
+        <v>53074.1666666667</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B59" s="23" t="n">
+        <v>240</v>
+      </c>
+      <c r="B59" s="24" t="n">
         <f aca="false">Inputs!$B$4*(1-Inputs!$B$13)</f>
         <v>52539.5</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B60" s="4" t="str">
-        <f aca="false">IF(B58&gt;B59*1.02,"⚠ MISMATCH: entered storage implies $"&amp;TEXT(B58,"#,##0")&amp;"/mo but only $"&amp;TEXT(B59,"#,##0")&amp;"/mo of the stated bill is non-compute — reduce storage PB or raise the bill","OK — storage consistent with stated bill")</f>
-        <v>OK — storage consistent with stated bill</v>
+        <f aca="false">IF(B58&gt;B59*1.02,"⚠ OVERALLOCATED: reconstructed storage+egress+admin exceed the stated non-compute budget by $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo — reduce storage PB or raise the bill",IF(B58&lt;B59*0.98,"ℹ UNALLOCATED: $"&amp;TEXT(B59-B58,"#,##0")&amp;"/mo of the stated bill is not explained by entered components (PaaS, other services?)","OK — within 2% tolerance (difference $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo)"))</f>
+        <v>OK — within 2% tolerance (difference $535/mo)</v>
       </c>
     </row>
   </sheetData>
@@ -3306,7 +4427,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -3315,355 +4436,364 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
         <v>1260948</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^1+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^1)</f>
         <v>1443785.46</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="24" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^2+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^2)</f>
         <v>1667036.3034</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="24" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^3+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^3)</f>
         <v>1940592.036786</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="24" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^4+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^4)</f>
         <v>2276808.56981994</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B7" s="23" t="n">
+        <v>251</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
         <v>194073.083333333</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="24" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^1</f>
         <v>201836.006666667</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^2</f>
         <v>209909.446933333</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="24" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^3</f>
         <v>218305.824810667</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^4</f>
         <v>227038.057803093</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>252</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
         <v>264813.083333333</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^1</f>
         <v>275405.606666667</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="24" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^2</f>
         <v>286421.830933333</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^3</f>
         <v>297878.704170667</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="24" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^4</f>
         <v>309793.852337493</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B12" s="23" t="n">
+        <v>257</v>
+      </c>
+      <c r="B12" s="24" t="n">
         <f aca="false">SUM($B$6:B6)</f>
         <v>1260948</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="24" t="n">
         <f aca="false">SUM($B$6:D6)</f>
         <v>4371769.7634</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="24" t="n">
         <f aca="false">SUM($B$6:F6)</f>
         <v>8589170.37000594</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B13" s="23" t="n">
+        <v>258</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)</f>
         <v>2401225.13333333</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7)</f>
         <v>2812970.58693333</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7)</f>
         <v>3258314.46954709</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="23" t="n">
+        <v>259</v>
+      </c>
+      <c r="B14" s="24" t="n">
         <f aca="false">B12-B13</f>
         <v>-1140277.13333333</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <f aca="false">C12-C13</f>
         <v>1558799.17646667</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <f aca="false">D12-D13</f>
         <v>5330855.90045885</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B15" s="26" t="n">
+        <v>260</v>
+      </c>
+      <c r="B15" s="27" t="n">
         <f aca="false">B14/B12</f>
         <v>-0.904301472648621</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <f aca="false">C14/C12</f>
         <v>0.356560217218384</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="27" t="n">
         <f aca="false">D14/D12</f>
         <v>0.620648522594757</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B16" s="23" t="n">
+        <v>261</v>
+      </c>
+      <c r="B16" s="24" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)</f>
         <v>3130209.18333333</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8)</f>
         <v>3692036.62093333</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8)</f>
         <v>4299709.17744149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B17" s="23" t="n">
+        <v>262</v>
+      </c>
+      <c r="B17" s="24" t="n">
         <f aca="false">B12-B16</f>
         <v>-1869261.18333333</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="24" t="n">
         <f aca="false">C12-C16</f>
         <v>679733.142466666</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="24" t="n">
         <f aca="false">D12-D16</f>
         <v>4289461.19256445</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B18" s="26" t="n">
+        <v>263</v>
+      </c>
+      <c r="B18" s="27" t="n">
         <f aca="false">B17/B12</f>
         <v>-1.48242527315427</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <f aca="false">C17/C12</f>
         <v>0.155482374245168</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="27" t="n">
         <f aca="false">D17/D12</f>
         <v>0.499403435696605</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B21" s="28" t="str">
+        <v>265</v>
+      </c>
+      <c r="B21" s="29" t="str">
         <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
         <v>1 / 2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B22" s="23" t="n">
+        <v>266</v>
+      </c>
+      <c r="B22" s="24" t="n">
         <f aca="false">Engine!$B$33</f>
         <v>2034793</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B23" s="26" t="str">
-        <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/(Engine!$B$19*Engine!$B$17),"0.0%")</f>
+        <v>267</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17),"0.0%")</f>
         <v>75.2% / 40.6%</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/(Engine!$B$19*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
+        <v>268</v>
+      </c>
+      <c r="B24" s="28" t="str">
+        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
         <v>6.3 / 2.3</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B25" s="23" t="n">
+        <v>269</v>
+      </c>
+      <c r="B25" s="24" t="n">
         <f aca="false">Engine!$B$25</f>
         <v>52500</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B26" s="27" t="n">
-        <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"no crossover at current spend and assumptions",IF((Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42)&gt;60,"no crossover within modeled horizon (&gt;60 mo)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42)))</f>
-        <v>26.9379395382105</v>
+        <v>270</v>
+      </c>
+      <c r="B26" s="28" t="str">
+        <f aca="false">IFERROR("Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),"no crossover within 60 months under the modeled trajectory")</f>
+        <v>Month 25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B27" s="23" t="str">
+        <v>271</v>
+      </c>
+      <c r="B27" s="24" t="str">
         <f aca="false">Engine!$B$51</f>
         <v>not entered</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B28" s="23" t="n">
+        <v>233</v>
+      </c>
+      <c r="B28" s="24" t="n">
         <f aca="false">Engine!$B$54</f>
         <v>360158</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B29" s="23" t="n">
+        <v>235</v>
+      </c>
+      <c r="B29" s="24" t="n">
         <f aca="false">Engine!$B$55</f>
         <v>187798.95</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B30" s="27" t="n">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/(Engine!$B$19*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
+        <v>272</v>
+      </c>
+      <c r="B30" s="28" t="n">
+        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
         <v>2.3321610412924</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B32" s="1" t="str">
         <f aca="false">Engine!$B$60</f>
-        <v>OK — storage consistent with stated bill</v>
+        <v>OK — within 2% tolerance (difference $535/mo)</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B33" s="28" t="n">
+        <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"n/a (opex exceeds bill)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42))</f>
+        <v>26.9379395382105</v>
       </c>
     </row>
   </sheetData>
@@ -3691,33 +4821,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B5" s="24" t="n">
+        <v>282</v>
+      </c>
+      <c r="B5" s="25" t="n">
         <f aca="false">8*RateCard!$B$36</f>
         <v>5840</v>
       </c>
@@ -3731,9 +4861,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="23" t="n">
+        <v>283</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
         <v>52005.2</v>
       </c>
@@ -3747,9 +4877,9 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B7" s="23" t="n">
+        <v>284</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>52500</v>
       </c>
@@ -3763,9 +4893,9 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>285</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
         <v>574.166666666667</v>
       </c>
@@ -3779,9 +4909,9 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="23" t="n">
+        <v>286</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <f aca="false">B6+B7+B8</f>
         <v>105079.366666667</v>
       </c>
@@ -3795,9 +4925,9 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B10" s="23" t="n">
+        <v>287</v>
+      </c>
+      <c r="B10" s="24" t="n">
         <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
@@ -3811,9 +4941,9 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B11" s="23" t="n">
+        <v>288</v>
+      </c>
+      <c r="B11" s="24" t="n">
         <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
         <v>675000</v>
       </c>
@@ -3827,9 +4957,9 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B12" s="23" t="n">
+        <v>289</v>
+      </c>
+      <c r="B12" s="24" t="n">
         <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
         <v>4166.64583333333</v>
       </c>
@@ -3843,9 +4973,9 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B13" s="23" t="n">
+        <v>290</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
         <v>7320</v>
       </c>
@@ -3859,9 +4989,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B14" s="23" t="n">
+        <v>291</v>
+      </c>
+      <c r="B14" s="24" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
         <v>3097.22222222222</v>
       </c>
@@ -3875,9 +5005,9 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B15" s="23" t="n">
+        <v>292</v>
+      </c>
+      <c r="B15" s="24" t="n">
         <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
@@ -3891,9 +5021,9 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B16" s="23" t="n">
+        <v>293</v>
+      </c>
+      <c r="B16" s="24" t="n">
         <f aca="false">B13+B14+B15</f>
         <v>11992.2222222222</v>
       </c>
@@ -3907,9 +5037,9 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B17" s="23" t="n">
+        <v>294</v>
+      </c>
+      <c r="B17" s="24" t="n">
         <f aca="false">1*RateCard!$B$33</f>
         <v>11387</v>
       </c>
@@ -3923,9 +5053,9 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B18" s="23" t="n">
+        <v>295</v>
+      </c>
+      <c r="B18" s="24" t="n">
         <f aca="false">B10*0.0281</f>
         <v>38210.1833</v>
       </c>
@@ -3939,9 +5069,9 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B19" s="23" t="n">
+        <v>296</v>
+      </c>
+      <c r="B19" s="24" t="n">
         <f aca="false">B11*0.0281+B12</f>
         <v>23134.1458333333</v>
       </c>
@@ -3955,9 +5085,9 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B20" s="23" t="n">
+        <v>297</v>
+      </c>
+      <c r="B20" s="24" t="n">
         <f aca="false">B18+B19+B16</f>
         <v>73336.5513555556</v>
       </c>
@@ -3971,7 +5101,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -3999,167 +5129,167 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B5" s="13" t="n">
+        <v>302</v>
+      </c>
+      <c r="B5" s="14" t="n">
         <v>105079</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B6" s="13" t="n">
+        <v>303</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>0.49491</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>97</v>
+        <v>304</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B8" s="13" t="n">
+        <v>305</v>
+      </c>
+      <c r="B8" s="14" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B9" s="13" t="n">
+        <v>306</v>
+      </c>
+      <c r="B9" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B10" s="13" t="n">
+        <v>307</v>
+      </c>
+      <c r="B10" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B11" s="13" t="n">
+        <v>308</v>
+      </c>
+      <c r="B11" s="14" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B12" s="13" t="n">
+        <v>309</v>
+      </c>
+      <c r="B12" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>134</v>
+        <v>310</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B14" s="13" t="n">
+        <v>311</v>
+      </c>
+      <c r="B14" s="14" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B15" s="13" t="n">
+        <v>312</v>
+      </c>
+      <c r="B15" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>85</v>
+        <v>313</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B17" s="13" t="n">
+        <v>314</v>
+      </c>
+      <c r="B17" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B21" s="28" t="str">
+        <v>319</v>
+      </c>
+      <c r="B21" s="29" t="str">
         <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200/B300-class",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS"),"YES","NO — set fixture first")</f>
         <v>NO — set fixture first</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B24" s="24" t="n">
+        <v>323</v>
+      </c>
+      <c r="B24" s="25" t="n">
         <f aca="false">Engine!$B$7</f>
         <v>5900</v>
       </c>
@@ -4173,9 +5303,9 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B25" s="22" t="n">
+        <v>324</v>
+      </c>
+      <c r="B25" s="23" t="n">
         <f aca="false">Engine!$B$4</f>
         <v>71.24</v>
       </c>
@@ -4189,13 +5319,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B26" s="25" t="n">
+        <v>325</v>
+      </c>
+      <c r="B26" s="26" t="n">
         <f aca="false">Engine!$B$11</f>
         <v>4.79741935483871</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="4" t="str">
@@ -4205,9 +5335,9 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B27" s="24" t="n">
+        <v>326</v>
+      </c>
+      <c r="B27" s="25" t="n">
         <f aca="false">Engine!$B$18</f>
         <v>1</v>
       </c>
@@ -4221,9 +5351,9 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B28" s="24" t="n">
+        <v>327</v>
+      </c>
+      <c r="B28" s="25" t="n">
         <f aca="false">Engine!$B$19</f>
         <v>2</v>
       </c>
@@ -4237,9 +5367,9 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B29" s="23" t="n">
+        <v>328</v>
+      </c>
+      <c r="B29" s="24" t="n">
         <f aca="false">Engine!$B$31</f>
         <v>1359793</v>
       </c>
@@ -4253,9 +5383,9 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B30" s="23" t="n">
+        <v>329</v>
+      </c>
+      <c r="B30" s="24" t="n">
         <f aca="false">Engine!$B$32</f>
         <v>675000</v>
       </c>
@@ -4269,9 +5399,9 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B31" s="23" t="n">
+        <v>330</v>
+      </c>
+      <c r="B31" s="24" t="n">
         <f aca="false">Engine!$B$39</f>
         <v>4166.64583333333</v>
       </c>
@@ -4285,9 +5415,9 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B32" s="23" t="n">
+        <v>331</v>
+      </c>
+      <c r="B32" s="24" t="n">
         <f aca="false">Engine!$B$35</f>
         <v>7320</v>
       </c>
@@ -4301,9 +5431,9 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B33" s="23" t="n">
+        <v>332</v>
+      </c>
+      <c r="B33" s="24" t="n">
         <f aca="false">Engine!$B$37</f>
         <v>3111.11111111111</v>
       </c>
@@ -4317,9 +5447,9 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B34" s="23" t="n">
+        <v>333</v>
+      </c>
+      <c r="B34" s="24" t="n">
         <f aca="false">Engine!$B$38</f>
         <v>1575</v>
       </c>
@@ -4333,9 +5463,9 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B35" s="23" t="n">
+        <v>334</v>
+      </c>
+      <c r="B35" s="24" t="n">
         <f aca="false">Engine!$B$42</f>
         <v>16172.7569444444</v>
       </c>
@@ -4349,9 +5479,9 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B36" s="23" t="n">
+        <v>335</v>
+      </c>
+      <c r="B36" s="24" t="n">
         <f aca="false">Engine!$B$54</f>
         <v>360158</v>
       </c>
@@ -4365,9 +5495,9 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B37" s="23" t="n">
+        <v>336</v>
+      </c>
+      <c r="B37" s="24" t="n">
         <f aca="false">Engine!$B$55</f>
         <v>187798.95</v>
       </c>
@@ -4381,9 +5511,9 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B38" s="23" t="n">
+        <v>337</v>
+      </c>
+      <c r="B38" s="24" t="n">
         <f aca="false">Engine!$B$25</f>
         <v>52500</v>
       </c>
@@ -4397,9 +5527,9 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B39" s="23" t="n">
+        <v>338</v>
+      </c>
+      <c r="B39" s="24" t="n">
         <f aca="false">Engine!$B$26</f>
         <v>574.166666666667</v>
       </c>
@@ -4413,9 +5543,9 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B40" s="23" t="n">
+        <v>339</v>
+      </c>
+      <c r="B40" s="24" t="n">
         <f aca="false">Engine!$B$5+Engine!$B$25+Engine!$B$26</f>
         <v>105613.666666667</v>
       </c>
@@ -4429,9 +5559,9 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B41" s="23" t="n">
+        <v>340</v>
+      </c>
+      <c r="B41" s="24" t="n">
         <f aca="false">Engine!$B$41</f>
         <v>15553.6458333333</v>
       </c>
@@ -4445,14 +5575,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B42" s="28" t="str">
+        <v>341</v>
+      </c>
+      <c r="B42" s="29" t="str">
         <f aca="false">Engine!$B$51</f>
         <v>not entered</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>339</v>
+      <c r="C42" s="14" t="s">
+        <v>342</v>
       </c>
       <c r="D42" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B42=C42,"PASS","FAIL"))</f>
@@ -4461,7 +5591,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reverse-tco-model-v1.xlsx
+++ b/docs/reverse-tco-model-v1.xlsx
@@ -10,14 +10,15 @@
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="RateCard" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Hardware" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="PerfFactors" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Inputs" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Engine" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Results" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Validation" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="EngineRegression" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Crossover" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="CloudRates" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Hardware" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="PerfFactors" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Inputs" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Engine" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Results" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Validation" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="EngineRegression" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Crossover" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="382">
   <si>
     <t xml:space="preserve">Reverse TCO Tool v1 — Cloud AIaaS Spend to On-Prem NVIDIA Infrastructure</t>
   </si>
@@ -103,6 +104,9 @@
     <t xml:space="preserve">GROWTH CONVENTION (documented, both engines): cloud compute spend grows at the selected demand-growth rate; cloud non-compute spend and all on-prem opex grow at the 4%/yr ops rate. Crossover (Results!B26) is computed from cumulative monthly cash flows on the Crossover sheet; static payback is retained as a secondary metric only. Equinix bundle note: per-DGX rate covers system colocation; separate storage-rack colocation is not separately modeled (storage support is).</t>
   </si>
   <si>
+    <t xml:space="preserve">V2.3 (audit round 5): CloudRates sheet — blended rate routed by selected GPU class (was hardwired to B200 rates, the round-5 P0); Crossover rebuilt on the STATED bill baseline with RateCard-referenced growth (hardcoded 1.04 removed); Tier-1 storage Auto mode derives PB from the bill (Known mode preserves Tier 2/3 entry); crossover suppressed when adjusted capacity exhausts before breakeven; fixture check includes storage mode; crossover regression check + 5-scenario manual checklist added; Validation tolerance tightened to MAX($1, 0.01%).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rate Card — all editable (blue). Effective date + source in column C.</t>
   </si>
   <si>
@@ -115,13 +119,13 @@
     <t xml:space="preserve">CLOUD (AWS, B200-class 8-GPU instance; NVIDIA TCO tool defaults Jul 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Instance rate, on-demand ($/instance-hr)</t>
+    <t xml:space="preserve">Instance rate, on-demand ($/instance-hr) — B200 REFERENCE ROW; Engine uses CloudRates lookup since v2.3</t>
   </si>
   <si>
     <t xml:space="preserve">p6-b200.48xlarge class; NVIDIA TCO tool</t>
   </si>
   <si>
-    <t xml:space="preserve">Instance rate, 1-yr reserved ($/instance-hr)</t>
+    <t xml:space="preserve">Instance rate, 1-yr reserved ($/instance-hr) — B200 REFERENCE ROW; Engine uses CloudRates lookup since v2.3</t>
   </si>
   <si>
     <t xml:space="preserve">NVIDIA TCO tool</t>
@@ -256,15 +260,75 @@
     <t xml:space="preserve">NVIDIA default</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud instance rates by GPU class — AWS (workbook scope)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPU class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OD $/instance-hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-yr $/instance-hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPUs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p4d.24xlarge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LISTED (tracker)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul-Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p5.48xlarge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p5e.48xlarge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B200/B300-class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p6-b200.48xlarge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LISTED (NVIDIA tool snapshot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved = 40% off on-demand (est., matches NVIDIA snapshot ratio). NVAIE support stays on RateCard (B6/B7, per instance-hr). v2.3: Engine!B4 routes by the GPU class selected on Inputs — previously all classes used the B200 row (audit round 5, P0).</t>
+  </si>
+  <si>
     <t xml:space="preserve">On-Prem System Registry — add rows as new systems are priced (blue = editable)</t>
   </si>
   <si>
     <t xml:space="preserve">System</t>
   </si>
   <si>
-    <t xml:space="preserve">GPUs</t>
-  </si>
-  <si>
     <t xml:space="preserve">System cost</t>
   </si>
   <si>
@@ -319,18 +383,6 @@
     <t xml:space="preserve">Cloud GPU class list (drives PerfFactors lookups; keep in sync with PerfFactors rows):</t>
   </si>
   <si>
-    <t xml:space="preserve">A100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B200/B300-class</t>
-  </si>
-  <si>
     <t xml:space="preserve">Generational performance factors: cloud GPU class -&gt; DGX B200 target (blue = editable)</t>
   </si>
   <si>
@@ -415,7 +467,7 @@
     <t xml:space="preserve">Total storage (PB)</t>
   </si>
   <si>
-    <t xml:space="preserve">If unknown, leave default; refine at Tier 3</t>
+    <t xml:space="preserve">Used only when Storage mode = Known (Inputs!B38); Auto derives PB from the bill</t>
   </si>
   <si>
     <t xml:space="preserve">Fast storage share (%)</t>
@@ -541,6 +593,15 @@
     <t xml:space="preserve">Flat % simplification; excludes cluster nodes/racks/one-time</t>
   </si>
   <si>
+    <t xml:space="preserve">Storage mode (Auto = derive PB from bill; Known = use entered PB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2.3: Tier 1 is a true two-input model — Auto sizes storage from the non-compute share of the bill; enter Known + PB for Tier 2/3 precision</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calculation Engine — no edits here (green = cross-tab links)</t>
   </si>
   <si>
@@ -553,7 +614,7 @@
     <t xml:space="preserve">Blended cloud rate ($/instance-hr)</t>
   </si>
   <si>
-    <t xml:space="preserve">Commitment-mix weighted, incl. NVAIE support and PaaS uplift</t>
+    <t xml:space="preserve">v2.3: rate now routed by the selected GPU class via CloudRates (audit round 5 P0 — was hardwired to B200 rates)</t>
   </si>
   <si>
     <t xml:space="preserve">Estimated monthly compute spend ($)</t>
@@ -757,6 +818,12 @@
     <t xml:space="preserve">Reconciliation status</t>
   </si>
   <si>
+    <t xml:space="preserve">Auto-derived total storage PB (from non-compute budget net of admin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective total storage PB used by the model</t>
+  </si>
+  <si>
     <t xml:space="preserve">Results — Cloud vs. On-Prem</t>
   </si>
   <si>
@@ -925,6 +992,9 @@
     <t xml:space="preserve">On-prem monthly total, leased ($/mo)</t>
   </si>
   <si>
+    <t xml:space="preserve">v2.3: tolerance tightened to MAX($1, 0.01%) matching the live regression standard (was 1%).</t>
+  </si>
+  <si>
     <t xml:space="preserve">All rows must read PASS before customer use. If a rate card value changes, expected values here describe the NVIDIA tool snapshot, not your new reality — they exist to prove the formula logic, not to freeze prices.</t>
   </si>
   <si>
@@ -988,6 +1058,12 @@
     <t xml:space="preserve">0 / 0 / 0 / 0 / 0%</t>
   </si>
   <si>
+    <t xml:space="preserve">Inputs!B38 Storage mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixture loaded?</t>
   </si>
   <si>
@@ -1060,9 +1136,33 @@
     <t xml:space="preserve">not entered</t>
   </si>
   <si>
+    <t xml:space="preserve">Crossover month under fixture (Results!B26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month 24</t>
+  </si>
+  <si>
     <t xml:space="preserve">v2.1: coverage extended to cloud storage/admin/total, Equinix option and lease text; fixture check now verifies GPU class, facility, system and provider.</t>
   </si>
   <si>
+    <t xml:space="preserve">SCENARIO CHECKLIST (manual, one at a time — v2.3):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1 No-crossover text: bill $10,000, Storage mode Auto, other defaults → Results!B26 shows the no-crossover text, not a month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 Ops-growth sensitivity: change RateCard!B37 from 0.04 to 0.08 → Results!B26 crossover month CHANGES (guards against re-hardcoding).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 N+1 invariance: toggle Inputs!B36 from 0 to 1 → Results!B23 headroom values UNCHANGED (spare is not growth capacity).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4 Capacity suppression: high bill (e.g. $2M) with growth 25% → if crossover month exceeds adjusted exhaustion, Results!B26 shows the cannot-be-determined text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5 Class routing: switch Inputs!B8 H100 ↔ B200/B300-class → Engine!B4 blended rate changes per CloudRates (H100 ≈ $35.90 vs B200 ≈ $71.24 at 100% reserved).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Month</t>
   </si>
   <si>
@@ -1075,14 +1175,14 @@
     <t xml:space="preserve">Crossed</t>
   </si>
   <si>
-    <t xml:space="preserve">v2.2: cumulative monthly cash flows (audit round 4). Cloud compute grows at demand rate, non-compute at 4%/yr, both stepped annually; on-prem = capex+one-time at month 1 + opex growing 4%/yr. Residual credit excluded (realized only at exit).</t>
+    <t xml:space="preserve">v2.3: cumulative monthly cash flows from the STATED bill (single source of truth with Results): compute portion grows at demand rate, non-compute at RateCard ops growth; reconstructed components validate the bill (reconciliation) but do not replace it. On-prem = capex + one-time at month 1 + opex growing at RateCard ops growth. Residual excluded until exit.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -1092,6 +1192,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
     <numFmt numFmtId="171" formatCode="0.00\x"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="173" formatCode="0.000&quot; PB&quot;"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1219,7 +1320,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1333,6 +1434,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1596,7 +1701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1732,6 +1837,11 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1750,6 +1860,550 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>105079</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0.49491</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B21" s="30" t="str">
+        <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200/B300-class",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS",Inputs!$B$38="Known"),"YES","NO — set fixture first")</f>
+        <v>NO — set fixture first</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B24" s="25" t="n">
+        <f aca="false">Engine!$B$7</f>
+        <v>11707.9665738162</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D24" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B24-C24)&lt;=MAX(1,0.0001*MAX(ABS(C24),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B25" s="23" t="n">
+        <f aca="false">Engine!$B$4</f>
+        <v>35.9</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>71.24</v>
+      </c>
+      <c r="D25" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B25-C25)&lt;=MAX(1,0.0001*MAX(ABS(C25),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B26" s="26" t="n">
+        <f aca="false">Engine!$B$11</f>
+        <v>4.79741935483871</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B26-C26)&lt;=MAX(1,0.0001*MAX(ABS(C26),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B27" s="25" t="n">
+        <f aca="false">Engine!$B$18</f>
+        <v>1</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B27-C27)&lt;=MAX(1,0.0001*MAX(ABS(C27),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <f aca="false">Engine!$B$19</f>
+        <v>3</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B28-C28)&lt;=MAX(1,0.0001*MAX(ABS(C28),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <f aca="false">Engine!$B$31</f>
+        <v>1359793</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1359793</v>
+      </c>
+      <c r="D29" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B29-C29)&lt;=MAX(1,0.0001*MAX(ABS(C29),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <f aca="false">Engine!$B$32</f>
+        <v>668125.714285714</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>675000</v>
+      </c>
+      <c r="D30" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B30-C30)&lt;=MAX(1,0.0001*MAX(ABS(C30),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B31" s="24" t="n">
+        <f aca="false">Engine!$B$39</f>
+        <v>4124.21218306878</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>4167</v>
+      </c>
+      <c r="D31" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B31-C31)&lt;=MAX(1,0.0001*MAX(ABS(C31),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B32" s="24" t="n">
+        <f aca="false">Engine!$B$35</f>
+        <v>7289.44761904762</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>7320</v>
+      </c>
+      <c r="D32" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B32-C32)&lt;=MAX(1,0.0001*MAX(ABS(C32),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B33" s="24" t="n">
+        <f aca="false">Engine!$B$37</f>
+        <v>3110.54532627866</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>3111</v>
+      </c>
+      <c r="D33" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B33-C33)&lt;=MAX(1,0.0001*MAX(ABS(C33),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B34" s="24" t="n">
+        <f aca="false">Engine!$B$38</f>
+        <v>1575</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>1575</v>
+      </c>
+      <c r="D34" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B34-C34)&lt;=MAX(1,0.0001*MAX(ABS(C34),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B35" s="24" t="n">
+        <f aca="false">Engine!$B$42</f>
+        <v>16099.2051283951</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>16173</v>
+      </c>
+      <c r="D35" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B35-C35)&lt;=MAX(1,0.0001*MAX(ABS(C35),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B36" s="24" t="n">
+        <f aca="false">Engine!$B$54</f>
+        <v>359648.793650794</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D36" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B36-C36)&lt;=MAX(1,0.0001*MAX(ABS(C36),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <f aca="false">Engine!$B$55</f>
+        <v>186767.807142857</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B37-C37)&lt;=MAX(1,0.0001*MAX(ABS(C37),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B38" s="24" t="n">
+        <f aca="false">Engine!$B$25</f>
+        <v>51965.3333333333</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>52500</v>
+      </c>
+      <c r="D38" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B38-C38)&lt;=MAX(1,0.0001*MAX(ABS(C38),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B39" s="24" t="n">
+        <f aca="false">Engine!$B$26</f>
+        <v>574.166666666667</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>574</v>
+      </c>
+      <c r="D39" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B39-C39)&lt;=MAX(1,0.0001*MAX(ABS(C39),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B40" s="24" t="n">
+        <f aca="false">Engine!$B$5+Engine!$B$25+Engine!$B$26</f>
+        <v>105079</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>105079</v>
+      </c>
+      <c r="D40" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B40-C40)&lt;=MAX(1,0.0001*MAX(ABS(C40),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B41" s="24" t="n">
+        <f aca="false">Engine!$B$41</f>
+        <v>15511.2121830688</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>15554</v>
+      </c>
+      <c r="D41" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B41-C41)&lt;=MAX(1,0.0001*MAX(ABS(C41),1)),"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" s="30" t="str">
+        <f aca="false">Engine!$B$51</f>
+        <v>not entered</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D42" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B42=C42,"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B43" s="30" t="str">
+        <f aca="false">Results!$B$26</f>
+        <v>Month 25</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="D43" s="4" t="str">
+        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B43=C43,"PASS","FAIL"))</f>
+        <v>FIXTURE NOT LOADED</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1759,32 +2413,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="n">
-        <f aca="false">(Engine!$B$5*(1+Inputs!$B$14)^INT((1-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((1-1)/12))</f>
-        <v>105613.666666667</v>
-      </c>
-      <c r="C2" s="30" t="n">
-        <f aca="false">Engine!$B$33+Engine!$B$54+(Engine!$B$42*1.04^INT((1-1)/12))</f>
-        <v>2411123.75694444</v>
+      <c r="B2" s="31" t="n">
+        <f aca="false">(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((1-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((1-1)/12))</f>
+        <v>105079</v>
+      </c>
+      <c r="C2" s="31" t="n">
+        <f aca="false">Engine!$B$33+Engine!$B$54+(Engine!$B$42*(1+RateCard!$B$37)^INT((1-1)/12))</f>
+        <v>2403666.7130649</v>
       </c>
       <c r="D2" s="1" t="n">
         <f aca="false">IF(B2&gt;=C2,1,0)</f>
@@ -1795,13 +2449,13 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="n">
-        <f aca="false">B2+(Engine!$B$5*(1+Inputs!$B$14)^INT((2-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((2-1)/12))</f>
-        <v>211227.333333333</v>
-      </c>
-      <c r="C3" s="30" t="n">
-        <f aca="false">C2+(Engine!$B$42*1.04^INT((2-1)/12))</f>
-        <v>2427296.51388889</v>
+      <c r="B3" s="31" t="n">
+        <f aca="false">B2+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((2-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((2-1)/12))</f>
+        <v>210158</v>
+      </c>
+      <c r="C3" s="31" t="n">
+        <f aca="false">C2+(Engine!$B$42*(1+RateCard!$B$37)^INT((2-1)/12))</f>
+        <v>2419765.9181933</v>
       </c>
       <c r="D3" s="1" t="n">
         <f aca="false">IF(B3&gt;=C3,1,0)</f>
@@ -1812,13 +2466,13 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="n">
-        <f aca="false">B3+(Engine!$B$5*(1+Inputs!$B$14)^INT((3-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((3-1)/12))</f>
-        <v>316841</v>
-      </c>
-      <c r="C4" s="30" t="n">
-        <f aca="false">C3+(Engine!$B$42*1.04^INT((3-1)/12))</f>
-        <v>2443469.27083333</v>
+      <c r="B4" s="31" t="n">
+        <f aca="false">B3+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((3-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((3-1)/12))</f>
+        <v>315237</v>
+      </c>
+      <c r="C4" s="31" t="n">
+        <f aca="false">C3+(Engine!$B$42*(1+RateCard!$B$37)^INT((3-1)/12))</f>
+        <v>2435865.12332169</v>
       </c>
       <c r="D4" s="1" t="n">
         <f aca="false">IF(B4&gt;=C4,1,0)</f>
@@ -1829,13 +2483,13 @@
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="n">
-        <f aca="false">B4+(Engine!$B$5*(1+Inputs!$B$14)^INT((4-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((4-1)/12))</f>
-        <v>422454.666666667</v>
-      </c>
-      <c r="C5" s="30" t="n">
-        <f aca="false">C4+(Engine!$B$42*1.04^INT((4-1)/12))</f>
-        <v>2459642.02777778</v>
+      <c r="B5" s="31" t="n">
+        <f aca="false">B4+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((4-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((4-1)/12))</f>
+        <v>420316</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <f aca="false">C4+(Engine!$B$42*(1+RateCard!$B$37)^INT((4-1)/12))</f>
+        <v>2451964.32845009</v>
       </c>
       <c r="D5" s="1" t="n">
         <f aca="false">IF(B5&gt;=C5,1,0)</f>
@@ -1846,13 +2500,13 @@
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="30" t="n">
-        <f aca="false">B5+(Engine!$B$5*(1+Inputs!$B$14)^INT((5-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((5-1)/12))</f>
-        <v>528068.333333333</v>
-      </c>
-      <c r="C6" s="30" t="n">
-        <f aca="false">C5+(Engine!$B$42*1.04^INT((5-1)/12))</f>
-        <v>2475814.78472222</v>
+      <c r="B6" s="31" t="n">
+        <f aca="false">B5+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((5-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((5-1)/12))</f>
+        <v>525395</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <f aca="false">C5+(Engine!$B$42*(1+RateCard!$B$37)^INT((5-1)/12))</f>
+        <v>2468063.53357848</v>
       </c>
       <c r="D6" s="1" t="n">
         <f aca="false">IF(B6&gt;=C6,1,0)</f>
@@ -1863,13 +2517,13 @@
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="30" t="n">
-        <f aca="false">B6+(Engine!$B$5*(1+Inputs!$B$14)^INT((6-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((6-1)/12))</f>
-        <v>633682</v>
-      </c>
-      <c r="C7" s="30" t="n">
-        <f aca="false">C6+(Engine!$B$42*1.04^INT((6-1)/12))</f>
-        <v>2491987.54166667</v>
+      <c r="B7" s="31" t="n">
+        <f aca="false">B6+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((6-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((6-1)/12))</f>
+        <v>630474</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <f aca="false">C6+(Engine!$B$42*(1+RateCard!$B$37)^INT((6-1)/12))</f>
+        <v>2484162.73870688</v>
       </c>
       <c r="D7" s="1" t="n">
         <f aca="false">IF(B7&gt;=C7,1,0)</f>
@@ -1880,13 +2534,13 @@
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="30" t="n">
-        <f aca="false">B7+(Engine!$B$5*(1+Inputs!$B$14)^INT((7-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((7-1)/12))</f>
-        <v>739295.666666667</v>
-      </c>
-      <c r="C8" s="30" t="n">
-        <f aca="false">C7+(Engine!$B$42*1.04^INT((7-1)/12))</f>
-        <v>2508160.29861111</v>
+      <c r="B8" s="31" t="n">
+        <f aca="false">B7+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((7-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((7-1)/12))</f>
+        <v>735553</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <f aca="false">C7+(Engine!$B$42*(1+RateCard!$B$37)^INT((7-1)/12))</f>
+        <v>2500261.94383527</v>
       </c>
       <c r="D8" s="1" t="n">
         <f aca="false">IF(B8&gt;=C8,1,0)</f>
@@ -1897,13 +2551,13 @@
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="30" t="n">
-        <f aca="false">B8+(Engine!$B$5*(1+Inputs!$B$14)^INT((8-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((8-1)/12))</f>
-        <v>844909.333333333</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <f aca="false">C8+(Engine!$B$42*1.04^INT((8-1)/12))</f>
-        <v>2524333.05555556</v>
+      <c r="B9" s="31" t="n">
+        <f aca="false">B8+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((8-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((8-1)/12))</f>
+        <v>840632</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <f aca="false">C8+(Engine!$B$42*(1+RateCard!$B$37)^INT((8-1)/12))</f>
+        <v>2516361.14896367</v>
       </c>
       <c r="D9" s="1" t="n">
         <f aca="false">IF(B9&gt;=C9,1,0)</f>
@@ -1914,13 +2568,13 @@
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="30" t="n">
-        <f aca="false">B9+(Engine!$B$5*(1+Inputs!$B$14)^INT((9-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((9-1)/12))</f>
-        <v>950523</v>
-      </c>
-      <c r="C10" s="30" t="n">
-        <f aca="false">C9+(Engine!$B$42*1.04^INT((9-1)/12))</f>
-        <v>2540505.8125</v>
+      <c r="B10" s="31" t="n">
+        <f aca="false">B9+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((9-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((9-1)/12))</f>
+        <v>945711</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <f aca="false">C9+(Engine!$B$42*(1+RateCard!$B$37)^INT((9-1)/12))</f>
+        <v>2532460.35409206</v>
       </c>
       <c r="D10" s="1" t="n">
         <f aca="false">IF(B10&gt;=C10,1,0)</f>
@@ -1931,13 +2585,13 @@
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="30" t="n">
-        <f aca="false">B10+(Engine!$B$5*(1+Inputs!$B$14)^INT((10-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((10-1)/12))</f>
-        <v>1056136.66666667</v>
-      </c>
-      <c r="C11" s="30" t="n">
-        <f aca="false">C10+(Engine!$B$42*1.04^INT((10-1)/12))</f>
-        <v>2556678.56944445</v>
+      <c r="B11" s="31" t="n">
+        <f aca="false">B10+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((10-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((10-1)/12))</f>
+        <v>1050790</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <f aca="false">C10+(Engine!$B$42*(1+RateCard!$B$37)^INT((10-1)/12))</f>
+        <v>2548559.55922046</v>
       </c>
       <c r="D11" s="1" t="n">
         <f aca="false">IF(B11&gt;=C11,1,0)</f>
@@ -1948,13 +2602,13 @@
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="30" t="n">
-        <f aca="false">B11+(Engine!$B$5*(1+Inputs!$B$14)^INT((11-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((11-1)/12))</f>
-        <v>1161750.33333333</v>
-      </c>
-      <c r="C12" s="30" t="n">
-        <f aca="false">C11+(Engine!$B$42*1.04^INT((11-1)/12))</f>
-        <v>2572851.32638889</v>
+      <c r="B12" s="31" t="n">
+        <f aca="false">B11+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((11-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((11-1)/12))</f>
+        <v>1155869</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <f aca="false">C11+(Engine!$B$42*(1+RateCard!$B$37)^INT((11-1)/12))</f>
+        <v>2564658.76434885</v>
       </c>
       <c r="D12" s="1" t="n">
         <f aca="false">IF(B12&gt;=C12,1,0)</f>
@@ -1965,13 +2619,13 @@
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="30" t="n">
-        <f aca="false">B12+(Engine!$B$5*(1+Inputs!$B$14)^INT((12-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((12-1)/12))</f>
-        <v>1267364</v>
-      </c>
-      <c r="C13" s="30" t="n">
-        <f aca="false">C12+(Engine!$B$42*1.04^INT((12-1)/12))</f>
-        <v>2589024.08333333</v>
+      <c r="B13" s="31" t="n">
+        <f aca="false">B12+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((12-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((12-1)/12))</f>
+        <v>1260948</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <f aca="false">C12+(Engine!$B$42*(1+RateCard!$B$37)^INT((12-1)/12))</f>
+        <v>2580757.96947725</v>
       </c>
       <c r="D13" s="1" t="n">
         <f aca="false">IF(B13&gt;=C13,1,0)</f>
@@ -1982,13 +2636,13 @@
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="30" t="n">
-        <f aca="false">B13+(Engine!$B$5*(1+Inputs!$B$14)^INT((13-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((13-1)/12))</f>
-        <v>1388235.50833333</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <f aca="false">C13+(Engine!$B$42*1.04^INT((13-1)/12))</f>
-        <v>2605843.75055556</v>
+      <c r="B14" s="31" t="n">
+        <f aca="false">B13+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((13-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((13-1)/12))</f>
+        <v>1381263.455</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <f aca="false">C13+(Engine!$B$42*(1+RateCard!$B$37)^INT((13-1)/12))</f>
+        <v>2597501.14281078</v>
       </c>
       <c r="D14" s="1" t="n">
         <f aca="false">IF(B14&gt;=C14,1,0)</f>
@@ -1999,13 +2653,13 @@
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="30" t="n">
-        <f aca="false">B14+(Engine!$B$5*(1+Inputs!$B$14)^INT((14-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((14-1)/12))</f>
-        <v>1509107.01666667</v>
-      </c>
-      <c r="C15" s="30" t="n">
-        <f aca="false">C14+(Engine!$B$42*1.04^INT((14-1)/12))</f>
-        <v>2622663.41777778</v>
+      <c r="B15" s="31" t="n">
+        <f aca="false">B14+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((14-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((14-1)/12))</f>
+        <v>1501578.91</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">C14+(Engine!$B$42*(1+RateCard!$B$37)^INT((14-1)/12))</f>
+        <v>2614244.31614431</v>
       </c>
       <c r="D15" s="1" t="n">
         <f aca="false">IF(B15&gt;=C15,1,0)</f>
@@ -2016,13 +2670,13 @@
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="30" t="n">
-        <f aca="false">B15+(Engine!$B$5*(1+Inputs!$B$14)^INT((15-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((15-1)/12))</f>
-        <v>1629978.525</v>
-      </c>
-      <c r="C16" s="30" t="n">
-        <f aca="false">C15+(Engine!$B$42*1.04^INT((15-1)/12))</f>
-        <v>2639483.085</v>
+      <c r="B16" s="31" t="n">
+        <f aca="false">B15+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((15-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((15-1)/12))</f>
+        <v>1621894.365</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <f aca="false">C15+(Engine!$B$42*(1+RateCard!$B$37)^INT((15-1)/12))</f>
+        <v>2630987.48947784</v>
       </c>
       <c r="D16" s="1" t="n">
         <f aca="false">IF(B16&gt;=C16,1,0)</f>
@@ -2033,13 +2687,13 @@
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="30" t="n">
-        <f aca="false">B16+(Engine!$B$5*(1+Inputs!$B$14)^INT((16-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((16-1)/12))</f>
-        <v>1750850.03333333</v>
-      </c>
-      <c r="C17" s="30" t="n">
-        <f aca="false">C16+(Engine!$B$42*1.04^INT((16-1)/12))</f>
-        <v>2656302.75222222</v>
+      <c r="B17" s="31" t="n">
+        <f aca="false">B16+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((16-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((16-1)/12))</f>
+        <v>1742209.82</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <f aca="false">C16+(Engine!$B$42*(1+RateCard!$B$37)^INT((16-1)/12))</f>
+        <v>2647730.66281137</v>
       </c>
       <c r="D17" s="1" t="n">
         <f aca="false">IF(B17&gt;=C17,1,0)</f>
@@ -2050,13 +2704,13 @@
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="30" t="n">
-        <f aca="false">B17+(Engine!$B$5*(1+Inputs!$B$14)^INT((17-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((17-1)/12))</f>
-        <v>1871721.54166667</v>
-      </c>
-      <c r="C18" s="30" t="n">
-        <f aca="false">C17+(Engine!$B$42*1.04^INT((17-1)/12))</f>
-        <v>2673122.41944445</v>
+      <c r="B18" s="31" t="n">
+        <f aca="false">B17+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((17-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((17-1)/12))</f>
+        <v>1862525.275</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <f aca="false">C17+(Engine!$B$42*(1+RateCard!$B$37)^INT((17-1)/12))</f>
+        <v>2664473.8361449</v>
       </c>
       <c r="D18" s="1" t="n">
         <f aca="false">IF(B18&gt;=C18,1,0)</f>
@@ -2067,13 +2721,13 @@
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="30" t="n">
-        <f aca="false">B18+(Engine!$B$5*(1+Inputs!$B$14)^INT((18-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((18-1)/12))</f>
-        <v>1992593.05</v>
-      </c>
-      <c r="C19" s="30" t="n">
-        <f aca="false">C18+(Engine!$B$42*1.04^INT((18-1)/12))</f>
-        <v>2689942.08666667</v>
+      <c r="B19" s="31" t="n">
+        <f aca="false">B18+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((18-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((18-1)/12))</f>
+        <v>1982840.73</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <f aca="false">C18+(Engine!$B$42*(1+RateCard!$B$37)^INT((18-1)/12))</f>
+        <v>2681217.00947843</v>
       </c>
       <c r="D19" s="1" t="n">
         <f aca="false">IF(B19&gt;=C19,1,0)</f>
@@ -2084,13 +2738,13 @@
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="30" t="n">
-        <f aca="false">B19+(Engine!$B$5*(1+Inputs!$B$14)^INT((19-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((19-1)/12))</f>
-        <v>2113464.55833333</v>
-      </c>
-      <c r="C20" s="30" t="n">
-        <f aca="false">C19+(Engine!$B$42*1.04^INT((19-1)/12))</f>
-        <v>2706761.75388889</v>
+      <c r="B20" s="31" t="n">
+        <f aca="false">B19+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((19-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((19-1)/12))</f>
+        <v>2103156.185</v>
+      </c>
+      <c r="C20" s="31" t="n">
+        <f aca="false">C19+(Engine!$B$42*(1+RateCard!$B$37)^INT((19-1)/12))</f>
+        <v>2697960.18281196</v>
       </c>
       <c r="D20" s="1" t="n">
         <f aca="false">IF(B20&gt;=C20,1,0)</f>
@@ -2101,13 +2755,13 @@
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="30" t="n">
-        <f aca="false">B20+(Engine!$B$5*(1+Inputs!$B$14)^INT((20-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((20-1)/12))</f>
-        <v>2234336.06666667</v>
-      </c>
-      <c r="C21" s="30" t="n">
-        <f aca="false">C20+(Engine!$B$42*1.04^INT((20-1)/12))</f>
-        <v>2723581.42111111</v>
+      <c r="B21" s="31" t="n">
+        <f aca="false">B20+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((20-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((20-1)/12))</f>
+        <v>2223471.64</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <f aca="false">C20+(Engine!$B$42*(1+RateCard!$B$37)^INT((20-1)/12))</f>
+        <v>2714703.35614549</v>
       </c>
       <c r="D21" s="1" t="n">
         <f aca="false">IF(B21&gt;=C21,1,0)</f>
@@ -2118,13 +2772,13 @@
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="30" t="n">
-        <f aca="false">B21+(Engine!$B$5*(1+Inputs!$B$14)^INT((21-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((21-1)/12))</f>
-        <v>2355207.575</v>
-      </c>
-      <c r="C22" s="30" t="n">
-        <f aca="false">C21+(Engine!$B$42*1.04^INT((21-1)/12))</f>
-        <v>2740401.08833334</v>
+      <c r="B22" s="31" t="n">
+        <f aca="false">B21+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((21-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((21-1)/12))</f>
+        <v>2343787.095</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <f aca="false">C21+(Engine!$B$42*(1+RateCard!$B$37)^INT((21-1)/12))</f>
+        <v>2731446.52947903</v>
       </c>
       <c r="D22" s="1" t="n">
         <f aca="false">IF(B22&gt;=C22,1,0)</f>
@@ -2135,13 +2789,13 @@
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="30" t="n">
-        <f aca="false">B22+(Engine!$B$5*(1+Inputs!$B$14)^INT((22-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((22-1)/12))</f>
-        <v>2476079.08333333</v>
-      </c>
-      <c r="C23" s="30" t="n">
-        <f aca="false">C22+(Engine!$B$42*1.04^INT((22-1)/12))</f>
-        <v>2757220.75555556</v>
+      <c r="B23" s="31" t="n">
+        <f aca="false">B22+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((22-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((22-1)/12))</f>
+        <v>2464102.55</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <f aca="false">C22+(Engine!$B$42*(1+RateCard!$B$37)^INT((22-1)/12))</f>
+        <v>2748189.70281256</v>
       </c>
       <c r="D23" s="1" t="n">
         <f aca="false">IF(B23&gt;=C23,1,0)</f>
@@ -2152,13 +2806,13 @@
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="30" t="n">
-        <f aca="false">B23+(Engine!$B$5*(1+Inputs!$B$14)^INT((23-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((23-1)/12))</f>
-        <v>2596950.59166667</v>
-      </c>
-      <c r="C24" s="30" t="n">
-        <f aca="false">C23+(Engine!$B$42*1.04^INT((23-1)/12))</f>
-        <v>2774040.42277778</v>
+      <c r="B24" s="31" t="n">
+        <f aca="false">B23+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((23-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((23-1)/12))</f>
+        <v>2584418.005</v>
+      </c>
+      <c r="C24" s="31" t="n">
+        <f aca="false">C23+(Engine!$B$42*(1+RateCard!$B$37)^INT((23-1)/12))</f>
+        <v>2764932.87614609</v>
       </c>
       <c r="D24" s="1" t="n">
         <f aca="false">IF(B24&gt;=C24,1,0)</f>
@@ -2169,13 +2823,13 @@
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="30" t="n">
-        <f aca="false">B24+(Engine!$B$5*(1+Inputs!$B$14)^INT((24-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((24-1)/12))</f>
-        <v>2717822.1</v>
-      </c>
-      <c r="C25" s="30" t="n">
-        <f aca="false">C24+(Engine!$B$42*1.04^INT((24-1)/12))</f>
-        <v>2790860.09</v>
+      <c r="B25" s="31" t="n">
+        <f aca="false">B24+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((24-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((24-1)/12))</f>
+        <v>2704733.46</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <f aca="false">C24+(Engine!$B$42*(1+RateCard!$B$37)^INT((24-1)/12))</f>
+        <v>2781676.04947962</v>
       </c>
       <c r="D25" s="1" t="n">
         <f aca="false">IF(B25&gt;=C25,1,0)</f>
@@ -2186,13 +2840,13 @@
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="30" t="n">
-        <f aca="false">B25+(Engine!$B$5*(1+Inputs!$B$14)^INT((25-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((25-1)/12))</f>
-        <v>2857320.08741667</v>
-      </c>
-      <c r="C26" s="30" t="n">
-        <f aca="false">C25+(Engine!$B$42*1.04^INT((25-1)/12))</f>
-        <v>2808352.54391111</v>
+      <c r="B26" s="31" t="n">
+        <f aca="false">B25+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((25-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((25-1)/12))</f>
+        <v>2843653.15195</v>
+      </c>
+      <c r="C26" s="31" t="n">
+        <f aca="false">C25+(Engine!$B$42*(1+RateCard!$B$37)^INT((25-1)/12))</f>
+        <v>2799088.94974649</v>
       </c>
       <c r="D26" s="1" t="n">
         <f aca="false">IF(B26&gt;=C26,1,0)</f>
@@ -2203,13 +2857,13 @@
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="30" t="n">
-        <f aca="false">B26+(Engine!$B$5*(1+Inputs!$B$14)^INT((26-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((26-1)/12))</f>
-        <v>2996818.07483333</v>
-      </c>
-      <c r="C27" s="30" t="n">
-        <f aca="false">C26+(Engine!$B$42*1.04^INT((26-1)/12))</f>
-        <v>2825844.99782222</v>
+      <c r="B27" s="31" t="n">
+        <f aca="false">B26+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((26-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((26-1)/12))</f>
+        <v>2982572.8439</v>
+      </c>
+      <c r="C27" s="31" t="n">
+        <f aca="false">C26+(Engine!$B$42*(1+RateCard!$B$37)^INT((26-1)/12))</f>
+        <v>2816501.85001336</v>
       </c>
       <c r="D27" s="1" t="n">
         <f aca="false">IF(B27&gt;=C27,1,0)</f>
@@ -2220,13 +2874,13 @@
       <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="30" t="n">
-        <f aca="false">B27+(Engine!$B$5*(1+Inputs!$B$14)^INT((27-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((27-1)/12))</f>
-        <v>3136316.06225</v>
-      </c>
-      <c r="C28" s="30" t="n">
-        <f aca="false">C27+(Engine!$B$42*1.04^INT((27-1)/12))</f>
-        <v>2843337.45173334</v>
+      <c r="B28" s="31" t="n">
+        <f aca="false">B27+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((27-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((27-1)/12))</f>
+        <v>3121492.53585</v>
+      </c>
+      <c r="C28" s="31" t="n">
+        <f aca="false">C27+(Engine!$B$42*(1+RateCard!$B$37)^INT((27-1)/12))</f>
+        <v>2833914.75028023</v>
       </c>
       <c r="D28" s="1" t="n">
         <f aca="false">IF(B28&gt;=C28,1,0)</f>
@@ -2237,13 +2891,13 @@
       <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="30" t="n">
-        <f aca="false">B28+(Engine!$B$5*(1+Inputs!$B$14)^INT((28-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((28-1)/12))</f>
-        <v>3275814.04966667</v>
-      </c>
-      <c r="C29" s="30" t="n">
-        <f aca="false">C28+(Engine!$B$42*1.04^INT((28-1)/12))</f>
-        <v>2860829.90564445</v>
+      <c r="B29" s="31" t="n">
+        <f aca="false">B28+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((28-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((28-1)/12))</f>
+        <v>3260412.2278</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <f aca="false">C28+(Engine!$B$42*(1+RateCard!$B$37)^INT((28-1)/12))</f>
+        <v>2851327.65054711</v>
       </c>
       <c r="D29" s="1" t="n">
         <f aca="false">IF(B29&gt;=C29,1,0)</f>
@@ -2254,13 +2908,13 @@
       <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="30" t="n">
-        <f aca="false">B29+(Engine!$B$5*(1+Inputs!$B$14)^INT((29-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((29-1)/12))</f>
-        <v>3415312.03708333</v>
-      </c>
-      <c r="C30" s="30" t="n">
-        <f aca="false">C29+(Engine!$B$42*1.04^INT((29-1)/12))</f>
-        <v>2878322.35955556</v>
+      <c r="B30" s="31" t="n">
+        <f aca="false">B29+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((29-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((29-1)/12))</f>
+        <v>3399331.91975</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <f aca="false">C29+(Engine!$B$42*(1+RateCard!$B$37)^INT((29-1)/12))</f>
+        <v>2868740.55081398</v>
       </c>
       <c r="D30" s="1" t="n">
         <f aca="false">IF(B30&gt;=C30,1,0)</f>
@@ -2271,13 +2925,13 @@
       <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="30" t="n">
-        <f aca="false">B30+(Engine!$B$5*(1+Inputs!$B$14)^INT((30-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((30-1)/12))</f>
-        <v>3554810.0245</v>
-      </c>
-      <c r="C31" s="30" t="n">
-        <f aca="false">C30+(Engine!$B$42*1.04^INT((30-1)/12))</f>
-        <v>2895814.81346667</v>
+      <c r="B31" s="31" t="n">
+        <f aca="false">B30+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((30-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((30-1)/12))</f>
+        <v>3538251.6117</v>
+      </c>
+      <c r="C31" s="31" t="n">
+        <f aca="false">C30+(Engine!$B$42*(1+RateCard!$B$37)^INT((30-1)/12))</f>
+        <v>2886153.45108085</v>
       </c>
       <c r="D31" s="1" t="n">
         <f aca="false">IF(B31&gt;=C31,1,0)</f>
@@ -2288,13 +2942,13 @@
       <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="30" t="n">
-        <f aca="false">B31+(Engine!$B$5*(1+Inputs!$B$14)^INT((31-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((31-1)/12))</f>
-        <v>3694308.01191667</v>
-      </c>
-      <c r="C32" s="30" t="n">
-        <f aca="false">C31+(Engine!$B$42*1.04^INT((31-1)/12))</f>
-        <v>2913307.26737778</v>
+      <c r="B32" s="31" t="n">
+        <f aca="false">B31+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((31-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((31-1)/12))</f>
+        <v>3677171.30365</v>
+      </c>
+      <c r="C32" s="31" t="n">
+        <f aca="false">C31+(Engine!$B$42*(1+RateCard!$B$37)^INT((31-1)/12))</f>
+        <v>2903566.35134772</v>
       </c>
       <c r="D32" s="1" t="n">
         <f aca="false">IF(B32&gt;=C32,1,0)</f>
@@ -2305,13 +2959,13 @@
       <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="30" t="n">
-        <f aca="false">B32+(Engine!$B$5*(1+Inputs!$B$14)^INT((32-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((32-1)/12))</f>
-        <v>3833805.99933333</v>
-      </c>
-      <c r="C33" s="30" t="n">
-        <f aca="false">C32+(Engine!$B$42*1.04^INT((32-1)/12))</f>
-        <v>2930799.72128889</v>
+      <c r="B33" s="31" t="n">
+        <f aca="false">B32+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((32-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((32-1)/12))</f>
+        <v>3816090.9956</v>
+      </c>
+      <c r="C33" s="31" t="n">
+        <f aca="false">C32+(Engine!$B$42*(1+RateCard!$B$37)^INT((32-1)/12))</f>
+        <v>2920979.2516146</v>
       </c>
       <c r="D33" s="1" t="n">
         <f aca="false">IF(B33&gt;=C33,1,0)</f>
@@ -2322,13 +2976,13 @@
       <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="30" t="n">
-        <f aca="false">B33+(Engine!$B$5*(1+Inputs!$B$14)^INT((33-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((33-1)/12))</f>
-        <v>3973303.98675</v>
-      </c>
-      <c r="C34" s="30" t="n">
-        <f aca="false">C33+(Engine!$B$42*1.04^INT((33-1)/12))</f>
-        <v>2948292.1752</v>
+      <c r="B34" s="31" t="n">
+        <f aca="false">B33+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((33-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((33-1)/12))</f>
+        <v>3955010.68755</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <f aca="false">C33+(Engine!$B$42*(1+RateCard!$B$37)^INT((33-1)/12))</f>
+        <v>2938392.15188147</v>
       </c>
       <c r="D34" s="1" t="n">
         <f aca="false">IF(B34&gt;=C34,1,0)</f>
@@ -2339,13 +2993,13 @@
       <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="30" t="n">
-        <f aca="false">B34+(Engine!$B$5*(1+Inputs!$B$14)^INT((34-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((34-1)/12))</f>
-        <v>4112801.97416666</v>
-      </c>
-      <c r="C35" s="30" t="n">
-        <f aca="false">C34+(Engine!$B$42*1.04^INT((34-1)/12))</f>
-        <v>2965784.62911111</v>
+      <c r="B35" s="31" t="n">
+        <f aca="false">B34+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((34-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((34-1)/12))</f>
+        <v>4093930.3795</v>
+      </c>
+      <c r="C35" s="31" t="n">
+        <f aca="false">C34+(Engine!$B$42*(1+RateCard!$B$37)^INT((34-1)/12))</f>
+        <v>2955805.05214834</v>
       </c>
       <c r="D35" s="1" t="n">
         <f aca="false">IF(B35&gt;=C35,1,0)</f>
@@ -2356,13 +3010,13 @@
       <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="30" t="n">
-        <f aca="false">B35+(Engine!$B$5*(1+Inputs!$B$14)^INT((35-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((35-1)/12))</f>
-        <v>4252299.96158333</v>
-      </c>
-      <c r="C36" s="30" t="n">
-        <f aca="false">C35+(Engine!$B$42*1.04^INT((35-1)/12))</f>
-        <v>2983277.08302223</v>
+      <c r="B36" s="31" t="n">
+        <f aca="false">B35+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((35-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((35-1)/12))</f>
+        <v>4232850.07145</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <f aca="false">C35+(Engine!$B$42*(1+RateCard!$B$37)^INT((35-1)/12))</f>
+        <v>2973217.95241521</v>
       </c>
       <c r="D36" s="1" t="n">
         <f aca="false">IF(B36&gt;=C36,1,0)</f>
@@ -2373,13 +3027,13 @@
       <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="30" t="n">
-        <f aca="false">B36+(Engine!$B$5*(1+Inputs!$B$14)^INT((36-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((36-1)/12))</f>
-        <v>4391797.949</v>
-      </c>
-      <c r="C37" s="30" t="n">
-        <f aca="false">C36+(Engine!$B$42*1.04^INT((36-1)/12))</f>
-        <v>3000769.53693334</v>
+      <c r="B37" s="31" t="n">
+        <f aca="false">B36+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((36-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((36-1)/12))</f>
+        <v>4371769.7634</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <f aca="false">C36+(Engine!$B$42*(1+RateCard!$B$37)^INT((36-1)/12))</f>
+        <v>2990630.85268208</v>
       </c>
       <c r="D37" s="1" t="n">
         <f aca="false">IF(B37&gt;=C37,1,0)</f>
@@ -2390,13 +3044,13 @@
       <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="30" t="n">
-        <f aca="false">B37+(Engine!$B$5*(1+Inputs!$B$14)^INT((37-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((37-1)/12))</f>
-        <v>4554115.37935083</v>
-      </c>
-      <c r="C38" s="30" t="n">
-        <f aca="false">C37+(Engine!$B$42*1.04^INT((37-1)/12))</f>
-        <v>3018961.68900089</v>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((37-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((37-1)/12))</f>
+        <v>4533485.7664655</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <f aca="false">C37+(Engine!$B$42*(1+RateCard!$B$37)^INT((37-1)/12))</f>
+        <v>3008740.26895963</v>
       </c>
       <c r="D38" s="1" t="n">
         <f aca="false">IF(B38&gt;=C38,1,0)</f>
@@ -2407,13 +3061,13 @@
       <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="30" t="n">
-        <f aca="false">B38+(Engine!$B$5*(1+Inputs!$B$14)^INT((38-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((38-1)/12))</f>
-        <v>4716432.80970167</v>
-      </c>
-      <c r="C39" s="30" t="n">
-        <f aca="false">C38+(Engine!$B$42*1.04^INT((38-1)/12))</f>
-        <v>3037153.84106845</v>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B38+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((38-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((38-1)/12))</f>
+        <v>4695201.769531</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <f aca="false">C38+(Engine!$B$42*(1+RateCard!$B$37)^INT((38-1)/12))</f>
+        <v>3026849.68523718</v>
       </c>
       <c r="D39" s="1" t="n">
         <f aca="false">IF(B39&gt;=C39,1,0)</f>
@@ -2424,13 +3078,13 @@
       <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="30" t="n">
-        <f aca="false">B39+(Engine!$B$5*(1+Inputs!$B$14)^INT((39-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((39-1)/12))</f>
-        <v>4878750.2400525</v>
-      </c>
-      <c r="C40" s="30" t="n">
-        <f aca="false">C39+(Engine!$B$42*1.04^INT((39-1)/12))</f>
-        <v>3055345.993136</v>
+      <c r="B40" s="31" t="n">
+        <f aca="false">B39+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((39-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((39-1)/12))</f>
+        <v>4856917.7725965</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <f aca="false">C39+(Engine!$B$42*(1+RateCard!$B$37)^INT((39-1)/12))</f>
+        <v>3044959.10151473</v>
       </c>
       <c r="D40" s="1" t="n">
         <f aca="false">IF(B40&gt;=C40,1,0)</f>
@@ -2441,13 +3095,13 @@
       <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="30" t="n">
-        <f aca="false">B40+(Engine!$B$5*(1+Inputs!$B$14)^INT((40-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((40-1)/12))</f>
-        <v>5041067.67040333</v>
-      </c>
-      <c r="C41" s="30" t="n">
-        <f aca="false">C40+(Engine!$B$42*1.04^INT((40-1)/12))</f>
-        <v>3073538.14520356</v>
+      <c r="B41" s="31" t="n">
+        <f aca="false">B40+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((40-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((40-1)/12))</f>
+        <v>5018633.775662</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <f aca="false">C40+(Engine!$B$42*(1+RateCard!$B$37)^INT((40-1)/12))</f>
+        <v>3063068.51779227</v>
       </c>
       <c r="D41" s="1" t="n">
         <f aca="false">IF(B41&gt;=C41,1,0)</f>
@@ -2458,13 +3112,13 @@
       <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="30" t="n">
-        <f aca="false">B41+(Engine!$B$5*(1+Inputs!$B$14)^INT((41-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((41-1)/12))</f>
-        <v>5203385.10075417</v>
-      </c>
-      <c r="C42" s="30" t="n">
-        <f aca="false">C41+(Engine!$B$42*1.04^INT((41-1)/12))</f>
-        <v>3091730.29727111</v>
+      <c r="B42" s="31" t="n">
+        <f aca="false">B41+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((41-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((41-1)/12))</f>
+        <v>5180349.7787275</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <f aca="false">C41+(Engine!$B$42*(1+RateCard!$B$37)^INT((41-1)/12))</f>
+        <v>3081177.93406982</v>
       </c>
       <c r="D42" s="1" t="n">
         <f aca="false">IF(B42&gt;=C42,1,0)</f>
@@ -2475,13 +3129,13 @@
       <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="30" t="n">
-        <f aca="false">B42+(Engine!$B$5*(1+Inputs!$B$14)^INT((42-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((42-1)/12))</f>
-        <v>5365702.531105</v>
-      </c>
-      <c r="C43" s="30" t="n">
-        <f aca="false">C42+(Engine!$B$42*1.04^INT((42-1)/12))</f>
-        <v>3109922.44933867</v>
+      <c r="B43" s="31" t="n">
+        <f aca="false">B42+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((42-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((42-1)/12))</f>
+        <v>5342065.781793</v>
+      </c>
+      <c r="C43" s="31" t="n">
+        <f aca="false">C42+(Engine!$B$42*(1+RateCard!$B$37)^INT((42-1)/12))</f>
+        <v>3099287.35034737</v>
       </c>
       <c r="D43" s="1" t="n">
         <f aca="false">IF(B43&gt;=C43,1,0)</f>
@@ -2492,13 +3146,13 @@
       <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="30" t="n">
-        <f aca="false">B43+(Engine!$B$5*(1+Inputs!$B$14)^INT((43-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((43-1)/12))</f>
-        <v>5528019.96145583</v>
-      </c>
-      <c r="C44" s="30" t="n">
-        <f aca="false">C43+(Engine!$B$42*1.04^INT((43-1)/12))</f>
-        <v>3128114.60140623</v>
+      <c r="B44" s="31" t="n">
+        <f aca="false">B43+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((43-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((43-1)/12))</f>
+        <v>5503781.7848585</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <f aca="false">C43+(Engine!$B$42*(1+RateCard!$B$37)^INT((43-1)/12))</f>
+        <v>3117396.76662491</v>
       </c>
       <c r="D44" s="1" t="n">
         <f aca="false">IF(B44&gt;=C44,1,0)</f>
@@ -2509,13 +3163,13 @@
       <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="30" t="n">
-        <f aca="false">B44+(Engine!$B$5*(1+Inputs!$B$14)^INT((44-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((44-1)/12))</f>
-        <v>5690337.39180667</v>
-      </c>
-      <c r="C45" s="30" t="n">
-        <f aca="false">C44+(Engine!$B$42*1.04^INT((44-1)/12))</f>
-        <v>3146306.75347378</v>
+      <c r="B45" s="31" t="n">
+        <f aca="false">B44+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((44-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((44-1)/12))</f>
+        <v>5665497.787924</v>
+      </c>
+      <c r="C45" s="31" t="n">
+        <f aca="false">C44+(Engine!$B$42*(1+RateCard!$B$37)^INT((44-1)/12))</f>
+        <v>3135506.18290246</v>
       </c>
       <c r="D45" s="1" t="n">
         <f aca="false">IF(B45&gt;=C45,1,0)</f>
@@ -2526,13 +3180,13 @@
       <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="30" t="n">
-        <f aca="false">B45+(Engine!$B$5*(1+Inputs!$B$14)^INT((45-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((45-1)/12))</f>
-        <v>5852654.8221575</v>
-      </c>
-      <c r="C46" s="30" t="n">
-        <f aca="false">C45+(Engine!$B$42*1.04^INT((45-1)/12))</f>
-        <v>3164498.90554134</v>
+      <c r="B46" s="31" t="n">
+        <f aca="false">B45+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((45-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((45-1)/12))</f>
+        <v>5827213.7909895</v>
+      </c>
+      <c r="C46" s="31" t="n">
+        <f aca="false">C45+(Engine!$B$42*(1+RateCard!$B$37)^INT((45-1)/12))</f>
+        <v>3153615.59918001</v>
       </c>
       <c r="D46" s="1" t="n">
         <f aca="false">IF(B46&gt;=C46,1,0)</f>
@@ -2543,13 +3197,13 @@
       <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="30" t="n">
-        <f aca="false">B46+(Engine!$B$5*(1+Inputs!$B$14)^INT((46-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((46-1)/12))</f>
-        <v>6014972.25250833</v>
-      </c>
-      <c r="C47" s="30" t="n">
-        <f aca="false">C46+(Engine!$B$42*1.04^INT((46-1)/12))</f>
-        <v>3182691.05760889</v>
+      <c r="B47" s="31" t="n">
+        <f aca="false">B46+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((46-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((46-1)/12))</f>
+        <v>5988929.794055</v>
+      </c>
+      <c r="C47" s="31" t="n">
+        <f aca="false">C46+(Engine!$B$42*(1+RateCard!$B$37)^INT((46-1)/12))</f>
+        <v>3171725.01545755</v>
       </c>
       <c r="D47" s="1" t="n">
         <f aca="false">IF(B47&gt;=C47,1,0)</f>
@@ -2560,13 +3214,13 @@
       <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="30" t="n">
-        <f aca="false">B47+(Engine!$B$5*(1+Inputs!$B$14)^INT((47-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((47-1)/12))</f>
-        <v>6177289.68285917</v>
-      </c>
-      <c r="C48" s="30" t="n">
-        <f aca="false">C47+(Engine!$B$42*1.04^INT((47-1)/12))</f>
-        <v>3200883.20967645</v>
+      <c r="B48" s="31" t="n">
+        <f aca="false">B47+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((47-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((47-1)/12))</f>
+        <v>6150645.7971205</v>
+      </c>
+      <c r="C48" s="31" t="n">
+        <f aca="false">C47+(Engine!$B$42*(1+RateCard!$B$37)^INT((47-1)/12))</f>
+        <v>3189834.4317351</v>
       </c>
       <c r="D48" s="1" t="n">
         <f aca="false">IF(B48&gt;=C48,1,0)</f>
@@ -2577,13 +3231,13 @@
       <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="30" t="n">
-        <f aca="false">B48+(Engine!$B$5*(1+Inputs!$B$14)^INT((48-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((48-1)/12))</f>
-        <v>6339607.11321</v>
-      </c>
-      <c r="C49" s="30" t="n">
-        <f aca="false">C48+(Engine!$B$42*1.04^INT((48-1)/12))</f>
-        <v>3219075.361744</v>
+      <c r="B49" s="31" t="n">
+        <f aca="false">B48+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((48-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((48-1)/12))</f>
+        <v>6312361.800186</v>
+      </c>
+      <c r="C49" s="31" t="n">
+        <f aca="false">C48+(Engine!$B$42*(1+RateCard!$B$37)^INT((48-1)/12))</f>
+        <v>3207943.84801265</v>
       </c>
       <c r="D49" s="1" t="n">
         <f aca="false">IF(B49&gt;=C49,1,0)</f>
@@ -2594,13 +3248,13 @@
       <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="30" t="n">
-        <f aca="false">B49+(Engine!$B$5*(1+Inputs!$B$14)^INT((49-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((49-1)/12))</f>
-        <v>6529966.64507174</v>
-      </c>
-      <c r="C50" s="30" t="n">
-        <f aca="false">C49+(Engine!$B$42*1.04^INT((49-1)/12))</f>
-        <v>3237995.19989426</v>
+      <c r="B50" s="31" t="n">
+        <f aca="false">B49+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((49-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((49-1)/12))</f>
+        <v>6502095.847671</v>
+      </c>
+      <c r="C50" s="31" t="n">
+        <f aca="false">C49+(Engine!$B$42*(1+RateCard!$B$37)^INT((49-1)/12))</f>
+        <v>3226777.6409413</v>
       </c>
       <c r="D50" s="1" t="n">
         <f aca="false">IF(B50&gt;=C50,1,0)</f>
@@ -2611,13 +3265,13 @@
       <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="30" t="n">
-        <f aca="false">B50+(Engine!$B$5*(1+Inputs!$B$14)^INT((50-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((50-1)/12))</f>
-        <v>6720326.17693349</v>
-      </c>
-      <c r="C51" s="30" t="n">
-        <f aca="false">C50+(Engine!$B$42*1.04^INT((50-1)/12))</f>
-        <v>3256915.03804452</v>
+      <c r="B51" s="31" t="n">
+        <f aca="false">B50+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((50-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((50-1)/12))</f>
+        <v>6691829.89515599</v>
+      </c>
+      <c r="C51" s="31" t="n">
+        <f aca="false">C50+(Engine!$B$42*(1+RateCard!$B$37)^INT((50-1)/12))</f>
+        <v>3245611.43386994</v>
       </c>
       <c r="D51" s="1" t="n">
         <f aca="false">IF(B51&gt;=C51,1,0)</f>
@@ -2628,13 +3282,13 @@
       <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="30" t="n">
-        <f aca="false">B51+(Engine!$B$5*(1+Inputs!$B$14)^INT((51-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((51-1)/12))</f>
-        <v>6910685.70879523</v>
-      </c>
-      <c r="C52" s="30" t="n">
-        <f aca="false">C51+(Engine!$B$42*1.04^INT((51-1)/12))</f>
-        <v>3275834.87619478</v>
+      <c r="B52" s="31" t="n">
+        <f aca="false">B51+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((51-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((51-1)/12))</f>
+        <v>6881563.94264099</v>
+      </c>
+      <c r="C52" s="31" t="n">
+        <f aca="false">C51+(Engine!$B$42*(1+RateCard!$B$37)^INT((51-1)/12))</f>
+        <v>3264445.22679859</v>
       </c>
       <c r="D52" s="1" t="n">
         <f aca="false">IF(B52&gt;=C52,1,0)</f>
@@ -2645,13 +3299,13 @@
       <c r="A53" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="30" t="n">
-        <f aca="false">B52+(Engine!$B$5*(1+Inputs!$B$14)^INT((52-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((52-1)/12))</f>
-        <v>7101045.24065697</v>
-      </c>
-      <c r="C53" s="30" t="n">
-        <f aca="false">C52+(Engine!$B$42*1.04^INT((52-1)/12))</f>
-        <v>3294754.71434503</v>
+      <c r="B53" s="31" t="n">
+        <f aca="false">B52+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((52-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((52-1)/12))</f>
+        <v>7071297.99012598</v>
+      </c>
+      <c r="C53" s="31" t="n">
+        <f aca="false">C52+(Engine!$B$42*(1+RateCard!$B$37)^INT((52-1)/12))</f>
+        <v>3283279.01972724</v>
       </c>
       <c r="D53" s="1" t="n">
         <f aca="false">IF(B53&gt;=C53,1,0)</f>
@@ -2662,13 +3316,13 @@
       <c r="A54" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="30" t="n">
-        <f aca="false">B53+(Engine!$B$5*(1+Inputs!$B$14)^INT((53-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((53-1)/12))</f>
-        <v>7291404.77251871</v>
-      </c>
-      <c r="C54" s="30" t="n">
-        <f aca="false">C53+(Engine!$B$42*1.04^INT((53-1)/12))</f>
-        <v>3313674.55249529</v>
+      <c r="B54" s="31" t="n">
+        <f aca="false">B53+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((53-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((53-1)/12))</f>
+        <v>7261032.03761098</v>
+      </c>
+      <c r="C54" s="31" t="n">
+        <f aca="false">C53+(Engine!$B$42*(1+RateCard!$B$37)^INT((53-1)/12))</f>
+        <v>3302112.81265589</v>
       </c>
       <c r="D54" s="1" t="n">
         <f aca="false">IF(B54&gt;=C54,1,0)</f>
@@ -2679,13 +3333,13 @@
       <c r="A55" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="30" t="n">
-        <f aca="false">B54+(Engine!$B$5*(1+Inputs!$B$14)^INT((54-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((54-1)/12))</f>
-        <v>7481764.30438045</v>
-      </c>
-      <c r="C55" s="30" t="n">
-        <f aca="false">C54+(Engine!$B$42*1.04^INT((54-1)/12))</f>
-        <v>3332594.39064555</v>
+      <c r="B55" s="31" t="n">
+        <f aca="false">B54+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((54-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((54-1)/12))</f>
+        <v>7450766.08509597</v>
+      </c>
+      <c r="C55" s="31" t="n">
+        <f aca="false">C54+(Engine!$B$42*(1+RateCard!$B$37)^INT((54-1)/12))</f>
+        <v>3320946.60558454</v>
       </c>
       <c r="D55" s="1" t="n">
         <f aca="false">IF(B55&gt;=C55,1,0)</f>
@@ -2696,13 +3350,13 @@
       <c r="A56" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="30" t="n">
-        <f aca="false">B55+(Engine!$B$5*(1+Inputs!$B$14)^INT((55-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((55-1)/12))</f>
-        <v>7672123.8362422</v>
-      </c>
-      <c r="C56" s="30" t="n">
-        <f aca="false">C55+(Engine!$B$42*1.04^INT((55-1)/12))</f>
-        <v>3351514.22879581</v>
+      <c r="B56" s="31" t="n">
+        <f aca="false">B55+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((55-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((55-1)/12))</f>
+        <v>7640500.13258097</v>
+      </c>
+      <c r="C56" s="31" t="n">
+        <f aca="false">C55+(Engine!$B$42*(1+RateCard!$B$37)^INT((55-1)/12))</f>
+        <v>3339780.39851319</v>
       </c>
       <c r="D56" s="1" t="n">
         <f aca="false">IF(B56&gt;=C56,1,0)</f>
@@ -2713,13 +3367,13 @@
       <c r="A57" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="30" t="n">
-        <f aca="false">B56+(Engine!$B$5*(1+Inputs!$B$14)^INT((56-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((56-1)/12))</f>
-        <v>7862483.36810394</v>
-      </c>
-      <c r="C57" s="30" t="n">
-        <f aca="false">C56+(Engine!$B$42*1.04^INT((56-1)/12))</f>
-        <v>3370434.06694607</v>
+      <c r="B57" s="31" t="n">
+        <f aca="false">B56+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((56-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((56-1)/12))</f>
+        <v>7830234.18006596</v>
+      </c>
+      <c r="C57" s="31" t="n">
+        <f aca="false">C56+(Engine!$B$42*(1+RateCard!$B$37)^INT((56-1)/12))</f>
+        <v>3358614.19144184</v>
       </c>
       <c r="D57" s="1" t="n">
         <f aca="false">IF(B57&gt;=C57,1,0)</f>
@@ -2730,13 +3384,13 @@
       <c r="A58" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="30" t="n">
-        <f aca="false">B57+(Engine!$B$5*(1+Inputs!$B$14)^INT((57-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((57-1)/12))</f>
-        <v>8052842.89996568</v>
-      </c>
-      <c r="C58" s="30" t="n">
-        <f aca="false">C57+(Engine!$B$42*1.04^INT((57-1)/12))</f>
-        <v>3389353.90509632</v>
+      <c r="B58" s="31" t="n">
+        <f aca="false">B57+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((57-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((57-1)/12))</f>
+        <v>8019968.22755096</v>
+      </c>
+      <c r="C58" s="31" t="n">
+        <f aca="false">C57+(Engine!$B$42*(1+RateCard!$B$37)^INT((57-1)/12))</f>
+        <v>3377447.98437049</v>
       </c>
       <c r="D58" s="1" t="n">
         <f aca="false">IF(B58&gt;=C58,1,0)</f>
@@ -2747,13 +3401,13 @@
       <c r="A59" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="30" t="n">
-        <f aca="false">B58+(Engine!$B$5*(1+Inputs!$B$14)^INT((58-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((58-1)/12))</f>
-        <v>8243202.43182742</v>
-      </c>
-      <c r="C59" s="30" t="n">
-        <f aca="false">C58+(Engine!$B$42*1.04^INT((58-1)/12))</f>
-        <v>3408273.74324658</v>
+      <c r="B59" s="31" t="n">
+        <f aca="false">B58+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((58-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((58-1)/12))</f>
+        <v>8209702.27503595</v>
+      </c>
+      <c r="C59" s="31" t="n">
+        <f aca="false">C58+(Engine!$B$42*(1+RateCard!$B$37)^INT((58-1)/12))</f>
+        <v>3396281.77729913</v>
       </c>
       <c r="D59" s="1" t="n">
         <f aca="false">IF(B59&gt;=C59,1,0)</f>
@@ -2764,13 +3418,13 @@
       <c r="A60" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="30" t="n">
-        <f aca="false">B59+(Engine!$B$5*(1+Inputs!$B$14)^INT((59-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((59-1)/12))</f>
-        <v>8433561.96368916</v>
-      </c>
-      <c r="C60" s="30" t="n">
-        <f aca="false">C59+(Engine!$B$42*1.04^INT((59-1)/12))</f>
-        <v>3427193.58139684</v>
+      <c r="B60" s="31" t="n">
+        <f aca="false">B59+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((59-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((59-1)/12))</f>
+        <v>8399436.32252095</v>
+      </c>
+      <c r="C60" s="31" t="n">
+        <f aca="false">C59+(Engine!$B$42*(1+RateCard!$B$37)^INT((59-1)/12))</f>
+        <v>3415115.57022778</v>
       </c>
       <c r="D60" s="1" t="n">
         <f aca="false">IF(B60&gt;=C60,1,0)</f>
@@ -2781,13 +3435,13 @@
       <c r="A61" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="30" t="n">
-        <f aca="false">B60+(Engine!$B$5*(1+Inputs!$B$14)^INT((60-1)/12)+(Engine!$B$25+Engine!$B$26)*1.04^INT((60-1)/12))</f>
-        <v>8623921.4955509</v>
-      </c>
-      <c r="C61" s="30" t="n">
-        <f aca="false">C60+(Engine!$B$42*1.04^INT((60-1)/12))</f>
-        <v>3446113.4195471</v>
+      <c r="B61" s="31" t="n">
+        <f aca="false">B60+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((60-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((60-1)/12))</f>
+        <v>8589170.37000595</v>
+      </c>
+      <c r="C61" s="31" t="n">
+        <f aca="false">C60+(Engine!$B$42*(1+RateCard!$B$37)^INT((60-1)/12))</f>
+        <v>3433949.36315643</v>
       </c>
       <c r="D61" s="1" t="n">
         <f aca="false">IF(B61&gt;=C61,1,0)</f>
@@ -2820,89 +3474,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>113.93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>68.36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>2.88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.05</v>
@@ -2911,18 +3565,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>189000</v>
@@ -2931,7 +3585,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>5000</v>
@@ -2940,29 +3594,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>8</v>
@@ -2971,23 +3625,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>25000</v>
@@ -2996,29 +3650,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>1200000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>100000</v>
@@ -3027,18 +3681,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>500000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>33333</v>
@@ -3047,7 +3701,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
@@ -3056,29 +3710,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>3000</v>
@@ -3087,7 +3741,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>2000</v>
@@ -3096,7 +3750,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
@@ -3105,7 +3759,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>189000</v>
@@ -3114,40 +3768,40 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>11387</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>730</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>0.04</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -3162,6 +3816,158 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>113.93</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3179,47 +3985,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>8</v>
@@ -3246,15 +4052,15 @@
         <v>2</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>8</v>
@@ -3281,15 +4087,15 @@
         <v>2</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>8</v>
@@ -3316,15 +4122,15 @@
         <v>2</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>72</v>
@@ -3351,174 +4157,35 @@
         <v>1</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="70"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C4" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3537,7 +4204,146 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="70"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56"/>
@@ -3547,309 +4353,320 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>105079</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>0.85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B24" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B25" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B26" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="3" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>100000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B37" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>169</v>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation allowBlank="true" error="Must be zero or positive" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4 B11 B16 B21 B33:B35" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -3866,552 +4683,11 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
+    <dataValidation allowBlank="false" error="Auto or Known" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B38" type="list">
+      <formula1>"Auto,Known"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C60"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="23" t="n">
-        <f aca="false">(Inputs!$B$10*(RateCard!$B$4+RateCard!$B$6)+(1-Inputs!$B$10)*(RateCard!$B$5+RateCard!$B$7))*(1+RateCard!$B$15)</f>
-        <v>71.24</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="24" t="n">
-        <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
-        <v>52539.5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B6" s="25" t="n">
-        <f aca="false">B5/B4</f>
-        <v>737.5</v>
-      </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*RateCard!$B$16)</f>
-        <v>5900</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="26" t="n">
-        <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
-        <v>2.83870967741935</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="26" t="n">
-        <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
-        <v>4.79741935483871</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B12" s="25" t="n">
-        <f aca="false">B7/B11</f>
-        <v>1229.82786444325</v>
-      </c>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B13" s="25" t="n">
-        <f aca="false">B7</f>
-        <v>5900</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="25" t="n">
-        <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
-        <v>8</v>
-      </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="25" t="n">
-        <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
-        <v>4964</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B18" s="25" t="n">
-        <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
-        <v>1</v>
-      </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B19" s="25" t="n">
-        <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
-        <v>2</v>
-      </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B20" s="27" t="n">
-        <f aca="false">1-B12/((B18-Inputs!$B$36)*B17)</f>
-        <v>0.752250631659297</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B23" s="28" t="n">
-        <f aca="false">Inputs!$B$11*Inputs!$B$12</f>
-        <v>0.25</v>
-      </c>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B24" s="28" t="n">
-        <f aca="false">Inputs!$B$11*(1-Inputs!$B$12)</f>
-        <v>0.75</v>
-      </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B25" s="24" t="n">
-        <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+Inputs!$B$11*1000000*RateCard!$B$11*RateCard!$B$10</f>
-        <v>52500</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B26" s="24" t="n">
-        <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
-        <v>574.166666666667</v>
-      </c>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B29" s="24" t="n">
-        <f aca="false">IF(OR(INDEX(Hardware!$J$3:$J$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;&gt;"YES",INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))=0),NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
-        <v>744793</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B30" s="25" t="n">
-        <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B31" s="24" t="n">
-        <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
-        <v>1359793</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B32" s="24" t="n">
-        <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
-        <v>675000</v>
-      </c>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B33" s="24" t="n">
-        <f aca="false">B31+B32</f>
-        <v>2034793</v>
-      </c>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B34" s="28" t="n">
-        <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
-        <v>14.4</v>
-      </c>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B35" s="24" t="n">
-        <f aca="false">(B18*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16</f>
-        <v>7320</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B36" s="28" t="n">
-        <f aca="false">B30+Inputs!$B$11*RateCard!$B$27</f>
-        <v>2</v>
-      </c>
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B37" s="24" t="n">
-        <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/36</f>
-        <v>3111.11111111111</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B38" s="24" t="n">
-        <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
-        <v>1575</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B39" s="24" t="n">
-        <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
-        <v>4166.64583333333</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B40" s="24" t="n">
-        <f aca="false">B35+B37+B38+B39</f>
-        <v>16172.7569444444</v>
-      </c>
-      <c r="C40" s="3"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B41" s="24" t="n">
-        <f aca="false">B18*RateCard!$B$33+B39</f>
-        <v>15553.6458333333</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B42" s="24" t="n">
-        <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
-        <v>16172.7569444444</v>
-      </c>
-      <c r="C42" s="3"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B45" s="24" t="n">
-        <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
-        <v>2779586</v>
-      </c>
-      <c r="C45" s="3"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B46" s="24" t="n">
-        <f aca="false">(B19*B34+Inputs!$B$11*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+Inputs!$B$11*RateCard!$B$27)/36+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
-        <v>22067.7569444444</v>
-      </c>
-      <c r="C46" s="3"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B47" s="24" t="n">
-        <f aca="false">B19*RateCard!$B$33+B39</f>
-        <v>26940.6458333333</v>
-      </c>
-      <c r="C47" s="3"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B48" s="24" t="n">
-        <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
-        <v>22067.7569444444</v>
-      </c>
-      <c r="C48" s="3"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B51" s="24" t="str">
-        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
-        <v>not entered</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B52" s="24" t="str">
-        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
-        <v>not entered</v>
-      </c>
-      <c r="C52" s="3"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B54" s="24" t="n">
-        <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+Inputs!$B$11*1000000*RateCard!$B$10</f>
-        <v>360158</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B55" s="24" t="n">
-        <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
-        <v>187798.95</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B56" s="24" t="n">
-        <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
-        <v>274347.9</v>
-      </c>
-      <c r="C56" s="3"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B58" s="24" t="n">
-        <f aca="false">Engine!$B$25+Engine!$B$26</f>
-        <v>53074.1666666667</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B59" s="24" t="n">
-        <f aca="false">Inputs!$B$4*(1-Inputs!$B$13)</f>
-        <v>52539.5</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B60" s="4" t="str">
-        <f aca="false">IF(B58&gt;B59*1.02,"⚠ OVERALLOCATED: reconstructed storage+egress+admin exceed the stated non-compute budget by $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo — reduce storage PB or raise the bill",IF(B58&lt;B59*0.98,"ℹ UNALLOCATED: $"&amp;TEXT(B59-B58,"#,##0")&amp;"/mo of the stated bill is not explained by entered components (PaaS, other services?)","OK — within 2% tolerance (difference $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo)"))</f>
-        <v>OK — within 2% tolerance (difference $535/mo)</v>
-      </c>
-    </row>
-  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4427,373 +4703,551 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>243</v>
+        <v>190</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>244</v>
+      <c r="A4" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="23" t="n">
+        <f aca="false">(Inputs!$B$10*(INDEX(CloudRates!$C$3:$C$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$6)+(1-Inputs!$B$10)*(INDEX(CloudRates!$D$3:$D$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$7))*(1+RateCard!$B$15)</f>
+        <v>35.9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>249</v>
+      <c r="A5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
+        <v>52539.5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
-        <v>1260948</v>
-      </c>
-      <c r="C6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^1+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^1)</f>
-        <v>1443785.46</v>
-      </c>
-      <c r="D6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^2+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^2)</f>
-        <v>1667036.3034</v>
-      </c>
-      <c r="E6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^3+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^3)</f>
-        <v>1940592.036786</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^4+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^4)</f>
-        <v>2276808.56981994</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B6" s="25" t="n">
+        <f aca="false">B5/B4</f>
+        <v>1463.49582172702</v>
+      </c>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
-        <v>194073.083333333</v>
-      </c>
-      <c r="C7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^1</f>
-        <v>201836.006666667</v>
-      </c>
-      <c r="D7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^2</f>
-        <v>209909.446933333</v>
-      </c>
-      <c r="E7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^3</f>
-        <v>218305.824810667</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^4</f>
-        <v>227038.057803093</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
-        <v>264813.083333333</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^1</f>
-        <v>275405.606666667</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^2</f>
-        <v>286421.830933333</v>
-      </c>
-      <c r="E8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^3</f>
-        <v>297878.704170667</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^4</f>
-        <v>309793.852337493</v>
+        <v>198</v>
+      </c>
+      <c r="B7" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*RateCard!$B$16)</f>
+        <v>11707.9665738162</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>253</v>
+      <c r="A10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="26" t="n">
+        <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
+        <v>2.83870967741935</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>256</v>
+      <c r="A11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="26" t="n">
+        <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
+        <v>4.79741935483871</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B12" s="24" t="n">
-        <f aca="false">SUM($B$6:B6)</f>
-        <v>1260948</v>
-      </c>
-      <c r="C12" s="24" t="n">
-        <f aca="false">SUM($B$6:D6)</f>
-        <v>4371769.7634</v>
-      </c>
-      <c r="D12" s="24" t="n">
-        <f aca="false">SUM($B$6:F6)</f>
-        <v>8589170.37000594</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <f aca="false">B7/B11</f>
+        <v>2440.47178448293</v>
+      </c>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B13" s="24" t="n">
-        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)</f>
-        <v>2401225.13333333</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7)</f>
-        <v>2812970.58693333</v>
-      </c>
-      <c r="D13" s="24" t="n">
-        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7)</f>
-        <v>3258314.46954709</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B14" s="24" t="n">
-        <f aca="false">B12-B13</f>
-        <v>-1140277.13333333</v>
-      </c>
-      <c r="C14" s="24" t="n">
-        <f aca="false">C12-C13</f>
-        <v>1558799.17646667</v>
-      </c>
-      <c r="D14" s="24" t="n">
-        <f aca="false">D12-D13</f>
-        <v>5330855.90045885</v>
+        <v>206</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <f aca="false">B7</f>
+        <v>11707.9665738162</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B15" s="27" t="n">
-        <f aca="false">B14/B12</f>
-        <v>-0.904301472648621</v>
-      </c>
-      <c r="C15" s="27" t="n">
-        <f aca="false">C14/C12</f>
-        <v>0.356560217218384</v>
-      </c>
-      <c r="D15" s="27" t="n">
-        <f aca="false">D14/D12</f>
-        <v>0.620648522594757</v>
+      <c r="A15" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B16" s="24" t="n">
-        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)</f>
-        <v>3130209.18333333</v>
-      </c>
-      <c r="C16" s="24" t="n">
-        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8)</f>
-        <v>3692036.62093333</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8)</f>
-        <v>4299709.17744149</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="B16" s="25" t="n">
+        <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
+        <v>8</v>
+      </c>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B17" s="24" t="n">
-        <f aca="false">B12-B16</f>
-        <v>-1869261.18333333</v>
-      </c>
-      <c r="C17" s="24" t="n">
-        <f aca="false">C12-C16</f>
-        <v>679733.142466666</v>
-      </c>
-      <c r="D17" s="24" t="n">
-        <f aca="false">D12-D16</f>
-        <v>4289461.19256445</v>
+      <c r="A17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" s="25" t="n">
+        <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
+        <v>4964</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B18" s="27" t="n">
-        <f aca="false">B17/B12</f>
-        <v>-1.48242527315427</v>
-      </c>
-      <c r="C18" s="27" t="n">
-        <f aca="false">C17/C12</f>
-        <v>0.155482374245168</v>
-      </c>
-      <c r="D18" s="27" t="n">
-        <f aca="false">D17/D12</f>
-        <v>0.499403435696605</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="B18" s="25" t="n">
+        <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
+        <v>3</v>
+      </c>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B21" s="29" t="str">
-        <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
-        <v>1 / 2</v>
+      <c r="A20" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" s="27" t="n">
+        <f aca="false">1-B12/((B18-Inputs!$B$36)*B17)</f>
+        <v>0.508365877420845</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B22" s="24" t="n">
-        <f aca="false">Engine!$B$33</f>
-        <v>2034793</v>
+      <c r="A22" s="6" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17),"0.0%")</f>
-        <v>75.2% / 40.6%</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="B23" s="28" t="n">
+        <f aca="false">B62*Inputs!$B$12</f>
+        <v>0.247453968253968</v>
+      </c>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B24" s="28" t="str">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
-        <v>6.3 / 2.3</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="B24" s="28" t="n">
+        <f aca="false">B62*(1-Inputs!$B$12)</f>
+        <v>0.742361904761905</v>
+      </c>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="B25" s="24" t="n">
-        <f aca="false">Engine!$B$25</f>
-        <v>52500</v>
+        <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+B62*1000000*RateCard!$B$11*RateCard!$B$10</f>
+        <v>51965.3333333333</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B26" s="28" t="str">
-        <f aca="false">IFERROR("Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),"no crossover within 60 months under the modeled trajectory")</f>
-        <v>Month 25</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B27" s="24" t="str">
-        <f aca="false">Engine!$B$51</f>
+        <v>221</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
+        <v>574.166666666667</v>
+      </c>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <f aca="false">IF(OR(INDEX(Hardware!$J$3:$J$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;&gt;"YES",INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))=0),NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
+        <v>744793</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B30" s="25" t="n">
+        <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="24" t="n">
+        <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
+        <v>1359793</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" s="24" t="n">
+        <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
+        <v>668125.714285714</v>
+      </c>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" s="24" t="n">
+        <f aca="false">B31+B32</f>
+        <v>2027918.71428571</v>
+      </c>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B34" s="28" t="n">
+        <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
+        <v>14.4</v>
+      </c>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="24" t="n">
+        <f aca="false">(B18*B34+B62*RateCard!$B$26)*Inputs!$B$16</f>
+        <v>7289.44761904762</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B36" s="28" t="n">
+        <f aca="false">B30+B62*RateCard!$B$27</f>
+        <v>1.98981587301587</v>
+      </c>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/36</f>
+        <v>3110.54532627866</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" s="24" t="n">
+        <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
+        <v>1575</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B39" s="24" t="n">
+        <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
+        <v>4124.21218306878</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" s="24" t="n">
+        <f aca="false">B35+B37+B38+B39</f>
+        <v>16099.2051283951</v>
+      </c>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="24" t="n">
+        <f aca="false">B18*RateCard!$B$33+B39</f>
+        <v>15511.2121830688</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
+        <v>16099.2051283951</v>
+      </c>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
+        <v>3532504.71428571</v>
+      </c>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B46" s="24" t="n">
+        <f aca="false">(B19*B34+B62*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+B62*RateCard!$B$27)/36+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
+        <v>27944.7606839506</v>
+      </c>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B47" s="24" t="n">
+        <f aca="false">B19*RateCard!$B$33+B39</f>
+        <v>38285.2121830688</v>
+      </c>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B48" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
+        <v>27944.7606839506</v>
+      </c>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B51" s="24" t="str">
+        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
         <v>not entered</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B28" s="24" t="n">
-        <f aca="false">Engine!$B$54</f>
-        <v>360158</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B29" s="24" t="n">
-        <f aca="false">Engine!$B$55</f>
-        <v>187798.95</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B30" s="28" t="n">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
-        <v>2.3321610412924</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B32" s="1" t="str">
-        <f aca="false">Engine!$B$60</f>
-        <v>OK — within 2% tolerance (difference $535/mo)</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B33" s="28" t="n">
-        <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"n/a (opex exceeds bill)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42))</f>
-        <v>26.9379395382105</v>
+      <c r="C51" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B52" s="24" t="str">
+        <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
+        <v>not entered</v>
+      </c>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B54" s="24" t="n">
+        <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+B62*1000000*RateCard!$B$10</f>
+        <v>359648.793650794</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B55" s="24" t="n">
+        <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
+        <v>186767.807142857</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B56" s="24" t="n">
+        <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
+        <v>359865.707142857</v>
+      </c>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B58" s="24" t="n">
+        <f aca="false">Engine!$B$25+Engine!$B$26</f>
+        <v>52539.5</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B59" s="24" t="n">
+        <f aca="false">Inputs!$B$4*(1-Inputs!$B$13)</f>
+        <v>52539.5</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B60" s="4" t="str">
+        <f aca="false">IF(B58&gt;B59*1.02,"⚠ OVERALLOCATED: reconstructed storage+egress+admin exceed the stated non-compute budget by $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo — reduce storage PB or raise the bill",IF(B58&lt;B59*0.98,"ℹ UNALLOCATED: $"&amp;TEXT(B59-B58,"#,##0")&amp;"/mo of the stated bill is not explained by entered components (PaaS, other services?)","OK — within 2% tolerance (difference $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo)"))</f>
+        <v>OK — within 2% tolerance (difference $0/mo)</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B61" s="29" t="n">
+        <f aca="false">MAX(0,(Inputs!$B$4*(1-Inputs!$B$13)-B26)/(Inputs!$B$12*1000000*RateCard!$B$8+(1-Inputs!$B$12)*1000000*RateCard!$B$9+1000000*RateCard!$B$11*RateCard!$B$10))</f>
+        <v>0.989815873015873</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B62" s="29" t="n">
+        <f aca="false">IF(Inputs!$B$38="Auto",B61,Inputs!$B$11)</f>
+        <v>0.989815873015873</v>
       </c>
     </row>
   </sheetData>
@@ -4812,296 +5266,373 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>281</v>
+      <c r="A4" s="6" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="25" t="n">
-        <f aca="false">8*RateCard!$B$36</f>
-        <v>5840</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>5840</v>
-      </c>
-      <c r="D5" s="4" t="str">
-        <f aca="false">IF(ABS(B5-C5)/C5&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B6" s="24" t="n">
-        <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
-        <v>52005.2</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>52005</v>
-      </c>
-      <c r="D6" s="4" t="str">
-        <f aca="false">IF(ABS(B6-C6)/C6&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
+        <v>1260948</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^1+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^1)</f>
+        <v>1443785.46</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^2+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^2)</f>
+        <v>1667036.3034</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^3+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^3)</f>
+        <v>1940592.036786</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^4+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^4)</f>
+        <v>2276808.56981994</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B7" s="24" t="n">
-        <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
-        <v>52500</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>52500</v>
-      </c>
-      <c r="D7" s="4" t="str">
-        <f aca="false">IF(ABS(B7-C7)/C7&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
+        <v>193190.461540741</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^1</f>
+        <v>200918.08000237</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^2</f>
+        <v>208954.803202465</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^3</f>
+        <v>217312.995330564</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^4</f>
+        <v>226005.515143786</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B8" s="24" t="n">
-        <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
-        <v>574.166666666667</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>574</v>
-      </c>
-      <c r="D8" s="4" t="str">
-        <f aca="false">IF(ABS(B8-C8)/C8&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B9" s="24" t="n">
-        <f aca="false">B6+B7+B8</f>
-        <v>105079.366666667</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>105079</v>
-      </c>
-      <c r="D9" s="4" t="str">
-        <f aca="false">IF(ABS(B9-C9)/C9&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
+        <v>335337.128207407</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^1</f>
+        <v>348750.613335704</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^2</f>
+        <v>362700.637869132</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^3</f>
+        <v>377208.663383897</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^4</f>
+        <v>392297.009919253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B10" s="24" t="n">
-        <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
-        <v>1359793</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>1359793</v>
-      </c>
-      <c r="D10" s="4" t="str">
-        <f aca="false">IF(ABS(B10-C10)/C10&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+      <c r="A10" s="6" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="24" t="n">
-        <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
-        <v>675000</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>675000</v>
-      </c>
-      <c r="D11" s="4" t="str">
-        <f aca="false">IF(ABS(B11-C11)/C11&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="B12" s="24" t="n">
-        <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
-        <v>4166.64583333333</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>4167</v>
-      </c>
-      <c r="D12" s="4" t="str">
-        <f aca="false">IF(ABS(B12-C12)/C12&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">SUM($B$6:B6)</f>
+        <v>1260948</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <f aca="false">SUM($B$6:D6)</f>
+        <v>4371769.7634</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <f aca="false">SUM($B$6:F6)</f>
+        <v>8589170.37000594</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B13" s="24" t="n">
-        <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
-        <v>7320</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>7320</v>
-      </c>
-      <c r="D13" s="4" t="str">
-        <f aca="false">IF(ABS(B13-C13)/C13&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)</f>
+        <v>2393990.16233439</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7)</f>
+        <v>2803863.04553923</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7)</f>
+        <v>3247181.55601358</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>291</v>
+      <c r="A14" s="4" t="s">
+        <v>281</v>
       </c>
       <c r="B14" s="24" t="n">
-        <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
-        <v>3097.22222222222</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>3097</v>
-      </c>
-      <c r="D14" s="4" t="str">
-        <f aca="false">IF(ABS(B14-C14)/C14&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">B12-B13</f>
+        <v>-1133042.16233439</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <f aca="false">C12-C13</f>
+        <v>1567906.71786077</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <f aca="false">D12-D13</f>
+        <v>5341988.81399236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B15" s="24" t="n">
-        <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
-        <v>1575</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>1575</v>
-      </c>
-      <c r="D15" s="4" t="str">
-        <f aca="false">IF(ABS(B15-C15)/C15&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>282</v>
+      </c>
+      <c r="B15" s="27" t="n">
+        <f aca="false">B14/B12</f>
+        <v>-0.898563749127158</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <f aca="false">C14/C12</f>
+        <v>0.358643479120773</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <f aca="false">D14/D12</f>
+        <v>0.621944679622028</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B16" s="24" t="n">
-        <f aca="false">B13+B14+B15</f>
-        <v>11992.2222222222</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>11992</v>
-      </c>
-      <c r="D16" s="4" t="str">
-        <f aca="false">IF(ABS(B16-C16)/C16&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)</f>
+        <v>3867624.92900106</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8)</f>
+        <v>4579076.1802059</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8)</f>
+        <v>5348581.85350904</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>294</v>
+      <c r="A17" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="B17" s="24" t="n">
-        <f aca="false">1*RateCard!$B$33</f>
-        <v>11387</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>11387</v>
-      </c>
-      <c r="D17" s="4" t="str">
-        <f aca="false">IF(ABS(B17-C17)/C17&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <f aca="false">B12-B16</f>
+        <v>-2606676.92900106</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <f aca="false">C12-C16</f>
+        <v>-207306.416805895</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <f aca="false">D12-D16</f>
+        <v>3240588.5164969</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <f aca="false">B17/B12</f>
+        <v>-2.0672358646043</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <f aca="false">C17/C12</f>
+        <v>-0.0474193354237094</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">D17/D12</f>
+        <v>0.377287721269715</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B21" s="30" t="str">
+        <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
+        <v>1 / 3</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <f aca="false">Engine!$B$33</f>
+        <v>2027918.71428571</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17),"0.0%")</f>
+        <v>50.8% / 21.4%</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B24" s="28" t="str">
+        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
+        <v>3.2 / 1.1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <f aca="false">Engine!$B$25</f>
+        <v>51965.3333333333</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B26" s="28" t="str">
+        <f aca="false">IF(ISNA(MATCH(1,Crossover!$D$2:$D$61,0)),"no crossover within 60 months under the modeled trajectory",IF(Inputs!$B$14=0,"Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),IF(MATCH(1,Crossover!$D$2:$D$61,0)&gt;12*LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"crossover cannot be determined in the workbook — additional capacity is required before breakeven; use the dynamic web model","Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0))))</f>
+        <v>Month 25</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B27" s="24" t="str">
+        <f aca="false">Engine!$B$51</f>
+        <v>not entered</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <f aca="false">Engine!$B$54</f>
+        <v>359648.793650794</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <f aca="false">Engine!$B$55</f>
+        <v>186767.807142857</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B30" s="28" t="n">
+        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
+        <v>1.0780264128397</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B18" s="24" t="n">
-        <f aca="false">B10*0.0281</f>
-        <v>38210.1833</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>38210</v>
-      </c>
-      <c r="D18" s="4" t="str">
-        <f aca="false">IF(ABS(B18-C18)/C18&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B19" s="24" t="n">
-        <f aca="false">B11*0.0281+B12</f>
-        <v>23134.1458333333</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>23135</v>
-      </c>
-      <c r="D19" s="4" t="str">
-        <f aca="false">IF(ABS(B19-C19)/C19&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="B32" s="1" t="str">
+        <f aca="false">Engine!$B$60</f>
+        <v>OK — within 2% tolerance (difference $0/mo)</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="24" t="n">
-        <f aca="false">B18+B19+B16</f>
-        <v>73336.5513555556</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>73337</v>
-      </c>
-      <c r="D20" s="4" t="str">
-        <f aca="false">IF(ABS(B20-C20)/C20&lt;0.01,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>298</v>
+      <c r="B33" s="28" t="n">
+        <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"n/a (opex exceeds bill)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42))</f>
+        <v>26.8326928757444</v>
       </c>
     </row>
   </sheetData>
@@ -5120,478 +5651,301 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>301</v>
       </c>
+      <c r="C4" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B5" s="14" t="n">
+      <c r="A5" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B5" s="25" t="n">
+        <f aca="false">8*RateCard!$B$36</f>
+        <v>5840</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D5" s="4" t="str">
+        <f aca="false">IF(ABS(B5-C5)&lt;=MAX(1,0.0001*ABS(C5)),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
+        <v>52005.2</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>52005</v>
+      </c>
+      <c r="D6" s="4" t="str">
+        <f aca="false">IF(ABS(B6-C6)&lt;=MAX(1,0.0001*ABS(C6)),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
+        <v>52500</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>52500</v>
+      </c>
+      <c r="D7" s="4" t="str">
+        <f aca="false">IF(ABS(B7-C7)&lt;=MAX(1,0.0001*ABS(C7)),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
+        <v>574.166666666667</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>574</v>
+      </c>
+      <c r="D8" s="4" t="str">
+        <f aca="false">IF(ABS(B8-C8)&lt;=MAX(1,0.0001*ABS(C8)),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <f aca="false">B6+B7+B8</f>
+        <v>105079.366666667</v>
+      </c>
+      <c r="C9" s="9" t="n">
         <v>105079</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>0.49491</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>0</v>
+      <c r="D9" s="4" t="str">
+        <f aca="false">IF(ABS(B9-C9)&lt;=MAX(1,0.0001*ABS(C9)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>1</v>
+      <c r="A10" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
+        <v>1359793</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1359793</v>
+      </c>
+      <c r="D10" s="4" t="str">
+        <f aca="false">IF(ABS(B10-C10)&lt;=MAX(1,0.0001*ABS(C10)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>0.25</v>
+      <c r="A11" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
+        <v>675000</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>675000</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f aca="false">IF(ABS(B11-C11)&lt;=MAX(1,0.0001*ABS(C11)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>0</v>
+      <c r="A12" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
+        <v>4166.64583333333</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>4167</v>
+      </c>
+      <c r="D12" s="4" t="str">
+        <f aca="false">IF(ABS(B12-C12)&lt;=MAX(1,0.0001*ABS(C12)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>136</v>
+      <c r="A13" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
+        <v>7320</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>7320</v>
+      </c>
+      <c r="D13" s="4" t="str">
+        <f aca="false">IF(ABS(B13-C13)&lt;=MAX(1,0.0001*ABS(C13)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>300</v>
+      <c r="A14" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
+        <v>3097.22222222222</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>3097</v>
+      </c>
+      <c r="D14" s="4" t="str">
+        <f aca="false">IF(ABS(B14-C14)&lt;=MAX(1,0.0001*ABS(C14)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>1</v>
+      <c r="A15" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
+        <v>1575</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>1575</v>
+      </c>
+      <c r="D15" s="4" t="str">
+        <f aca="false">IF(ABS(B15-C15)&lt;=MAX(1,0.0001*ABS(C15)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>87</v>
+      <c r="A16" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <f aca="false">B13+B14+B15</f>
+        <v>11992.2222222222</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>11992</v>
+      </c>
+      <c r="D16" s="4" t="str">
+        <f aca="false">IF(ABS(B16-C16)&lt;=MAX(1,0.0001*ABS(C16)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>0</v>
+      <c r="A17" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <f aca="false">1*RateCard!$B$33</f>
+        <v>11387</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>11387</v>
+      </c>
+      <c r="D17" s="4" t="str">
+        <f aca="false">IF(ABS(B17-C17)&lt;=MAX(1,0.0001*ABS(C17)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>316</v>
+      <c r="A18" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <f aca="false">B10*0.0281</f>
+        <v>38210.1833</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>38210</v>
+      </c>
+      <c r="D18" s="4" t="str">
+        <f aca="false">IF(ABS(B18-C18)&lt;=MAX(1,0.0001*ABS(C18)),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="3" t="s">
         <v>318</v>
       </c>
+      <c r="B19" s="24" t="n">
+        <f aca="false">B11*0.0281+B12</f>
+        <v>23134.1458333333</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>23135</v>
+      </c>
+      <c r="D19" s="4" t="str">
+        <f aca="false">IF(ABS(B19-C19)&lt;=MAX(1,0.0001*ABS(C19)),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <f aca="false">B18+B19+B16</f>
+        <v>73336.5513555556</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>73337</v>
+      </c>
+      <c r="D20" s="4" t="str">
+        <f aca="false">IF(ABS(B20-C20)&lt;=MAX(1,0.0001*ABS(C20)),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B21" s="29" t="str">
-        <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200/B300-class",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS"),"YES","NO — set fixture first")</f>
-        <v>NO — set fixture first</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A21" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B23" s="5" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B24" s="25" t="n">
-        <f aca="false">Engine!$B$7</f>
-        <v>5900</v>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>5840</v>
-      </c>
-      <c r="D24" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B24-C24)&lt;=MAX(1,0.0001*MAX(ABS(C24),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B25" s="23" t="n">
-        <f aca="false">Engine!$B$4</f>
-        <v>71.24</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>71.24</v>
-      </c>
-      <c r="D25" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B25-C25)&lt;=MAX(1,0.0001*MAX(ABS(C25),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B26" s="26" t="n">
-        <f aca="false">Engine!$B$11</f>
-        <v>4.79741935483871</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B26-C26)&lt;=MAX(1,0.0001*MAX(ABS(C26),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B27" s="25" t="n">
-        <f aca="false">Engine!$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B27-C27)&lt;=MAX(1,0.0001*MAX(ABS(C27),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B28" s="25" t="n">
-        <f aca="false">Engine!$B$19</f>
-        <v>2</v>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B28-C28)&lt;=MAX(1,0.0001*MAX(ABS(C28),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B29" s="24" t="n">
-        <f aca="false">Engine!$B$31</f>
-        <v>1359793</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>1359793</v>
-      </c>
-      <c r="D29" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B29-C29)&lt;=MAX(1,0.0001*MAX(ABS(C29),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B30" s="24" t="n">
-        <f aca="false">Engine!$B$32</f>
-        <v>675000</v>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>675000</v>
-      </c>
-      <c r="D30" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B30-C30)&lt;=MAX(1,0.0001*MAX(ABS(C30),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B31" s="24" t="n">
-        <f aca="false">Engine!$B$39</f>
-        <v>4166.64583333333</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>4167</v>
-      </c>
-      <c r="D31" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B31-C31)&lt;=MAX(1,0.0001*MAX(ABS(C31),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B32" s="24" t="n">
-        <f aca="false">Engine!$B$35</f>
-        <v>7320</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>7320</v>
-      </c>
-      <c r="D32" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B32-C32)&lt;=MAX(1,0.0001*MAX(ABS(C32),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B33" s="24" t="n">
-        <f aca="false">Engine!$B$37</f>
-        <v>3111.11111111111</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>3111</v>
-      </c>
-      <c r="D33" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B33-C33)&lt;=MAX(1,0.0001*MAX(ABS(C33),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B34" s="24" t="n">
-        <f aca="false">Engine!$B$38</f>
-        <v>1575</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>1575</v>
-      </c>
-      <c r="D34" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B34-C34)&lt;=MAX(1,0.0001*MAX(ABS(C34),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B35" s="24" t="n">
-        <f aca="false">Engine!$B$42</f>
-        <v>16172.7569444444</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>16173</v>
-      </c>
-      <c r="D35" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B35-C35)&lt;=MAX(1,0.0001*MAX(ABS(C35),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B36" s="24" t="n">
-        <f aca="false">Engine!$B$54</f>
-        <v>360158</v>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D36" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B36-C36)&lt;=MAX(1,0.0001*MAX(ABS(C36),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B37" s="24" t="n">
-        <f aca="false">Engine!$B$55</f>
-        <v>187798.95</v>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B37-C37)&lt;=MAX(1,0.0001*MAX(ABS(C37),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B38" s="24" t="n">
-        <f aca="false">Engine!$B$25</f>
-        <v>52500</v>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>52500</v>
-      </c>
-      <c r="D38" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B38-C38)&lt;=MAX(1,0.0001*MAX(ABS(C38),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B39" s="24" t="n">
-        <f aca="false">Engine!$B$26</f>
-        <v>574.166666666667</v>
-      </c>
-      <c r="C39" s="9" t="n">
-        <v>574</v>
-      </c>
-      <c r="D39" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B39-C39)&lt;=MAX(1,0.0001*MAX(ABS(C39),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B40" s="24" t="n">
-        <f aca="false">Engine!$B$5+Engine!$B$25+Engine!$B$26</f>
-        <v>105613.666666667</v>
-      </c>
-      <c r="C40" s="9" t="n">
-        <v>105079</v>
-      </c>
-      <c r="D40" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B40-C40)&lt;=MAX(1,0.0001*MAX(ABS(C40),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B41" s="24" t="n">
-        <f aca="false">Engine!$B$41</f>
-        <v>15553.6458333333</v>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>15554</v>
-      </c>
-      <c r="D41" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(ABS(B41-C41)&lt;=MAX(1,0.0001*MAX(ABS(C41),1)),"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B42" s="29" t="str">
-        <f aca="false">Engine!$B$51</f>
-        <v>not entered</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="D42" s="4" t="str">
-        <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B42=C42,"PASS","FAIL"))</f>
-        <v>FIXTURE NOT LOADED</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reverse-tco-model-v1.xlsx
+++ b/docs/reverse-tco-model-v1.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="387">
   <si>
     <t xml:space="preserve">Reverse TCO Tool v1 — Cloud AIaaS Spend to On-Prem NVIDIA Infrastructure</t>
   </si>
@@ -107,6 +107,9 @@
     <t xml:space="preserve">V2.3 (audit round 5): CloudRates sheet — blended rate routed by selected GPU class (was hardwired to B200 rates, the round-5 P0); Crossover rebuilt on the STATED bill baseline with RateCard-referenced growth (hardcoded 1.04 removed); Tier-1 storage Auto mode derives PB from the bill (Known mode preserves Tier 2/3 entry); crossover suppressed when adjusted capacity exhausts before breakeven; fixture check includes storage mode; crossover regression check + 5-scenario manual checklist added; Validation tolerance tightened to MAX($1, 0.01%).</t>
   </si>
   <si>
+    <t xml:space="preserve">V2.4 (audit round 6): B200 split from B300 — class renamed to plain B200, B300 blocked from the workbook rent-side via data validation pending a benchmark-derived B300→B200 factor (web calculator offers B300 with EST-flagged rates and provisional index — a deliberate reference-vs-product scope split); CloudRates carries per-price confidence (OD LISTED-tracker, 1-yr EST-derived, B200 SNAPSHOT); provider hard-stop — non-AWS selection deliberately NA-errors the calculation with a visible Results guard message; S2 regression rewritten as a cell-level check; Validation header tolerance sentence corrected.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rate Card — all editable (blue). Effective date + source in column C.</t>
   </si>
   <si>
@@ -278,7 +281,10 @@
     <t xml:space="preserve">GPUs</t>
   </si>
   <si>
-    <t xml:space="preserve">Confidence</t>
+    <t xml:space="preserve">OD confidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-yr confidence</t>
   </si>
   <si>
     <t xml:space="preserve">As of</t>
@@ -290,7 +296,10 @@
     <t xml:space="preserve">p4d.24xlarge</t>
   </si>
   <si>
-    <t xml:space="preserve">LISTED (tracker)</t>
+    <t xml:space="preserve">LISTED — secondary tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EST — 40% off OD assumption</t>
   </si>
   <si>
     <t xml:space="preserve">Jul-Aug 2026</t>
@@ -308,81 +317,84 @@
     <t xml:space="preserve">p5e.48xlarge</t>
   </si>
   <si>
+    <t xml:space="preserve">B200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p6-b200.48xlarge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNAPSHOT — NVIDIA TCO tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2.4: each price carries its own provenance — AWS sells On-Demand, Savings Plans and Capacity Blocks as distinct purchasing constructs, so an assumed 40%-off rate is labeled EST, never implied as an AWS-listed reserved price. B200 row = NVIDIA TCO tool snapshot (both prices). NVAIE support stays on RateCard (B6/B7, per instance-hr). B300 is intentionally absent: workbook blocks it pending a benchmark-derived factor; the web calculator offers it with EST-flagged rates and a provisional capability index.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Prem System Registry — add rows as new systems are priced (blue = editable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW suite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compute fabric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage fabric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mgmt fabric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kW per system (avg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sys/rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priced?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGX B200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA TCO tool Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGX B300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholder — price before selecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGX H200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGX GB200 NVL-72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud GPU class list (drives PerfFactors lookups; keep in sync with PerfFactors rows):</t>
+  </si>
+  <si>
     <t xml:space="preserve">B200/B300-class</t>
   </si>
   <si>
-    <t xml:space="preserve">p6-b200.48xlarge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LISTED (NVIDIA tool snapshot)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved = 40% off on-demand (est., matches NVIDIA snapshot ratio). NVAIE support stays on RateCard (B6/B7, per instance-hr). v2.3: Engine!B4 routes by the GPU class selected on Inputs — previously all classes used the B200 row (audit round 5, P0).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-Prem System Registry — add rows as new systems are priced (blue = editable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW suite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compute fabric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage fabric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mgmt fabric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kW per system (avg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sys/rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priced?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGX B200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA TCO tool Jul 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGX B300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placeholder — price before selecting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGX H200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGX GB200 NVL-72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud GPU class list (drives PerfFactors lookups; keep in sync with PerfFactors rows):</t>
-  </si>
-  <si>
     <t xml:space="preserve">Generational performance factors: cloud GPU class -&gt; DGX B200 target (blue = editable)</t>
   </si>
   <si>
@@ -440,7 +452,7 @@
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
-    <t xml:space="preserve">WORKBOOK: AWS rates only (web app routes all five providers). Selecting others here still computes AWS-class economics.</t>
+    <t xml:space="preserve">AWS ONLY in this workbook — any other selection deliberately stops the calculation (NA errors). Use the web calculator for Azure / GCP / OCI / CoreWeave.</t>
   </si>
   <si>
     <t xml:space="preserve">TIER 2 — refine when known (defaults otherwise)</t>
@@ -449,7 +461,7 @@
     <t xml:space="preserve">Current cloud GPU class</t>
   </si>
   <si>
-    <t xml:space="preserve">Must match a PerfFactors row: A100 / H100 / H200 / B200/B300-class</t>
+    <t xml:space="preserve">A100 / H100 / H200 / B200 only. B300 renters: use the web calculator — the workbook blocks B300 pending a benchmark-derived B300→B200 factor (audit round 6).</t>
   </si>
   <si>
     <t xml:space="preserve">Workload mix: training share (%)</t>
@@ -614,7 +626,7 @@
     <t xml:space="preserve">Blended cloud rate ($/instance-hr)</t>
   </si>
   <si>
-    <t xml:space="preserve">v2.3: rate now routed by the selected GPU class via CloudRates (audit round 5 P0 — was hardwired to B200 rates)</t>
+    <t xml:space="preserve">v2.4: hard-stops (NA) for non-AWS providers — prevents screenshotting AWS math under another provider's name; v2.3 class routing retained</t>
   </si>
   <si>
     <t xml:space="preserve">Estimated monthly compute spend ($)</t>
@@ -926,10 +938,13 @@
     <t xml:space="preserve">Simple static payback, adjusted (months — SECONDARY metric only)</t>
   </si>
   <si>
+    <t xml:space="preserve">Provider guard</t>
+  </si>
+  <si>
     <t xml:space="preserve">Validation — reproduce NVIDIA DGX TCO tool Test 1 from this rate card</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario: 1x DGX B200 vs AWS B200-class, all perf factors 1.00, 100% utilization, 100% 1-yr reserved, 0.25 PB fast + 0.75 PB bulk, self-hosted. Expected values from NVIDIA tool screenshots (Aug 2026). Tolerance 1% (small deltas = NVIDIA's 4% ops growth compounding inside 3-yr totals).</t>
+    <t xml:space="preserve">Scenario: 1x DGX B200 vs AWS B200-class, all perf factors 1.00, 100% utilization, 100% 1-yr reserved, 0.25 PB fast + 0.75 PB bulk, self-hosted. Expected values from NVIDIA tool screenshots (Aug 2026). Tolerance MAX($1, 0.01%) — tightened in v2.3 to match the live regression standard.</t>
   </si>
   <si>
     <t xml:space="preserve">Check</t>
@@ -1151,7 +1166,7 @@
     <t xml:space="preserve">S1 No-crossover text: bill $10,000, Storage mode Auto, other defaults → Results!B26 shows the no-crossover text, not a month.</t>
   </si>
   <si>
-    <t xml:space="preserve">S2 Ops-growth sensitivity: change RateCard!B37 from 0.04 to 0.08 → Results!B26 crossover month CHANGES (guards against re-hardcoding).</t>
+    <t xml:space="preserve">S2 Ops-growth sensitivity (cell-based): note Crossover!B61 and C61 (month-60 cumulative cloud and on-prem), change RateCard!B37 from 0.04 to 0.08, confirm BOTH cells increase, then restore 0.04. Do not use the rounded crossover month as the signal — at default spend it stays Month 25 for both rates (rounding), which is exactly why a cell-level check is required (audit round 6).</t>
   </si>
   <si>
     <t xml:space="preserve">S3 N+1 invariance: toggle Inputs!B36 from 0 to 1 → Results!B23 headroom values UNCHANGED (spare is not growth capacity).</t>
@@ -1701,7 +1716,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1842,6 +1857,11 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1869,22 +1889,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>105079</v>
@@ -1892,7 +1912,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>0.49491</v>
@@ -1900,15 +1920,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>0.5</v>
@@ -1916,7 +1936,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>0</v>
@@ -1924,7 +1944,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>1</v>
@@ -1932,7 +1952,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>0.25</v>
@@ -1940,7 +1960,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>0</v>
@@ -1948,15 +1968,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>300</v>
@@ -1964,7 +1984,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>1</v>
@@ -1972,15 +1992,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B17" s="14" t="n">
         <v>0</v>
@@ -1988,54 +2008,54 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B21" s="30" t="str">
-        <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200/B300-class",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS",Inputs!$B$38="Known"),"YES","NO — set fixture first")</f>
+        <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS",Inputs!$B$38="Known"),"YES","NO — set fixture first")</f>
         <v>NO — set fixture first</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">Engine!$B$7</f>
@@ -2051,7 +2071,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">Engine!$B$4</f>
@@ -2067,7 +2087,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">Engine!$B$11</f>
@@ -2083,7 +2103,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B27" s="25" t="n">
         <f aca="false">Engine!$B$18</f>
@@ -2099,7 +2119,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B28" s="25" t="n">
         <f aca="false">Engine!$B$19</f>
@@ -2115,7 +2135,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">Engine!$B$31</f>
@@ -2131,7 +2151,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B30" s="24" t="n">
         <f aca="false">Engine!$B$32</f>
@@ -2147,7 +2167,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B31" s="24" t="n">
         <f aca="false">Engine!$B$39</f>
@@ -2163,7 +2183,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B32" s="24" t="n">
         <f aca="false">Engine!$B$35</f>
@@ -2179,7 +2199,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">Engine!$B$37</f>
@@ -2195,7 +2215,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">Engine!$B$38</f>
@@ -2211,7 +2231,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B35" s="24" t="n">
         <f aca="false">Engine!$B$42</f>
@@ -2227,7 +2247,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B36" s="24" t="n">
         <f aca="false">Engine!$B$54</f>
@@ -2243,7 +2263,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B37" s="24" t="n">
         <f aca="false">Engine!$B$55</f>
@@ -2259,7 +2279,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B38" s="24" t="n">
         <f aca="false">Engine!$B$25</f>
@@ -2275,7 +2295,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B39" s="24" t="n">
         <f aca="false">Engine!$B$26</f>
@@ -2291,7 +2311,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">Engine!$B$5+Engine!$B$25+Engine!$B$26</f>
@@ -2307,7 +2327,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">Engine!$B$41</f>
@@ -2323,14 +2343,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B42" s="30" t="str">
         <f aca="false">Engine!$B$51</f>
         <v>not entered</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D42" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B42=C42,"PASS","FAIL"))</f>
@@ -2339,14 +2359,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B43" s="30" t="str">
         <f aca="false">Results!$B$26</f>
         <v>Month 25</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D43" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B43=C43,"PASS","FAIL"))</f>
@@ -2355,37 +2375,37 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -2413,19 +2433,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3474,89 +3494,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>113.93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>68.36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>2.88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.05</v>
@@ -3565,18 +3585,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>189000</v>
@@ -3585,7 +3605,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>5000</v>
@@ -3594,29 +3614,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>8</v>
@@ -3625,23 +3645,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>25000</v>
@@ -3650,29 +3670,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>1200000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>100000</v>
@@ -3681,18 +3701,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>500000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>33333</v>
@@ -3701,7 +3721,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
@@ -3710,29 +3730,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>3000</v>
@@ -3741,7 +3761,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>2000</v>
@@ -3750,7 +3770,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
@@ -3759,7 +3779,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>189000</v>
@@ -3768,40 +3788,40 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>11387</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>730</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>0.04</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3820,7 +3840,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -3833,38 +3853,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>32.8</v>
@@ -3876,18 +3899,21 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>55.04</v>
@@ -3899,18 +3925,21 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3922,18 +3951,21 @@
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>113.93</v>
@@ -3945,15 +3977,18 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3985,47 +4020,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>8</v>
@@ -4052,15 +4087,15 @@
         <v>2</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>8</v>
@@ -4087,15 +4122,15 @@
         <v>2</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>8</v>
@@ -4122,15 +4157,15 @@
         <v>2</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>72</v>
@@ -4157,35 +4192,35 @@
         <v>1</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4214,32 +4249,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>4.4</v>
@@ -4254,12 +4289,12 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>2.2</v>
@@ -4274,12 +4309,12 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>1.5</v>
@@ -4294,12 +4329,12 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -4314,17 +4349,17 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -4353,320 +4388,320 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>105079</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>0.85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B24" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B25" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B26" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>100000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B37" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation allowBlank="true" error="Must be zero or positive" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4 B11 B16 B21 B33:B35" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -4685,6 +4720,10 @@
     </dataValidation>
     <dataValidation allowBlank="false" error="Auto or Known" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B38" type="list">
       <formula1>"Auto,Known"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Workbook supports A100/H100/H200/B200. B300: use the web calculator." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B8" type="list">
+      <formula1>"A100,H100,H200,B200"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4713,47 +4752,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B4" s="23" t="n">
-        <f aca="false">(Inputs!$B$10*(INDEX(CloudRates!$C$3:$C$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$6)+(1-Inputs!$B$10)*(INDEX(CloudRates!$D$3:$D$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$7))*(1+RateCard!$B$15)</f>
+        <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS",NA(),(Inputs!$B$10*(INDEX(CloudRates!$C$3:$C$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$6)+(1-Inputs!$B$10)*(INDEX(CloudRates!$D$3:$D$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$7))*(1+RateCard!$B$15))</f>
         <v>35.9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B5" s="24" t="n">
         <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
         <v>52539.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">B5/B4</f>
@@ -4763,48 +4802,48 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*RateCard!$B$16)</f>
         <v>11707.9665738162</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
         <v>2.83870967741935</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
         <v>4.79741935483871</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">B7/B11</f>
@@ -4814,24 +4853,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">B7</f>
         <v>11707.9665738162</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -4841,19 +4880,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
         <v>4964</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
@@ -4863,7 +4902,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
@@ -4873,24 +4912,24 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B20" s="27" t="n">
         <f aca="false">1-B12/((B18-Inputs!$B$36)*B17)</f>
         <v>0.508365877420845</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">B62*Inputs!$B$12</f>
@@ -4900,7 +4939,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B24" s="28" t="n">
         <f aca="false">B62*(1-Inputs!$B$12)</f>
@@ -4910,19 +4949,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B25" s="24" t="n">
         <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+B62*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>51965.3333333333</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B26" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -4932,24 +4971,24 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">IF(OR(INDEX(Hardware!$J$3:$J$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;&gt;"YES",INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))=0),NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
         <v>744793</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B30" s="25" t="n">
         <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
@@ -4959,19 +4998,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B31" s="24" t="n">
         <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B32" s="24" t="n">
         <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
@@ -4981,7 +5020,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">B31+B32</f>
@@ -4991,7 +5030,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B34" s="28" t="n">
         <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -5001,19 +5040,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B35" s="24" t="n">
         <f aca="false">(B18*B34+B62*RateCard!$B$26)*Inputs!$B$16</f>
         <v>7289.44761904762</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B36" s="28" t="n">
         <f aca="false">B30+B62*RateCard!$B$27</f>
@@ -5023,43 +5062,43 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B37" s="24" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/36</f>
         <v>3110.54532627866</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B38" s="24" t="n">
         <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B39" s="24" t="n">
         <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
         <v>4124.21218306878</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">B35+B37+B38+B39</f>
@@ -5069,19 +5108,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">B18*RateCard!$B$33+B39</f>
         <v>15511.2121830688</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B42" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
@@ -5091,12 +5130,12 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
@@ -5106,7 +5145,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B46" s="24" t="n">
         <f aca="false">(B19*B34+B62*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+B62*RateCard!$B$27)/36+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
@@ -5116,7 +5155,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B47" s="24" t="n">
         <f aca="false">B19*RateCard!$B$33+B39</f>
@@ -5126,7 +5165,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B48" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
@@ -5136,24 +5175,24 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B51" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
         <v>not entered</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B52" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
@@ -5163,36 +5202,36 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B54" s="24" t="n">
         <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+B62*1000000*RateCard!$B$10</f>
         <v>359648.793650794</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B55" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
         <v>186767.807142857</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B56" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
@@ -5202,12 +5241,12 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B58" s="24" t="n">
         <f aca="false">Engine!$B$25+Engine!$B$26</f>
@@ -5216,7 +5255,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B59" s="24" t="n">
         <f aca="false">Inputs!$B$4*(1-Inputs!$B$13)</f>
@@ -5225,7 +5264,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B60" s="4" t="str">
         <f aca="false">IF(B58&gt;B59*1.02,"⚠ OVERALLOCATED: reconstructed storage+egress+admin exceed the stated non-compute budget by $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo — reduce storage PB or raise the bill",IF(B58&lt;B59*0.98,"ℹ UNALLOCATED: $"&amp;TEXT(B59-B58,"#,##0")&amp;"/mo of the stated bill is not explained by entered components (PaaS, other services?)","OK — within 2% tolerance (difference $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo)"))</f>
@@ -5234,7 +5273,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">MAX(0,(Inputs!$B$4*(1-Inputs!$B$13)-B26)/(Inputs!$B$12*1000000*RateCard!$B$8+(1-Inputs!$B$12)*1000000*RateCard!$B$9+1000000*RateCard!$B$11*RateCard!$B$10))</f>
@@ -5243,7 +5282,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B62" s="29" t="n">
         <f aca="false">IF(Inputs!$B$38="Auto",B61,Inputs!$B$11)</f>
@@ -5266,7 +5305,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -5275,40 +5314,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
@@ -5333,7 +5372,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
@@ -5358,7 +5397,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
@@ -5383,24 +5422,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">SUM($B$6:B6)</f>
@@ -5417,7 +5456,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)</f>
@@ -5434,7 +5473,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">B12-B13</f>
@@ -5451,7 +5490,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B15" s="27" t="n">
         <f aca="false">B14/B12</f>
@@ -5468,7 +5507,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)</f>
@@ -5485,7 +5524,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">B12-B16</f>
@@ -5502,7 +5541,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B18" s="27" t="n">
         <f aca="false">B17/B12</f>
@@ -5519,12 +5558,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B21" s="30" t="str">
         <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
@@ -5533,7 +5572,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B22" s="24" t="n">
         <f aca="false">Engine!$B$33</f>
@@ -5542,7 +5581,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B23" s="27" t="str">
         <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17),"0.0%")</f>
@@ -5551,7 +5590,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B24" s="28" t="str">
         <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
@@ -5560,7 +5599,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B25" s="24" t="n">
         <f aca="false">Engine!$B$25</f>
@@ -5569,16 +5608,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B26" s="28" t="str">
-        <f aca="false">IF(ISNA(MATCH(1,Crossover!$D$2:$D$61,0)),"no crossover within 60 months under the modeled trajectory",IF(Inputs!$B$14=0,"Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),IF(MATCH(1,Crossover!$D$2:$D$61,0)&gt;12*LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"crossover cannot be determined in the workbook — additional capacity is required before breakeven; use the dynamic web model","Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0))))</f>
+        <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS","see provider guard — workbook is AWS only",IF(ISNA(MATCH(1,Crossover!$D$2:$D$61,0)),"no crossover within 60 months under the modeled trajectory",IF(Inputs!$B$14=0,"Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),IF(MATCH(1,Crossover!$D$2:$D$61,0)&gt;12*LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"crossover cannot be determined in the workbook — additional capacity is required before breakeven; use the dynamic web model","Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0)))))</f>
         <v>Month 25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B27" s="24" t="str">
         <f aca="false">Engine!$B$51</f>
@@ -5587,7 +5626,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B28" s="24" t="n">
         <f aca="false">Engine!$B$54</f>
@@ -5596,7 +5635,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">Engine!$B$55</f>
@@ -5605,7 +5644,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B30" s="28" t="n">
         <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
@@ -5614,12 +5653,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B32" s="1" t="str">
         <f aca="false">Engine!$B$60</f>
@@ -5628,11 +5667,20 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B33" s="28" t="n">
         <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"n/a (opex exceeds bill)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42))</f>
         <v>26.8326928757444</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B34" s="4" t="str">
+        <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS","⚠ Workbook reference implementation supports AWS only — use the web calculator for this provider","AWS — OK")</f>
+        <v>AWS — OK</v>
       </c>
     </row>
   </sheetData>
@@ -5660,31 +5708,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">8*RateCard!$B$36</f>
@@ -5700,7 +5748,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
@@ -5716,7 +5764,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
@@ -5732,7 +5780,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -5748,7 +5796,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">B6+B7+B8</f>
@@ -5764,7 +5812,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
@@ -5780,7 +5828,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B11" s="24" t="n">
         <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
@@ -5796,7 +5844,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
@@ -5812,7 +5860,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
@@ -5828,7 +5876,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
@@ -5844,7 +5892,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
@@ -5860,7 +5908,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">B13+B14+B15</f>
@@ -5876,7 +5924,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">1*RateCard!$B$33</f>
@@ -5892,7 +5940,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B18" s="24" t="n">
         <f aca="false">B10*0.0281</f>
@@ -5908,7 +5956,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B19" s="24" t="n">
         <f aca="false">B11*0.0281+B12</f>
@@ -5924,7 +5972,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B20" s="24" t="n">
         <f aca="false">B18+B19+B16</f>
@@ -5940,12 +5988,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reverse-tco-model-v1.xlsx
+++ b/docs/reverse-tco-model-v1.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="392">
   <si>
     <t xml:space="preserve">Reverse TCO Tool v1 — Cloud AIaaS Spend to On-Prem NVIDIA Infrastructure</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">  - Priced on-prem system: DGX B200 (other systems listed in Hardware are placeholders until priced).</t>
   </si>
   <si>
-    <t xml:space="preserve">  - Cloud rate card seeded with AWS p6-b200-class rates from the NVIDIA DGX TCO tool (Jul 2026). Add providers by extending RateCard.</t>
+    <t xml:space="preserve">  - Cloud rates live on the CloudRates sheet (AWS only in this reference workbook — non-AWS selections deliberately hard-stop; the web calculator routes all five providers). B200 row preserves the NVIDIA DGX TCO tool snapshot (Jul 2026).</t>
   </si>
   <si>
     <t xml:space="preserve">  - Financing: optional. Enter a day-of lease rate factor + term on Inputs to add a leased view; blank = capex view only.</t>
@@ -110,6 +110,9 @@
     <t xml:space="preserve">V2.4 (audit round 6): B200 split from B300 — class renamed to plain B200, B300 blocked from the workbook rent-side via data validation pending a benchmark-derived B300→B200 factor (web calculator offers B300 with EST-flagged rates and provisional index — a deliberate reference-vs-product scope split); CloudRates carries per-price confidence (OD LISTED-tracker, 1-yr EST-derived, B200 SNAPSHOT); provider hard-stop — non-AWS selection deliberately NA-errors the calculation with a visible Results guard message; S2 regression rewritten as a cell-level check; Validation header tolerance sentence corrected.</t>
   </si>
   <si>
+    <t xml:space="preserve">V2.5 (audit round 7): horizon totals suppress to explicit N/A when the static fleet is known-insufficient (per case, per horizon — adjusted AND floor); formula-level GPU-class guard catches pasted values that bypass data validation (Results row 35 + crossover short-circuit); stale B200/B300-class references cleaned; GPU count read from CloudRates registry; rack-setup amortization months promoted to an editable RateCard field; README provider language updated.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rate Card — all editable (blue). Effective date + source in column C.</t>
   </si>
   <si>
@@ -179,7 +182,7 @@
     <t xml:space="preserve">0 default; SageMaker/Vertex-style platforms typically 15-30%</t>
   </si>
   <si>
-    <t xml:space="preserve">GPUs per cloud instance</t>
+    <t xml:space="preserve">GPUs per cloud instance — LEGACY reference; Engine reads CloudRates!E per class since v2.5</t>
   </si>
   <si>
     <t xml:space="preserve">ON-PREM (DGX B200 reference; NVIDIA TCO tool defaults Jul 2026)</t>
@@ -263,6 +266,9 @@
     <t xml:space="preserve">NVIDIA default</t>
   </si>
   <si>
+    <t xml:space="preserve">Rack setup amortization (months)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud instance rates by GPU class — AWS (workbook scope)</t>
   </si>
   <si>
@@ -392,9 +398,6 @@
     <t xml:space="preserve">Cloud GPU class list (drives PerfFactors lookups; keep in sync with PerfFactors rows):</t>
   </si>
   <si>
-    <t xml:space="preserve">B200/B300-class</t>
-  </si>
-  <si>
     <t xml:space="preserve">Generational performance factors: cloud GPU class -&gt; DGX B200 target (blue = editable)</t>
   </si>
   <si>
@@ -641,7 +644,7 @@
     <t xml:space="preserve">Cloud GPU-hours per month</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 3 invoice hours override when provided</t>
+    <t xml:space="preserve">v2.5: GPU count read from the CloudRates registry row (was legacy RateCard!B16 constant)</t>
   </si>
   <si>
     <t xml:space="preserve">STEP 2 — Net Performance Factor</t>
@@ -836,6 +839,15 @@
     <t xml:space="preserve">Effective total storage PB used by the model</t>
   </si>
   <si>
+    <t xml:space="preserve">Inputs valid (provider AWS + supported class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhaustion years, adjusted (blank growth-free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhaustion years, floor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Results — Cloud vs. On-Prem</t>
   </si>
   <si>
@@ -941,6 +953,9 @@
     <t xml:space="preserve">Provider guard</t>
   </si>
   <si>
+    <t xml:space="preserve">GPU class guard</t>
+  </si>
+  <si>
     <t xml:space="preserve">Validation — reproduce NVIDIA DGX TCO tool Test 1 from this rate card</t>
   </si>
   <si>
@@ -1175,7 +1190,7 @@
     <t xml:space="preserve">S4 Capacity suppression: high bill (e.g. $2M) with growth 25% → if crossover month exceeds adjusted exhaustion, Results!B26 shows the cannot-be-determined text.</t>
   </si>
   <si>
-    <t xml:space="preserve">S5 Class routing: switch Inputs!B8 H100 ↔ B200/B300-class → Engine!B4 blended rate changes per CloudRates (H100 ≈ $35.90 vs B200 ≈ $71.24 at 100% reserved).</t>
+    <t xml:space="preserve">S5 Class routing: switch Inputs!B8 H100 ↔ B200 → Engine!B4 blended rate changes per CloudRates (H100 ≈ $35.90 vs B200 ≈ $71.24 at 100% reserved).</t>
   </si>
   <si>
     <t xml:space="preserve">Month</t>
@@ -1197,7 +1212,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -1208,6 +1223,7 @@
     <numFmt numFmtId="171" formatCode="0.00\x"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
     <numFmt numFmtId="173" formatCode="0.000&quot; PB&quot;"/>
+    <numFmt numFmtId="174" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1335,132 +1351,136 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1716,7 +1736,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1862,6 +1882,11 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1889,173 +1914,173 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B5" s="14" t="n">
+        <v>335</v>
+      </c>
+      <c r="B5" s="13" t="n">
         <v>105079</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B6" s="14" t="n">
+        <v>336</v>
+      </c>
+      <c r="B6" s="13" t="n">
         <v>0.49491</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>95</v>
+        <v>337</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B8" s="14" t="n">
+        <v>338</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B9" s="14" t="n">
+        <v>339</v>
+      </c>
+      <c r="B9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B10" s="14" t="n">
+        <v>340</v>
+      </c>
+      <c r="B10" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B11" s="14" t="n">
+        <v>341</v>
+      </c>
+      <c r="B11" s="13" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B12" s="14" t="n">
+        <v>342</v>
+      </c>
+      <c r="B12" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>157</v>
+        <v>343</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B14" s="14" t="n">
+        <v>344</v>
+      </c>
+      <c r="B14" s="13" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B15" s="14" t="n">
+        <v>345</v>
+      </c>
+      <c r="B15" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>111</v>
+        <v>346</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B17" s="14" t="n">
+        <v>347</v>
+      </c>
+      <c r="B17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>344</v>
+        <v>348</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>346</v>
+        <v>350</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>348</v>
+        <v>352</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B21" s="30" t="str">
+        <v>354</v>
+      </c>
+      <c r="B21" s="31" t="str">
         <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS",Inputs!$B$38="Known"),"YES","NO — set fixture first")</f>
         <v>NO — set fixture first</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">Engine!$B$7</f>
@@ -2071,7 +2096,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">Engine!$B$4</f>
@@ -2087,7 +2112,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">Engine!$B$11</f>
@@ -2103,7 +2128,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B27" s="25" t="n">
         <f aca="false">Engine!$B$18</f>
@@ -2119,7 +2144,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B28" s="25" t="n">
         <f aca="false">Engine!$B$19</f>
@@ -2135,7 +2160,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">Engine!$B$31</f>
@@ -2151,7 +2176,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B30" s="24" t="n">
         <f aca="false">Engine!$B$32</f>
@@ -2167,7 +2192,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B31" s="24" t="n">
         <f aca="false">Engine!$B$39</f>
@@ -2183,7 +2208,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B32" s="24" t="n">
         <f aca="false">Engine!$B$35</f>
@@ -2199,7 +2224,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">Engine!$B$37</f>
@@ -2215,7 +2240,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">Engine!$B$38</f>
@@ -2231,7 +2256,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B35" s="24" t="n">
         <f aca="false">Engine!$B$42</f>
@@ -2247,7 +2272,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B36" s="24" t="n">
         <f aca="false">Engine!$B$54</f>
@@ -2263,7 +2288,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B37" s="24" t="n">
         <f aca="false">Engine!$B$55</f>
@@ -2279,7 +2304,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B38" s="24" t="n">
         <f aca="false">Engine!$B$25</f>
@@ -2295,7 +2320,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B39" s="24" t="n">
         <f aca="false">Engine!$B$26</f>
@@ -2311,7 +2336,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">Engine!$B$5+Engine!$B$25+Engine!$B$26</f>
@@ -2327,7 +2352,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">Engine!$B$41</f>
@@ -2343,14 +2368,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B42" s="30" t="str">
+        <v>376</v>
+      </c>
+      <c r="B42" s="31" t="str">
         <f aca="false">Engine!$B$51</f>
         <v>not entered</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>372</v>
+      <c r="C42" s="13" t="s">
+        <v>377</v>
       </c>
       <c r="D42" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B42=C42,"PASS","FAIL"))</f>
@@ -2359,14 +2384,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B43" s="30" t="str">
+        <v>378</v>
+      </c>
+      <c r="B43" s="31" t="str">
         <f aca="false">Results!$B$26</f>
         <v>Month 25</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>374</v>
+      <c r="C43" s="13" t="s">
+        <v>379</v>
       </c>
       <c r="D43" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B43=C43,"PASS","FAIL"))</f>
@@ -2375,37 +2400,37 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -2433,30 +2458,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="n">
+      <c r="B2" s="32" t="n">
         <f aca="false">(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((1-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((1-1)/12))</f>
         <v>105079</v>
       </c>
-      <c r="C2" s="31" t="n">
+      <c r="C2" s="32" t="n">
         <f aca="false">Engine!$B$33+Engine!$B$54+(Engine!$B$42*(1+RateCard!$B$37)^INT((1-1)/12))</f>
         <v>2403666.7130649</v>
       </c>
@@ -2469,11 +2494,11 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="31" t="n">
+      <c r="B3" s="32" t="n">
         <f aca="false">B2+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((2-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((2-1)/12))</f>
         <v>210158</v>
       </c>
-      <c r="C3" s="31" t="n">
+      <c r="C3" s="32" t="n">
         <f aca="false">C2+(Engine!$B$42*(1+RateCard!$B$37)^INT((2-1)/12))</f>
         <v>2419765.9181933</v>
       </c>
@@ -2486,11 +2511,11 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="31" t="n">
+      <c r="B4" s="32" t="n">
         <f aca="false">B3+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((3-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((3-1)/12))</f>
         <v>315237</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="32" t="n">
         <f aca="false">C3+(Engine!$B$42*(1+RateCard!$B$37)^INT((3-1)/12))</f>
         <v>2435865.12332169</v>
       </c>
@@ -2503,11 +2528,11 @@
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="32" t="n">
         <f aca="false">B4+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((4-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((4-1)/12))</f>
         <v>420316</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="32" t="n">
         <f aca="false">C4+(Engine!$B$42*(1+RateCard!$B$37)^INT((4-1)/12))</f>
         <v>2451964.32845009</v>
       </c>
@@ -2520,11 +2545,11 @@
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <f aca="false">B5+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((5-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((5-1)/12))</f>
         <v>525395</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="32" t="n">
         <f aca="false">C5+(Engine!$B$42*(1+RateCard!$B$37)^INT((5-1)/12))</f>
         <v>2468063.53357848</v>
       </c>
@@ -2537,11 +2562,11 @@
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <f aca="false">B6+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((6-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((6-1)/12))</f>
         <v>630474</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="32" t="n">
         <f aca="false">C6+(Engine!$B$42*(1+RateCard!$B$37)^INT((6-1)/12))</f>
         <v>2484162.73870688</v>
       </c>
@@ -2554,11 +2579,11 @@
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <f aca="false">B7+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((7-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((7-1)/12))</f>
         <v>735553</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="32" t="n">
         <f aca="false">C7+(Engine!$B$42*(1+RateCard!$B$37)^INT((7-1)/12))</f>
         <v>2500261.94383527</v>
       </c>
@@ -2571,11 +2596,11 @@
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <f aca="false">B8+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((8-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((8-1)/12))</f>
         <v>840632</v>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="32" t="n">
         <f aca="false">C8+(Engine!$B$42*(1+RateCard!$B$37)^INT((8-1)/12))</f>
         <v>2516361.14896367</v>
       </c>
@@ -2588,11 +2613,11 @@
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <f aca="false">B9+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((9-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((9-1)/12))</f>
         <v>945711</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="32" t="n">
         <f aca="false">C9+(Engine!$B$42*(1+RateCard!$B$37)^INT((9-1)/12))</f>
         <v>2532460.35409206</v>
       </c>
@@ -2605,11 +2630,11 @@
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <f aca="false">B10+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((10-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((10-1)/12))</f>
         <v>1050790</v>
       </c>
-      <c r="C11" s="31" t="n">
+      <c r="C11" s="32" t="n">
         <f aca="false">C10+(Engine!$B$42*(1+RateCard!$B$37)^INT((10-1)/12))</f>
         <v>2548559.55922046</v>
       </c>
@@ -2622,11 +2647,11 @@
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <f aca="false">B11+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((11-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((11-1)/12))</f>
         <v>1155869</v>
       </c>
-      <c r="C12" s="31" t="n">
+      <c r="C12" s="32" t="n">
         <f aca="false">C11+(Engine!$B$42*(1+RateCard!$B$37)^INT((11-1)/12))</f>
         <v>2564658.76434885</v>
       </c>
@@ -2639,11 +2664,11 @@
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <f aca="false">B12+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((12-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((12-1)/12))</f>
         <v>1260948</v>
       </c>
-      <c r="C13" s="31" t="n">
+      <c r="C13" s="32" t="n">
         <f aca="false">C12+(Engine!$B$42*(1+RateCard!$B$37)^INT((12-1)/12))</f>
         <v>2580757.96947725</v>
       </c>
@@ -2656,11 +2681,11 @@
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <f aca="false">B13+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((13-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((13-1)/12))</f>
         <v>1381263.455</v>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="32" t="n">
         <f aca="false">C13+(Engine!$B$42*(1+RateCard!$B$37)^INT((13-1)/12))</f>
         <v>2597501.14281078</v>
       </c>
@@ -2673,11 +2698,11 @@
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="32" t="n">
         <f aca="false">B14+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((14-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((14-1)/12))</f>
         <v>1501578.91</v>
       </c>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="32" t="n">
         <f aca="false">C14+(Engine!$B$42*(1+RateCard!$B$37)^INT((14-1)/12))</f>
         <v>2614244.31614431</v>
       </c>
@@ -2690,11 +2715,11 @@
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="32" t="n">
         <f aca="false">B15+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((15-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((15-1)/12))</f>
         <v>1621894.365</v>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="32" t="n">
         <f aca="false">C15+(Engine!$B$42*(1+RateCard!$B$37)^INT((15-1)/12))</f>
         <v>2630987.48947784</v>
       </c>
@@ -2707,11 +2732,11 @@
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <f aca="false">B16+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((16-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((16-1)/12))</f>
         <v>1742209.82</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="32" t="n">
         <f aca="false">C16+(Engine!$B$42*(1+RateCard!$B$37)^INT((16-1)/12))</f>
         <v>2647730.66281137</v>
       </c>
@@ -2724,11 +2749,11 @@
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="32" t="n">
         <f aca="false">B17+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((17-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((17-1)/12))</f>
         <v>1862525.275</v>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C18" s="32" t="n">
         <f aca="false">C17+(Engine!$B$42*(1+RateCard!$B$37)^INT((17-1)/12))</f>
         <v>2664473.8361449</v>
       </c>
@@ -2741,11 +2766,11 @@
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="32" t="n">
         <f aca="false">B18+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((18-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((18-1)/12))</f>
         <v>1982840.73</v>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="32" t="n">
         <f aca="false">C18+(Engine!$B$42*(1+RateCard!$B$37)^INT((18-1)/12))</f>
         <v>2681217.00947843</v>
       </c>
@@ -2758,11 +2783,11 @@
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="32" t="n">
         <f aca="false">B19+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((19-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((19-1)/12))</f>
         <v>2103156.185</v>
       </c>
-      <c r="C20" s="31" t="n">
+      <c r="C20" s="32" t="n">
         <f aca="false">C19+(Engine!$B$42*(1+RateCard!$B$37)^INT((19-1)/12))</f>
         <v>2697960.18281196</v>
       </c>
@@ -2775,11 +2800,11 @@
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="32" t="n">
         <f aca="false">B20+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((20-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((20-1)/12))</f>
         <v>2223471.64</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C21" s="32" t="n">
         <f aca="false">C20+(Engine!$B$42*(1+RateCard!$B$37)^INT((20-1)/12))</f>
         <v>2714703.35614549</v>
       </c>
@@ -2792,11 +2817,11 @@
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <f aca="false">B21+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((21-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((21-1)/12))</f>
         <v>2343787.095</v>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="C22" s="32" t="n">
         <f aca="false">C21+(Engine!$B$42*(1+RateCard!$B$37)^INT((21-1)/12))</f>
         <v>2731446.52947903</v>
       </c>
@@ -2809,11 +2834,11 @@
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="32" t="n">
         <f aca="false">B22+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((22-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((22-1)/12))</f>
         <v>2464102.55</v>
       </c>
-      <c r="C23" s="31" t="n">
+      <c r="C23" s="32" t="n">
         <f aca="false">C22+(Engine!$B$42*(1+RateCard!$B$37)^INT((22-1)/12))</f>
         <v>2748189.70281256</v>
       </c>
@@ -2826,11 +2851,11 @@
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <f aca="false">B23+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((23-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((23-1)/12))</f>
         <v>2584418.005</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="32" t="n">
         <f aca="false">C23+(Engine!$B$42*(1+RateCard!$B$37)^INT((23-1)/12))</f>
         <v>2764932.87614609</v>
       </c>
@@ -2843,11 +2868,11 @@
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <f aca="false">B24+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((24-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((24-1)/12))</f>
         <v>2704733.46</v>
       </c>
-      <c r="C25" s="31" t="n">
+      <c r="C25" s="32" t="n">
         <f aca="false">C24+(Engine!$B$42*(1+RateCard!$B$37)^INT((24-1)/12))</f>
         <v>2781676.04947962</v>
       </c>
@@ -2860,11 +2885,11 @@
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <f aca="false">B25+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((25-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((25-1)/12))</f>
         <v>2843653.15195</v>
       </c>
-      <c r="C26" s="31" t="n">
+      <c r="C26" s="32" t="n">
         <f aca="false">C25+(Engine!$B$42*(1+RateCard!$B$37)^INT((25-1)/12))</f>
         <v>2799088.94974649</v>
       </c>
@@ -2877,11 +2902,11 @@
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="32" t="n">
         <f aca="false">B26+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((26-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((26-1)/12))</f>
         <v>2982572.8439</v>
       </c>
-      <c r="C27" s="31" t="n">
+      <c r="C27" s="32" t="n">
         <f aca="false">C26+(Engine!$B$42*(1+RateCard!$B$37)^INT((26-1)/12))</f>
         <v>2816501.85001336</v>
       </c>
@@ -2894,11 +2919,11 @@
       <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="32" t="n">
         <f aca="false">B27+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((27-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((27-1)/12))</f>
         <v>3121492.53585</v>
       </c>
-      <c r="C28" s="31" t="n">
+      <c r="C28" s="32" t="n">
         <f aca="false">C27+(Engine!$B$42*(1+RateCard!$B$37)^INT((27-1)/12))</f>
         <v>2833914.75028023</v>
       </c>
@@ -2911,11 +2936,11 @@
       <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="31" t="n">
+      <c r="B29" s="32" t="n">
         <f aca="false">B28+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((28-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((28-1)/12))</f>
         <v>3260412.2278</v>
       </c>
-      <c r="C29" s="31" t="n">
+      <c r="C29" s="32" t="n">
         <f aca="false">C28+(Engine!$B$42*(1+RateCard!$B$37)^INT((28-1)/12))</f>
         <v>2851327.65054711</v>
       </c>
@@ -2928,11 +2953,11 @@
       <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="31" t="n">
+      <c r="B30" s="32" t="n">
         <f aca="false">B29+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((29-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((29-1)/12))</f>
         <v>3399331.91975</v>
       </c>
-      <c r="C30" s="31" t="n">
+      <c r="C30" s="32" t="n">
         <f aca="false">C29+(Engine!$B$42*(1+RateCard!$B$37)^INT((29-1)/12))</f>
         <v>2868740.55081398</v>
       </c>
@@ -2945,11 +2970,11 @@
       <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="32" t="n">
         <f aca="false">B30+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((30-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((30-1)/12))</f>
         <v>3538251.6117</v>
       </c>
-      <c r="C31" s="31" t="n">
+      <c r="C31" s="32" t="n">
         <f aca="false">C30+(Engine!$B$42*(1+RateCard!$B$37)^INT((30-1)/12))</f>
         <v>2886153.45108085</v>
       </c>
@@ -2962,11 +2987,11 @@
       <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="32" t="n">
         <f aca="false">B31+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((31-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((31-1)/12))</f>
         <v>3677171.30365</v>
       </c>
-      <c r="C32" s="31" t="n">
+      <c r="C32" s="32" t="n">
         <f aca="false">C31+(Engine!$B$42*(1+RateCard!$B$37)^INT((31-1)/12))</f>
         <v>2903566.35134772</v>
       </c>
@@ -2979,11 +3004,11 @@
       <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="32" t="n">
         <f aca="false">B32+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((32-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((32-1)/12))</f>
         <v>3816090.9956</v>
       </c>
-      <c r="C33" s="31" t="n">
+      <c r="C33" s="32" t="n">
         <f aca="false">C32+(Engine!$B$42*(1+RateCard!$B$37)^INT((32-1)/12))</f>
         <v>2920979.2516146</v>
       </c>
@@ -2996,11 +3021,11 @@
       <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <f aca="false">B33+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((33-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((33-1)/12))</f>
         <v>3955010.68755</v>
       </c>
-      <c r="C34" s="31" t="n">
+      <c r="C34" s="32" t="n">
         <f aca="false">C33+(Engine!$B$42*(1+RateCard!$B$37)^INT((33-1)/12))</f>
         <v>2938392.15188147</v>
       </c>
@@ -3013,11 +3038,11 @@
       <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="32" t="n">
         <f aca="false">B34+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((34-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((34-1)/12))</f>
         <v>4093930.3795</v>
       </c>
-      <c r="C35" s="31" t="n">
+      <c r="C35" s="32" t="n">
         <f aca="false">C34+(Engine!$B$42*(1+RateCard!$B$37)^INT((34-1)/12))</f>
         <v>2955805.05214834</v>
       </c>
@@ -3030,11 +3055,11 @@
       <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="31" t="n">
+      <c r="B36" s="32" t="n">
         <f aca="false">B35+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((35-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((35-1)/12))</f>
         <v>4232850.07145</v>
       </c>
-      <c r="C36" s="31" t="n">
+      <c r="C36" s="32" t="n">
         <f aca="false">C35+(Engine!$B$42*(1+RateCard!$B$37)^INT((35-1)/12))</f>
         <v>2973217.95241521</v>
       </c>
@@ -3047,11 +3072,11 @@
       <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="31" t="n">
+      <c r="B37" s="32" t="n">
         <f aca="false">B36+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((36-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((36-1)/12))</f>
         <v>4371769.7634</v>
       </c>
-      <c r="C37" s="31" t="n">
+      <c r="C37" s="32" t="n">
         <f aca="false">C36+(Engine!$B$42*(1+RateCard!$B$37)^INT((36-1)/12))</f>
         <v>2990630.85268208</v>
       </c>
@@ -3064,11 +3089,11 @@
       <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="31" t="n">
+      <c r="B38" s="32" t="n">
         <f aca="false">B37+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((37-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((37-1)/12))</f>
         <v>4533485.7664655</v>
       </c>
-      <c r="C38" s="31" t="n">
+      <c r="C38" s="32" t="n">
         <f aca="false">C37+(Engine!$B$42*(1+RateCard!$B$37)^INT((37-1)/12))</f>
         <v>3008740.26895963</v>
       </c>
@@ -3081,11 +3106,11 @@
       <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="31" t="n">
+      <c r="B39" s="32" t="n">
         <f aca="false">B38+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((38-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((38-1)/12))</f>
         <v>4695201.769531</v>
       </c>
-      <c r="C39" s="31" t="n">
+      <c r="C39" s="32" t="n">
         <f aca="false">C38+(Engine!$B$42*(1+RateCard!$B$37)^INT((38-1)/12))</f>
         <v>3026849.68523718</v>
       </c>
@@ -3098,11 +3123,11 @@
       <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="31" t="n">
+      <c r="B40" s="32" t="n">
         <f aca="false">B39+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((39-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((39-1)/12))</f>
         <v>4856917.7725965</v>
       </c>
-      <c r="C40" s="31" t="n">
+      <c r="C40" s="32" t="n">
         <f aca="false">C39+(Engine!$B$42*(1+RateCard!$B$37)^INT((39-1)/12))</f>
         <v>3044959.10151473</v>
       </c>
@@ -3115,11 +3140,11 @@
       <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="31" t="n">
+      <c r="B41" s="32" t="n">
         <f aca="false">B40+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((40-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((40-1)/12))</f>
         <v>5018633.775662</v>
       </c>
-      <c r="C41" s="31" t="n">
+      <c r="C41" s="32" t="n">
         <f aca="false">C40+(Engine!$B$42*(1+RateCard!$B$37)^INT((40-1)/12))</f>
         <v>3063068.51779227</v>
       </c>
@@ -3132,11 +3157,11 @@
       <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="31" t="n">
+      <c r="B42" s="32" t="n">
         <f aca="false">B41+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((41-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((41-1)/12))</f>
         <v>5180349.7787275</v>
       </c>
-      <c r="C42" s="31" t="n">
+      <c r="C42" s="32" t="n">
         <f aca="false">C41+(Engine!$B$42*(1+RateCard!$B$37)^INT((41-1)/12))</f>
         <v>3081177.93406982</v>
       </c>
@@ -3149,11 +3174,11 @@
       <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="31" t="n">
+      <c r="B43" s="32" t="n">
         <f aca="false">B42+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((42-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((42-1)/12))</f>
         <v>5342065.781793</v>
       </c>
-      <c r="C43" s="31" t="n">
+      <c r="C43" s="32" t="n">
         <f aca="false">C42+(Engine!$B$42*(1+RateCard!$B$37)^INT((42-1)/12))</f>
         <v>3099287.35034737</v>
       </c>
@@ -3166,11 +3191,11 @@
       <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="32" t="n">
         <f aca="false">B43+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((43-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((43-1)/12))</f>
         <v>5503781.7848585</v>
       </c>
-      <c r="C44" s="31" t="n">
+      <c r="C44" s="32" t="n">
         <f aca="false">C43+(Engine!$B$42*(1+RateCard!$B$37)^INT((43-1)/12))</f>
         <v>3117396.76662491</v>
       </c>
@@ -3183,11 +3208,11 @@
       <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="32" t="n">
         <f aca="false">B44+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((44-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((44-1)/12))</f>
         <v>5665497.787924</v>
       </c>
-      <c r="C45" s="31" t="n">
+      <c r="C45" s="32" t="n">
         <f aca="false">C44+(Engine!$B$42*(1+RateCard!$B$37)^INT((44-1)/12))</f>
         <v>3135506.18290246</v>
       </c>
@@ -3200,11 +3225,11 @@
       <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="32" t="n">
         <f aca="false">B45+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((45-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((45-1)/12))</f>
         <v>5827213.7909895</v>
       </c>
-      <c r="C46" s="31" t="n">
+      <c r="C46" s="32" t="n">
         <f aca="false">C45+(Engine!$B$42*(1+RateCard!$B$37)^INT((45-1)/12))</f>
         <v>3153615.59918001</v>
       </c>
@@ -3217,11 +3242,11 @@
       <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="32" t="n">
         <f aca="false">B46+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((46-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((46-1)/12))</f>
         <v>5988929.794055</v>
       </c>
-      <c r="C47" s="31" t="n">
+      <c r="C47" s="32" t="n">
         <f aca="false">C46+(Engine!$B$42*(1+RateCard!$B$37)^INT((46-1)/12))</f>
         <v>3171725.01545755</v>
       </c>
@@ -3234,11 +3259,11 @@
       <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="32" t="n">
         <f aca="false">B47+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((47-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((47-1)/12))</f>
         <v>6150645.7971205</v>
       </c>
-      <c r="C48" s="31" t="n">
+      <c r="C48" s="32" t="n">
         <f aca="false">C47+(Engine!$B$42*(1+RateCard!$B$37)^INT((47-1)/12))</f>
         <v>3189834.4317351</v>
       </c>
@@ -3251,11 +3276,11 @@
       <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="31" t="n">
+      <c r="B49" s="32" t="n">
         <f aca="false">B48+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((48-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((48-1)/12))</f>
         <v>6312361.800186</v>
       </c>
-      <c r="C49" s="31" t="n">
+      <c r="C49" s="32" t="n">
         <f aca="false">C48+(Engine!$B$42*(1+RateCard!$B$37)^INT((48-1)/12))</f>
         <v>3207943.84801265</v>
       </c>
@@ -3268,11 +3293,11 @@
       <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="31" t="n">
+      <c r="B50" s="32" t="n">
         <f aca="false">B49+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((49-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((49-1)/12))</f>
         <v>6502095.847671</v>
       </c>
-      <c r="C50" s="31" t="n">
+      <c r="C50" s="32" t="n">
         <f aca="false">C49+(Engine!$B$42*(1+RateCard!$B$37)^INT((49-1)/12))</f>
         <v>3226777.6409413</v>
       </c>
@@ -3285,11 +3310,11 @@
       <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="31" t="n">
+      <c r="B51" s="32" t="n">
         <f aca="false">B50+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((50-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((50-1)/12))</f>
         <v>6691829.89515599</v>
       </c>
-      <c r="C51" s="31" t="n">
+      <c r="C51" s="32" t="n">
         <f aca="false">C50+(Engine!$B$42*(1+RateCard!$B$37)^INT((50-1)/12))</f>
         <v>3245611.43386994</v>
       </c>
@@ -3302,11 +3327,11 @@
       <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="31" t="n">
+      <c r="B52" s="32" t="n">
         <f aca="false">B51+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((51-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((51-1)/12))</f>
         <v>6881563.94264099</v>
       </c>
-      <c r="C52" s="31" t="n">
+      <c r="C52" s="32" t="n">
         <f aca="false">C51+(Engine!$B$42*(1+RateCard!$B$37)^INT((51-1)/12))</f>
         <v>3264445.22679859</v>
       </c>
@@ -3319,11 +3344,11 @@
       <c r="A53" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="31" t="n">
+      <c r="B53" s="32" t="n">
         <f aca="false">B52+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((52-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((52-1)/12))</f>
         <v>7071297.99012598</v>
       </c>
-      <c r="C53" s="31" t="n">
+      <c r="C53" s="32" t="n">
         <f aca="false">C52+(Engine!$B$42*(1+RateCard!$B$37)^INT((52-1)/12))</f>
         <v>3283279.01972724</v>
       </c>
@@ -3336,11 +3361,11 @@
       <c r="A54" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="31" t="n">
+      <c r="B54" s="32" t="n">
         <f aca="false">B53+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((53-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((53-1)/12))</f>
         <v>7261032.03761098</v>
       </c>
-      <c r="C54" s="31" t="n">
+      <c r="C54" s="32" t="n">
         <f aca="false">C53+(Engine!$B$42*(1+RateCard!$B$37)^INT((53-1)/12))</f>
         <v>3302112.81265589</v>
       </c>
@@ -3353,11 +3378,11 @@
       <c r="A55" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="31" t="n">
+      <c r="B55" s="32" t="n">
         <f aca="false">B54+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((54-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((54-1)/12))</f>
         <v>7450766.08509597</v>
       </c>
-      <c r="C55" s="31" t="n">
+      <c r="C55" s="32" t="n">
         <f aca="false">C54+(Engine!$B$42*(1+RateCard!$B$37)^INT((54-1)/12))</f>
         <v>3320946.60558454</v>
       </c>
@@ -3370,11 +3395,11 @@
       <c r="A56" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="31" t="n">
+      <c r="B56" s="32" t="n">
         <f aca="false">B55+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((55-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((55-1)/12))</f>
         <v>7640500.13258097</v>
       </c>
-      <c r="C56" s="31" t="n">
+      <c r="C56" s="32" t="n">
         <f aca="false">C55+(Engine!$B$42*(1+RateCard!$B$37)^INT((55-1)/12))</f>
         <v>3339780.39851319</v>
       </c>
@@ -3387,11 +3412,11 @@
       <c r="A57" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="31" t="n">
+      <c r="B57" s="32" t="n">
         <f aca="false">B56+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((56-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((56-1)/12))</f>
         <v>7830234.18006596</v>
       </c>
-      <c r="C57" s="31" t="n">
+      <c r="C57" s="32" t="n">
         <f aca="false">C56+(Engine!$B$42*(1+RateCard!$B$37)^INT((56-1)/12))</f>
         <v>3358614.19144184</v>
       </c>
@@ -3404,11 +3429,11 @@
       <c r="A58" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="31" t="n">
+      <c r="B58" s="32" t="n">
         <f aca="false">B57+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((57-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((57-1)/12))</f>
         <v>8019968.22755096</v>
       </c>
-      <c r="C58" s="31" t="n">
+      <c r="C58" s="32" t="n">
         <f aca="false">C57+(Engine!$B$42*(1+RateCard!$B$37)^INT((57-1)/12))</f>
         <v>3377447.98437049</v>
       </c>
@@ -3421,11 +3446,11 @@
       <c r="A59" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="32" t="n">
         <f aca="false">B58+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((58-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((58-1)/12))</f>
         <v>8209702.27503595</v>
       </c>
-      <c r="C59" s="31" t="n">
+      <c r="C59" s="32" t="n">
         <f aca="false">C58+(Engine!$B$42*(1+RateCard!$B$37)^INT((58-1)/12))</f>
         <v>3396281.77729913</v>
       </c>
@@ -3438,11 +3463,11 @@
       <c r="A60" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="31" t="n">
+      <c r="B60" s="32" t="n">
         <f aca="false">B59+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((59-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((59-1)/12))</f>
         <v>8399436.32252095</v>
       </c>
-      <c r="C60" s="31" t="n">
+      <c r="C60" s="32" t="n">
         <f aca="false">C59+(Engine!$B$42*(1+RateCard!$B$37)^INT((59-1)/12))</f>
         <v>3415115.57022778</v>
       </c>
@@ -3455,11 +3480,11 @@
       <c r="A61" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="31" t="n">
+      <c r="B61" s="32" t="n">
         <f aca="false">B60+(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^INT((60-1)/12)+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^INT((60-1)/12))</f>
         <v>8589170.37000595</v>
       </c>
-      <c r="C61" s="31" t="n">
+      <c r="C61" s="32" t="n">
         <f aca="false">C60+(Engine!$B$42*(1+RateCard!$B$37)^INT((60-1)/12))</f>
         <v>3433949.36315643</v>
       </c>
@@ -3484,7 +3509,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="62"/>
@@ -3494,89 +3519,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>113.93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>68.36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>2.88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.05</v>
@@ -3585,18 +3610,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>189000</v>
@@ -3605,7 +3630,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>5000</v>
@@ -3614,29 +3639,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>8</v>
@@ -3645,23 +3670,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>25000</v>
@@ -3670,29 +3695,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>1200000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>100000</v>
@@ -3701,18 +3726,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>500000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>33333</v>
@@ -3721,7 +3746,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
@@ -3730,29 +3755,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>3000</v>
@@ -3761,7 +3786,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>2000</v>
@@ -3770,7 +3795,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
@@ -3779,7 +3804,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>189000</v>
@@ -3788,40 +3813,48 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>11387</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>730</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>0.04</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3853,41 +3886,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>32.8</v>
@@ -3899,21 +3932,21 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>55.04</v>
@@ -3925,21 +3958,21 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3951,21 +3984,21 @@
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>113.93</v>
@@ -3977,18 +4010,18 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4020,47 +4053,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>109</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>111</v>
+      <c r="A3" s="13" t="s">
+        <v>113</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>8</v>
@@ -4083,19 +4116,19 @@
       <c r="H3" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="I3" s="14" t="n">
+      <c r="I3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>113</v>
+      <c r="J3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>114</v>
+      <c r="A4" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>8</v>
@@ -4118,19 +4151,19 @@
       <c r="H4" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="I4" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>116</v>
+      <c r="J4" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>117</v>
+      <c r="A5" s="13" t="s">
+        <v>119</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>8</v>
@@ -4153,19 +4186,19 @@
       <c r="H5" s="12" t="n">
         <v>10.2</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>116</v>
+      <c r="J5" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>118</v>
+      <c r="A6" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>72</v>
@@ -4188,39 +4221,39 @@
       <c r="H6" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>116</v>
+      <c r="J6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>86</v>
+      <c r="A9" s="13" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>91</v>
+      <c r="A10" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>93</v>
+      <c r="A11" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>120</v>
+      <c r="A12" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4249,32 +4282,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>86</v>
+      <c r="A3" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>4.4</v>
@@ -4289,12 +4322,12 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>91</v>
+      <c r="A4" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>2.2</v>
@@ -4309,12 +4342,12 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>93</v>
+      <c r="A5" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>1.5</v>
@@ -4329,12 +4362,12 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>95</v>
+      <c r="A6" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -4349,17 +4382,17 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -4388,316 +4421,316 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>105079</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>0.85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B24" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B25" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>100000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B38" s="14" t="s">
         <v>192</v>
       </c>
+      <c r="B38" s="13" t="s">
+        <v>193</v>
+      </c>
       <c r="C38" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -4742,7 +4775,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
@@ -4752,47 +4785,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B4" s="23" t="n">
         <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS",NA(),(Inputs!$B$10*(INDEX(CloudRates!$C$3:$C$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$6)+(1-Inputs!$B$10)*(INDEX(CloudRates!$D$3:$D$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$7))*(1+RateCard!$B$15))</f>
         <v>35.9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B5" s="24" t="n">
         <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
         <v>52539.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">B5/B4</f>
@@ -4802,48 +4835,48 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*RateCard!$B$16)</f>
+        <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*INDEX(CloudRates!$E$3:$E$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0)))</f>
         <v>11707.9665738162</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
         <v>2.83870967741935</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
         <v>4.79741935483871</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">B7/B11</f>
@@ -4853,24 +4886,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">B7</f>
         <v>11707.9665738162</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -4880,19 +4913,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
         <v>4964</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
@@ -4902,7 +4935,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
@@ -4912,24 +4945,24 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B20" s="27" t="n">
         <f aca="false">1-B12/((B18-Inputs!$B$36)*B17)</f>
         <v>0.508365877420845</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">B62*Inputs!$B$12</f>
@@ -4939,7 +4972,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B24" s="28" t="n">
         <f aca="false">B62*(1-Inputs!$B$12)</f>
@@ -4949,19 +4982,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" s="24" t="n">
         <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+B62*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>51965.3333333333</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B26" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -4971,24 +5004,24 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">IF(OR(INDEX(Hardware!$J$3:$J$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;&gt;"YES",INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))=0),NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
         <v>744793</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B30" s="25" t="n">
         <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
@@ -4998,19 +5031,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B31" s="24" t="n">
         <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B32" s="24" t="n">
         <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
@@ -5020,7 +5053,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">B31+B32</f>
@@ -5030,7 +5063,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B34" s="28" t="n">
         <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -5040,19 +5073,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B35" s="24" t="n">
         <f aca="false">(B18*B34+B62*RateCard!$B$26)*Inputs!$B$16</f>
         <v>7289.44761904762</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B36" s="28" t="n">
         <f aca="false">B30+B62*RateCard!$B$27</f>
@@ -5062,43 +5095,43 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B37" s="24" t="n">
-        <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/36</f>
+        <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/RateCard!$B$38</f>
         <v>3110.54532627866</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B38" s="24" t="n">
         <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B39" s="24" t="n">
         <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
         <v>4124.21218306878</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">B35+B37+B38+B39</f>
@@ -5108,19 +5141,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">B18*RateCard!$B$33+B39</f>
         <v>15511.2121830688</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B42" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
@@ -5130,12 +5163,12 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
@@ -5145,17 +5178,17 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B46" s="24" t="n">
-        <f aca="false">(B19*B34+B62*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+B62*RateCard!$B$27)/36+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
+        <f aca="false">(B19*B34+B62*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+B62*RateCard!$B$27)/RateCard!$B$38+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
         <v>27944.7606839506</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B47" s="24" t="n">
         <f aca="false">B19*RateCard!$B$33+B39</f>
@@ -5165,7 +5198,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B48" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
@@ -5175,24 +5208,24 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B51" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
         <v>not entered</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B52" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
@@ -5202,36 +5235,36 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B54" s="24" t="n">
         <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+B62*1000000*RateCard!$B$10</f>
         <v>359648.793650794</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B55" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
         <v>186767.807142857</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B56" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
@@ -5241,12 +5274,12 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B58" s="24" t="n">
         <f aca="false">Engine!$B$25+Engine!$B$26</f>
@@ -5255,7 +5288,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B59" s="24" t="n">
         <f aca="false">Inputs!$B$4*(1-Inputs!$B$13)</f>
@@ -5264,7 +5297,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B60" s="4" t="str">
         <f aca="false">IF(B58&gt;B59*1.02,"⚠ OVERALLOCATED: reconstructed storage+egress+admin exceed the stated non-compute budget by $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo — reduce storage PB or raise the bill",IF(B58&lt;B59*0.98,"ℹ UNALLOCATED: $"&amp;TEXT(B59-B58,"#,##0")&amp;"/mo of the stated bill is not explained by entered components (PaaS, other services?)","OK — within 2% tolerance (difference $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo)"))</f>
@@ -5273,7 +5306,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">MAX(0,(Inputs!$B$4*(1-Inputs!$B$13)-B26)/(Inputs!$B$12*1000000*RateCard!$B$8+(1-Inputs!$B$12)*1000000*RateCard!$B$9+1000000*RateCard!$B$11*RateCard!$B$10))</f>
@@ -5282,11 +5315,38 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B62" s="29" t="n">
         <f aca="false">IF(Inputs!$B$38="Auto",B61,Inputs!$B$11)</f>
         <v>0.989815873015873</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B63" s="30" t="b">
+        <f aca="false">AND(Inputs!$B$5="AWS",NOT(ISNA(MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <f aca="false">IF(Inputs!$B$14=0,999,LN(1/(1-B20))/LN(1+Inputs!$B$14))</f>
+        <v>3.18190011877922</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <f aca="false">IF(Inputs!$B$14=0,999,LN(1/(1-(1-B13/((B19-Inputs!$B$36)*B17))))/LN(1+Inputs!$B$14))</f>
+        <v>1.0780264128397</v>
       </c>
     </row>
   </sheetData>
@@ -5305,7 +5365,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -5314,40 +5374,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
@@ -5372,7 +5432,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
@@ -5397,7 +5457,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
@@ -5422,24 +5482,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">SUM($B$6:B6)</f>
@@ -5456,123 +5516,123 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B13" s="24" t="n">
-        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)</f>
+        <f aca="false">IF(Engine!$B$64&lt;1,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7))</f>
         <v>2393990.16233439</v>
       </c>
       <c r="C13" s="24" t="n">
-        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7)</f>
+        <f aca="false">IF(Engine!$B$64&lt;3,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7))</f>
         <v>2803863.04553923</v>
       </c>
-      <c r="D13" s="24" t="n">
-        <f aca="false">Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7)</f>
-        <v>3247181.55601358</v>
+      <c r="D13" s="24" t="str">
+        <f aca="false">IF(Engine!$B$64&lt;5,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7))</f>
+        <v>N/A — capacity exhausted yr 3.2; use web model</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B14" s="24" t="n">
-        <f aca="false">B12-B13</f>
+        <f aca="false">IF(ISNUMBER(B13),B12-B13,"N/A — see on-prem total")</f>
         <v>-1133042.16233439</v>
       </c>
       <c r="C14" s="24" t="n">
-        <f aca="false">C12-C13</f>
+        <f aca="false">IF(ISNUMBER(C13),C12-C13,"N/A — see on-prem total")</f>
         <v>1567906.71786077</v>
       </c>
-      <c r="D14" s="24" t="n">
-        <f aca="false">D12-D13</f>
-        <v>5341988.81399236</v>
+      <c r="D14" s="24" t="str">
+        <f aca="false">IF(ISNUMBER(D13),D12-D13,"N/A — see on-prem total")</f>
+        <v>N/A — see on-prem total</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B15" s="27" t="n">
-        <f aca="false">B14/B12</f>
+        <f aca="false">IF(ISNUMBER(B14),B14/B12,"—")</f>
         <v>-0.898563749127158</v>
       </c>
       <c r="C15" s="27" t="n">
-        <f aca="false">C14/C12</f>
+        <f aca="false">IF(ISNUMBER(C14),C14/C12,"—")</f>
         <v>0.358643479120773</v>
       </c>
-      <c r="D15" s="27" t="n">
-        <f aca="false">D14/D12</f>
-        <v>0.621944679622028</v>
+      <c r="D15" s="27" t="str">
+        <f aca="false">IF(ISNUMBER(D14),D14/D12,"—")</f>
+        <v>—</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B16" s="24" t="n">
-        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)</f>
+        <f aca="false">IF(Engine!$B$65&lt;1,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8))</f>
         <v>3867624.92900106</v>
       </c>
-      <c r="C16" s="24" t="n">
-        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8)</f>
-        <v>4579076.1802059</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <f aca="false">Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8)</f>
-        <v>5348581.85350904</v>
+      <c r="C16" s="24" t="str">
+        <f aca="false">IF(Engine!$B$65&lt;3,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8))</f>
+        <v>N/A — capacity exhausted yr 1.1; use web model</v>
+      </c>
+      <c r="D16" s="24" t="str">
+        <f aca="false">IF(Engine!$B$65&lt;5,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8))</f>
+        <v>N/A — capacity exhausted yr 1.1; use web model</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B17" s="24" t="n">
-        <f aca="false">B12-B16</f>
+        <f aca="false">IF(ISNUMBER(B16),B12-B16,"N/A — see on-prem total")</f>
         <v>-2606676.92900106</v>
       </c>
-      <c r="C17" s="24" t="n">
-        <f aca="false">C12-C16</f>
-        <v>-207306.416805895</v>
-      </c>
-      <c r="D17" s="24" t="n">
-        <f aca="false">D12-D16</f>
-        <v>3240588.5164969</v>
+      <c r="C17" s="24" t="str">
+        <f aca="false">IF(ISNUMBER(C16),C12-C16,"N/A — see on-prem total")</f>
+        <v>N/A — see on-prem total</v>
+      </c>
+      <c r="D17" s="24" t="str">
+        <f aca="false">IF(ISNUMBER(D16),D12-D16,"N/A — see on-prem total")</f>
+        <v>N/A — see on-prem total</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B18" s="27" t="n">
-        <f aca="false">B17/B12</f>
+        <f aca="false">IF(ISNUMBER(B17),B17/B12,"—")</f>
         <v>-2.0672358646043</v>
       </c>
-      <c r="C18" s="27" t="n">
-        <f aca="false">C17/C12</f>
-        <v>-0.0474193354237094</v>
-      </c>
-      <c r="D18" s="27" t="n">
-        <f aca="false">D17/D12</f>
-        <v>0.377287721269715</v>
+      <c r="C18" s="27" t="str">
+        <f aca="false">IF(ISNUMBER(C17),C17/C12,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="D18" s="27" t="str">
+        <f aca="false">IF(ISNUMBER(D17),D17/D12,"—")</f>
+        <v>—</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B21" s="30" t="str">
+        <v>295</v>
+      </c>
+      <c r="B21" s="31" t="str">
         <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
         <v>1 / 3</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B22" s="24" t="n">
         <f aca="false">Engine!$B$33</f>
@@ -5581,7 +5641,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B23" s="27" t="str">
         <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17),"0.0%")</f>
@@ -5590,7 +5650,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B24" s="28" t="str">
         <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
@@ -5599,7 +5659,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B25" s="24" t="n">
         <f aca="false">Engine!$B$25</f>
@@ -5608,16 +5668,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B26" s="28" t="str">
-        <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS","see provider guard — workbook is AWS only",IF(ISNA(MATCH(1,Crossover!$D$2:$D$61,0)),"no crossover within 60 months under the modeled trajectory",IF(Inputs!$B$14=0,"Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),IF(MATCH(1,Crossover!$D$2:$D$61,0)&gt;12*LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"crossover cannot be determined in the workbook — additional capacity is required before breakeven; use the dynamic web model","Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0)))))</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"see input guards — invalid provider or GPU class for this workbook",IF(ISNA(MATCH(1,Crossover!$D$2:$D$61,0)),"no crossover within 60 months under the modeled trajectory",IF(Inputs!$B$14=0,"Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),IF(MATCH(1,Crossover!$D$2:$D$61,0)&gt;12*LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"crossover cannot be determined in the workbook — additional capacity is required before breakeven; use the dynamic web model","Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0)))))</f>
         <v>Month 25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B27" s="24" t="str">
         <f aca="false">Engine!$B$51</f>
@@ -5626,7 +5686,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B28" s="24" t="n">
         <f aca="false">Engine!$B$54</f>
@@ -5635,7 +5695,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">Engine!$B$55</f>
@@ -5644,7 +5704,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B30" s="28" t="n">
         <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
@@ -5653,12 +5713,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B32" s="1" t="str">
         <f aca="false">Engine!$B$60</f>
@@ -5667,7 +5727,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B33" s="28" t="n">
         <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"n/a (opex exceeds bill)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42))</f>
@@ -5676,11 +5736,20 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B34" s="4" t="str">
         <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS","⚠ Workbook reference implementation supports AWS only — use the web calculator for this provider","AWS — OK")</f>
         <v>AWS — OK</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B35" s="4" t="str">
+        <f aca="false">IF(ISNA(MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0)),"⚠ Unsupported GPU class in reference workbook — use A100/H100/H200/B200 or the web calculator","OK")</f>
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
@@ -5708,31 +5777,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">8*RateCard!$B$36</f>
@@ -5748,7 +5817,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
@@ -5764,7 +5833,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
@@ -5780,7 +5849,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -5796,7 +5865,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">B6+B7+B8</f>
@@ -5812,7 +5881,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
@@ -5828,7 +5897,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B11" s="24" t="n">
         <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
@@ -5844,7 +5913,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
@@ -5860,7 +5929,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
@@ -5876,7 +5945,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
@@ -5892,7 +5961,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
@@ -5908,7 +5977,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">B13+B14+B15</f>
@@ -5924,7 +5993,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">1*RateCard!$B$33</f>
@@ -5940,7 +6009,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B18" s="24" t="n">
         <f aca="false">B10*0.0281</f>
@@ -5956,7 +6025,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B19" s="24" t="n">
         <f aca="false">B11*0.0281+B12</f>
@@ -5972,7 +6041,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B20" s="24" t="n">
         <f aca="false">B18+B19+B16</f>
@@ -5988,12 +6057,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reverse-tco-model-v1.xlsx
+++ b/docs/reverse-tco-model-v1.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="396">
   <si>
     <t xml:space="preserve">Reverse TCO Tool v1 — Cloud AIaaS Spend to On-Prem NVIDIA Infrastructure</t>
   </si>
@@ -113,6 +113,15 @@
     <t xml:space="preserve">V2.5 (audit round 7): horizon totals suppress to explicit N/A when the static fleet is known-insufficient (per case, per horizon — adjusted AND floor); formula-level GPU-class guard catches pasted values that bypass data validation (Results row 35 + crossover short-circuit); stale B200/B300-class references cleaned; GPU count read from CloudRates registry; rack-setup amortization months promoted to an editable RateCard field; README provider language updated.</t>
   </si>
   <si>
+    <t xml:space="preserve">SCOPE NOTES (v2.6): (a) Equinix branch — the $11,387/system/mo bundle covers system colocation; incremental storage-rack colocation/power beyond the bundle is NOT separately modeled (disclosed assumption; storage-heavy Equinix scenarios may run somewhat higher than shown). (b) Confidence ranges — Tier 1/2 range display remains a ROADMAP item for the web application; both engines currently output point estimates, with uncertainty carried via rate confidence labels and the floor-vs-adjusted spread rather than numeric ranges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2.6 (audit round 8): master input guard (Engine!B63) — formulas refuse impossible states even when pasted past data validation (zero spend/compute-share/utilization, &gt;100% residual, invalid facility/mode/hardware); all six horizon-total cells master-guarded to 'N/A — see input guard' instead of raw errors; data validations tightened (spend &gt; 0, compute share &gt; 0, facility/provider lists); Results TCO table reordered FLOOR FIRST per the design spec's credibility-anchor principle; spec Step 6 growth wording, Rate Card B200 row, and Open Question 4 rewritten in place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2.7 (audit round 9 — final input-hardening pass): master guard extended with ISNUMBER + range checks for power rate (≥0), all three performance factors at their documented NVIDIA ranges (1-2.5 / 1-10 / 1-5 — guard and documentation now agree), Tier-3 GPU-hours (≥0), and lease factor/term (positive when populated); ALL remaining visible Results key-figure rows (systems, capex, headroom, exhaustion, displaced storage, lease view, one-time, residual, earliest-exhaustion, reconciliation, static payback) master-guarded so an invalid pasted input produces zero raw Excel errors anywhere on Results. Note: Excel compares text greater than numbers, so every guarded numeric field carries an explicit ISNUMBER check.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rate Card — all editable (blue). Effective date + source in column C.</t>
   </si>
   <si>
@@ -839,7 +848,7 @@
     <t xml:space="preserve">Effective total storage PB used by the model</t>
   </si>
   <si>
-    <t xml:space="preserve">Inputs valid (provider AWS + supported class)</t>
+    <t xml:space="preserve">MASTER INPUT GUARD v2.7 — provider, class, hardware, all numeric fields (ISNUMBER + range), perf factors per documented NVIDIA ranges (1-2.5 / 1-10 / 1-5), Tier-3 hours ≥ 0, lease factor/term positive-if-populated</t>
   </si>
   <si>
     <t xml:space="preserve">Exhaustion years, adjusted (blank growth-free)</t>
@@ -896,6 +905,15 @@
     <t xml:space="preserve">Cloud total ($)</t>
   </si>
   <si>
+    <t xml:space="preserve">On-prem total, FLOOR — credibility anchor, no performance credit (capex + one-time - residual + opex) ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAVINGS, floor case ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings, floor case (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">On-prem total, ADJUSTED (capex + one-time - residual + opex) ($)</t>
   </si>
   <si>
@@ -905,15 +923,6 @@
     <t xml:space="preserve">Savings, adjusted (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">On-prem total, FLOOR (capex + one-time - residual + opex) ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAVINGS, floor case ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savings, floor case (%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">KEY FIGURES</t>
   </si>
   <si>
@@ -954,6 +963,9 @@
   </si>
   <si>
     <t xml:space="preserve">GPU class guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master input guard</t>
   </si>
   <si>
     <t xml:space="preserve">Validation — reproduce NVIDIA DGX TCO tool Test 1 from this rate card</t>
@@ -1356,131 +1368,131 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1736,7 +1748,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1884,9 +1896,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1914,22 +1941,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>105079</v>
@@ -1937,7 +1964,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>0.49491</v>
@@ -1945,15 +1972,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>0.5</v>
@@ -1961,7 +1988,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>0</v>
@@ -1969,7 +1996,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B10" s="13" t="n">
         <v>1</v>
@@ -1977,7 +2004,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>0.25</v>
@@ -1985,7 +2012,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>0</v>
@@ -1993,15 +2020,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B14" s="13" t="n">
         <v>300</v>
@@ -2009,7 +2036,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>1</v>
@@ -2017,15 +2044,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B17" s="13" t="n">
         <v>0</v>
@@ -2033,31 +2060,31 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B21" s="31" t="str">
         <f aca="false">IF(AND(Inputs!$B$4=105079,ABS(Inputs!$B$13-0.49491)&lt;0.0001,Inputs!$B$9=0.5,Inputs!$B$10=0,Inputs!$B$11=1,Inputs!$B$12=0.25,Inputs!$B$14=0,Inputs!$B$16=300,Inputs!$B$17=1,Inputs!$B$24=1,Inputs!$B$25=1,Inputs!$B$26=1,Inputs!$B$21=0,Inputs!$B$34=0,Inputs!$B$35=0,Inputs!$B$36=0,Inputs!$B$37=0,Inputs!$B$33=0,Inputs!$B$8="B200",Inputs!$B$15="Self-hosted",Inputs!$B$18="DGX B200",Inputs!$B$5="AWS",Inputs!$B$38="Known"),"YES","NO — set fixture first")</f>
@@ -2066,21 +2093,21 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">Engine!$B$7</f>
@@ -2096,7 +2123,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">Engine!$B$4</f>
@@ -2112,7 +2139,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">Engine!$B$11</f>
@@ -2128,7 +2155,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B27" s="25" t="n">
         <f aca="false">Engine!$B$18</f>
@@ -2144,7 +2171,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B28" s="25" t="n">
         <f aca="false">Engine!$B$19</f>
@@ -2160,7 +2187,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">Engine!$B$31</f>
@@ -2176,7 +2203,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B30" s="24" t="n">
         <f aca="false">Engine!$B$32</f>
@@ -2192,7 +2219,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B31" s="24" t="n">
         <f aca="false">Engine!$B$39</f>
@@ -2208,7 +2235,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B32" s="24" t="n">
         <f aca="false">Engine!$B$35</f>
@@ -2224,7 +2251,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">Engine!$B$37</f>
@@ -2240,7 +2267,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">Engine!$B$38</f>
@@ -2256,7 +2283,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B35" s="24" t="n">
         <f aca="false">Engine!$B$42</f>
@@ -2272,7 +2299,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B36" s="24" t="n">
         <f aca="false">Engine!$B$54</f>
@@ -2288,7 +2315,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B37" s="24" t="n">
         <f aca="false">Engine!$B$55</f>
@@ -2304,7 +2331,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B38" s="24" t="n">
         <f aca="false">Engine!$B$25</f>
@@ -2320,7 +2347,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B39" s="24" t="n">
         <f aca="false">Engine!$B$26</f>
@@ -2336,7 +2363,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">Engine!$B$5+Engine!$B$25+Engine!$B$26</f>
@@ -2352,7 +2379,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">Engine!$B$41</f>
@@ -2368,14 +2395,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B42" s="31" t="str">
         <f aca="false">Engine!$B$51</f>
         <v>not entered</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D42" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B42=C42,"PASS","FAIL"))</f>
@@ -2384,14 +2411,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B43" s="31" t="str">
         <f aca="false">Results!$B$26</f>
         <v>Month 25</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D43" s="4" t="str">
         <f aca="false">IF($B$21&lt;&gt;"YES","FIXTURE NOT LOADED",IF(B43=C43,"PASS","FAIL"))</f>
@@ -2400,37 +2427,37 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -2458,19 +2485,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3519,89 +3546,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>113.93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>68.36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>2.88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.05</v>
@@ -3610,18 +3637,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>189000</v>
@@ -3630,7 +3657,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>5000</v>
@@ -3639,29 +3666,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>8</v>
@@ -3670,23 +3697,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>25000</v>
@@ -3695,29 +3722,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>1200000</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>100000</v>
@@ -3726,18 +3753,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>500000</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>33333</v>
@@ -3746,7 +3773,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
@@ -3755,29 +3782,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>3000</v>
@@ -3786,7 +3813,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>2000</v>
@@ -3795,7 +3822,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
@@ -3804,7 +3831,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>189000</v>
@@ -3813,45 +3840,45 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>11387</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>730</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>0.04</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B38" s="13" t="n">
         <v>36</v>
@@ -3886,41 +3913,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>32.8</v>
@@ -3932,21 +3959,21 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>55.04</v>
@@ -3958,21 +3985,21 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3984,21 +4011,21 @@
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>113.93</v>
@@ -4010,18 +4037,18 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4053,47 +4080,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>8</v>
@@ -4120,15 +4147,15 @@
         <v>2</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>8</v>
@@ -4155,15 +4182,15 @@
         <v>2</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>8</v>
@@ -4190,15 +4217,15 @@
         <v>2</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>72</v>
@@ -4225,35 +4252,35 @@
         <v>1</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4282,32 +4309,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>4.4</v>
@@ -4322,12 +4349,12 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>2.2</v>
@@ -4342,12 +4369,12 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>1.5</v>
@@ -4362,12 +4389,12 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -4382,17 +4409,17 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -4421,325 +4448,329 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>105079</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>0.85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B24" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B25" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B26" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>100000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B37" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation allowBlank="true" error="Must be zero or positive" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4 B11 B16 B21 B33:B35" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="false" error="Monthly spend must be greater than zero" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Enter a fraction between 0 and 1" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B9:B10 B12:B14 B37" type="decimal">
+    <dataValidation allowBlank="false" error="Compute share must be &gt; 0% and ≤ 100%" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B13" type="decimal">
+      <formula1>0.0001</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Enter a fraction between 0 and 1" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B9:B10 B12 B14 B37" type="decimal">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -4747,16 +4778,48 @@
       <formula1>0.05</formula1>
       <formula2>1</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Must be zero or positive" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B11 B16 B21 B33:B35" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="false" error="0 = off, 1 = N+1" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B36" type="whole">
       <formula1>0</formula1>
       <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Workbook supports A100/H100/H200/B200. B300: use the web calculator." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B8" type="list">
+      <formula1>"A100,H100,H200,B200"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" error="Auto or Known" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B38" type="list">
       <formula1>"Auto,Known"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Workbook supports A100/H100/H200/B200. B300: use the web calculator." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B8" type="list">
-      <formula1>"A100,H100,H200,B200"</formula1>
+    <dataValidation allowBlank="false" error="Self-hosted, Self-hosted (retrofit), or Equinix" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B15" type="list">
+      <formula1>"Self-hosted,Self-hosted (retrofit),Equinix"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Note: non-AWS deliberately hard-stops this workbook" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B5" type="list">
+      <formula1>"AWS,Azure,GCP,OCI,CoreWeave"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Network factor: documented range 1.0-2.5x" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B24" type="decimal">
+      <formula1>1</formula1>
+      <formula2>2.5</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="AI Factory software factor: documented range 1.0-10x" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B25" type="decimal">
+      <formula1>1</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="NVAIE/NIMs factor: documented range 1.0-5x" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B26" type="decimal">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Lease factor must be positive when entered" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B29" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Lease term must be a positive number of months" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B30" type="whole">
+      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4785,47 +4848,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B4" s="23" t="n">
         <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS",NA(),(Inputs!$B$10*(INDEX(CloudRates!$C$3:$C$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$6)+(1-Inputs!$B$10)*(INDEX(CloudRates!$D$3:$D$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))+RateCard!$B$7))*(1+RateCard!$B$15))</f>
         <v>35.9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B5" s="24" t="n">
         <f aca="false">Inputs!$B$4*Inputs!$B$13</f>
         <v>52539.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">B5/B4</f>
@@ -4835,48 +4898,48 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="false">IF(Inputs!$B$21&gt;0,Inputs!$B$21,B6*INDEX(CloudRates!$E$3:$E$6,MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0)))</f>
         <v>11707.9665738162</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">1/(Inputs!$B$9/INDEX(PerfFactors!$B$3:$B$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0))+(1-Inputs!$B$9)/INDEX(PerfFactors!$D$3:$D$6,MATCH(Inputs!$B$8,PerfFactors!$A$3:$A$6,0)))</f>
         <v>2.83870967741935</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">B10*Inputs!$B$24*Inputs!$B$25*Inputs!$B$26</f>
         <v>4.79741935483871</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">B7/B11</f>
@@ -4886,24 +4949,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">B7</f>
         <v>11707.9665738162</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -4913,19 +4976,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">B16*RateCard!$B$36*Inputs!$B$17</f>
         <v>4964</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">CEILING(B12/B17,1)+Inputs!$B$36</f>
@@ -4935,7 +4998,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">CEILING(B13/B17,1)+Inputs!$B$36</f>
@@ -4945,24 +5008,24 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B20" s="27" t="n">
         <f aca="false">1-B12/((B18-Inputs!$B$36)*B17)</f>
         <v>0.508365877420845</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">B62*Inputs!$B$12</f>
@@ -4972,7 +5035,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B24" s="28" t="n">
         <f aca="false">B62*(1-Inputs!$B$12)</f>
@@ -4982,19 +5045,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B25" s="24" t="n">
         <f aca="false">B23*1000000*RateCard!$B$8+B24*1000000*RateCard!$B$9+B62*1000000*RateCard!$B$11*RateCard!$B$10</f>
         <v>51965.3333333333</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B26" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -5004,24 +5067,24 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">IF(OR(INDEX(Hardware!$J$3:$J$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))&lt;&gt;"YES",INDEX(Hardware!$B$3:$B$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))=0),NA(),INDEX(Hardware!$C$3:$C$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$E$3:$E$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$F$3:$F$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+INDEX(Hardware!$G$3:$G$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))+RateCard!$B$20)</f>
         <v>744793</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B30" s="25" t="n">
         <f aca="false">CEILING(B18/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)</f>
@@ -5031,19 +5094,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B31" s="24" t="n">
         <f aca="false">B18*B29+RateCard!$B$19+B30*RateCard!$B$21</f>
         <v>1359793</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B32" s="24" t="n">
         <f aca="false">B23*RateCard!$B$22+B24*RateCard!$B$24</f>
@@ -5053,7 +5116,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">B31+B32</f>
@@ -5063,7 +5126,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B34" s="28" t="n">
         <f aca="false">INDEX(Hardware!$H$3:$H$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))</f>
@@ -5073,19 +5136,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B35" s="24" t="n">
         <f aca="false">(B18*B34+B62*RateCard!$B$26)*Inputs!$B$16</f>
         <v>7289.44761904762</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B36" s="28" t="n">
         <f aca="false">B30+B62*RateCard!$B$27</f>
@@ -5095,43 +5158,43 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B37" s="24" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*B36/RateCard!$B$38</f>
         <v>3110.54532627866</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B38" s="24" t="n">
         <f aca="false">B18/RateCard!$B$31*RateCard!$B$32/12</f>
         <v>1575</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B39" s="24" t="n">
         <f aca="false">(B23*RateCard!$B$23+B24*RateCard!$B$25)/12</f>
         <v>4124.21218306878</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">B35+B37+B38+B39</f>
@@ -5141,19 +5204,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">B18*RateCard!$B$33+B39</f>
         <v>15511.2121830688</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B42" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B41,B40)</f>
@@ -5163,12 +5226,12 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">B19*B29+RateCard!$B$19+CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)*RateCard!$B$21+B32</f>
@@ -5178,7 +5241,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B46" s="24" t="n">
         <f aca="false">(B19*B34+B62*RateCard!$B$26)*Inputs!$B$16+RateCard!$B$29+RateCard!$B$30*(CEILING(B19/INDEX(Hardware!$I$3:$I$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)),1)+B62*RateCard!$B$27)/RateCard!$B$38+B19/RateCard!$B$31*RateCard!$B$32/12+B39</f>
@@ -5188,7 +5251,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B47" s="24" t="n">
         <f aca="false">B19*RateCard!$B$33+B39</f>
@@ -5198,7 +5261,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B48" s="24" t="n">
         <f aca="false">IF(Inputs!$B$15="Equinix",B47,B46)</f>
@@ -5208,24 +5271,24 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B51" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B33*Inputs!$B$29+B42)</f>
         <v>not entered</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B52" s="24" t="str">
         <f aca="false">IF(ISBLANK(Inputs!$B$29),"not entered",B45*Inputs!$B$29+B48)</f>
@@ -5235,36 +5298,36 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B54" s="24" t="n">
         <f aca="false">Inputs!$B$33+Inputs!$B$34+Inputs!$B$35*Inputs!$B$4+B62*1000000*RateCard!$B$10</f>
         <v>359648.793650794</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B55" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B18*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
         <v>186767.807142857</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B56" s="24" t="n">
         <f aca="false">Inputs!$B$37*(B19*(B29-RateCard!$B$20-INDEX(Hardware!$D$3:$D$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0)))+B32)</f>
@@ -5274,12 +5337,12 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B58" s="24" t="n">
         <f aca="false">Engine!$B$25+Engine!$B$26</f>
@@ -5288,7 +5351,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B59" s="24" t="n">
         <f aca="false">Inputs!$B$4*(1-Inputs!$B$13)</f>
@@ -5297,7 +5360,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B60" s="4" t="str">
         <f aca="false">IF(B58&gt;B59*1.02,"⚠ OVERALLOCATED: reconstructed storage+egress+admin exceed the stated non-compute budget by $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo — reduce storage PB or raise the bill",IF(B58&lt;B59*0.98,"ℹ UNALLOCATED: $"&amp;TEXT(B59-B58,"#,##0")&amp;"/mo of the stated bill is not explained by entered components (PaaS, other services?)","OK — within 2% tolerance (difference $"&amp;TEXT(B58-B59,"#,##0")&amp;"/mo)"))</f>
@@ -5306,7 +5369,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">MAX(0,(Inputs!$B$4*(1-Inputs!$B$13)-B26)/(Inputs!$B$12*1000000*RateCard!$B$8+(1-Inputs!$B$12)*1000000*RateCard!$B$9+1000000*RateCard!$B$11*RateCard!$B$10))</f>
@@ -5315,34 +5378,34 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B62" s="29" t="n">
         <f aca="false">IF(Inputs!$B$38="Auto",B61,Inputs!$B$11)</f>
         <v>0.989815873015873</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B63" s="30" t="b">
-        <f aca="false">AND(Inputs!$B$5="AWS",NOT(ISNA(MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))))</f>
+        <f aca="false">AND(Inputs!$B$5="AWS",NOT(ISNA(MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0))),NOT(ISNA(MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))),IFERROR(INDEX(Hardware!$J$3:$J$6,MATCH(Inputs!$B$18,Hardware!$A$3:$A$6,0))="YES",FALSE()),ISNUMBER(Inputs!$B$4),Inputs!$B$4&gt;0,ISNUMBER(Inputs!$B$13),Inputs!$B$13&gt;0,Inputs!$B$13&lt;=1,ISNUMBER(Inputs!$B$9),Inputs!$B$9&gt;=0,Inputs!$B$9&lt;=1,ISNUMBER(Inputs!$B$10),Inputs!$B$10&gt;=0,Inputs!$B$10&lt;=1,ISNUMBER(Inputs!$B$12),Inputs!$B$12&gt;=0,Inputs!$B$12&lt;=1,ISNUMBER(Inputs!$B$17),Inputs!$B$17&gt;0,Inputs!$B$17&lt;=1,ISNUMBER(Inputs!$B$14),Inputs!$B$14&gt;=0,ISNUMBER(Inputs!$B$37),Inputs!$B$37&gt;=0,Inputs!$B$37&lt;=1,ISNUMBER(Inputs!$B$33),Inputs!$B$33&gt;=0,ISNUMBER(Inputs!$B$34),Inputs!$B$34&gt;=0,ISNUMBER(Inputs!$B$35),Inputs!$B$35&gt;=0,ISNUMBER(Inputs!$B$11),Inputs!$B$11&gt;=0,ISNUMBER(Inputs!$B$16),Inputs!$B$16&gt;=0,ISNUMBER(Inputs!$B$24),Inputs!$B$24&gt;=1,Inputs!$B$24&lt;=2.5,ISNUMBER(Inputs!$B$25),Inputs!$B$25&gt;=1,Inputs!$B$25&lt;=10,ISNUMBER(Inputs!$B$26),Inputs!$B$26&gt;=1,Inputs!$B$26&lt;=5,ISNUMBER(Inputs!$B$21),Inputs!$B$21&gt;=0,OR(ISBLANK(Inputs!$B$29),AND(ISNUMBER(Inputs!$B$29),Inputs!$B$29&gt;0)),OR(ISBLANK(Inputs!$B$30),AND(ISNUMBER(Inputs!$B$30),Inputs!$B$30&gt;0)),OR(Inputs!$B$36=0,Inputs!$B$36=1),OR(Inputs!$B$15="Self-hosted",Inputs!$B$15="Self-hosted (retrofit)",Inputs!$B$15="Equinix"),OR(Inputs!$B$38="Auto",Inputs!$B$38="Known"))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B64" s="1" t="n">
         <f aca="false">IF(Inputs!$B$14=0,999,LN(1/(1-B20))/LN(1+Inputs!$B$14))</f>
         <v>3.18190011877922</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B65" s="1" t="n">
         <f aca="false">IF(Inputs!$B$14=0,999,LN(1/(1-(1-B13/((B19-Inputs!$B$36)*B17))))/LN(1+Inputs!$B$14))</f>
@@ -5365,7 +5428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -5374,132 +5437,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0)</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^0+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^0))</f>
         <v>1260948</v>
       </c>
       <c r="C6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^1+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^1)</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^1+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^1))</f>
         <v>1443785.46</v>
       </c>
       <c r="D6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^2+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^2)</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^2+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^2))</f>
         <v>1667036.3034</v>
       </c>
       <c r="E6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^3+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^3)</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^3+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^3))</f>
         <v>1940592.036786</v>
       </c>
       <c r="F6" s="24" t="n">
-        <f aca="false">12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^4+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^4)</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*(Inputs!$B$4*Inputs!$B$13*(1+Inputs!$B$14)^4+Inputs!$B$4*(1-Inputs!$B$13)*(1+RateCard!$B$37)^4))</f>
         <v>2276808.56981994</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^0</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$42*(1+RateCard!$B$37)^0)</f>
         <v>193190.461540741</v>
       </c>
       <c r="C7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^1</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$42*(1+RateCard!$B$37)^1)</f>
         <v>200918.08000237</v>
       </c>
       <c r="D7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^2</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$42*(1+RateCard!$B$37)^2)</f>
         <v>208954.803202465</v>
       </c>
       <c r="E7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^3</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$42*(1+RateCard!$B$37)^3)</f>
         <v>217312.995330564</v>
       </c>
       <c r="F7" s="24" t="n">
-        <f aca="false">12*Engine!$B$42*(1+RateCard!$B$37)^4</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$42*(1+RateCard!$B$37)^4)</f>
         <v>226005.515143786</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^0</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$48*(1+RateCard!$B$37)^0)</f>
         <v>335337.128207407</v>
       </c>
       <c r="C8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^1</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$48*(1+RateCard!$B$37)^1)</f>
         <v>348750.613335704</v>
       </c>
       <c r="D8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^2</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$48*(1+RateCard!$B$37)^2)</f>
         <v>362700.637869132</v>
       </c>
       <c r="E8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^3</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$48*(1+RateCard!$B$37)^3)</f>
         <v>377208.663383897</v>
       </c>
       <c r="F8" s="24" t="n">
-        <f aca="false">12*Engine!$B$48*(1+RateCard!$B$37)^4</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",12*Engine!$B$48*(1+RateCard!$B$37)^4)</f>
         <v>392297.009919253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">SUM($B$6:B6)</f>
@@ -5516,32 +5579,32 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B13" s="24" t="n">
-        <f aca="false">IF(Engine!$B$64&lt;1,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7))</f>
-        <v>2393990.16233439</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <f aca="false">IF(Engine!$B$64&lt;3,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7))</f>
-        <v>2803863.04553923</v>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Engine!$B$65&lt;1,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8)))</f>
+        <v>3867624.92900106</v>
+      </c>
+      <c r="C13" s="24" t="str">
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Engine!$B$65&lt;3,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8)))</f>
+        <v>N/A — capacity exhausted yr 1.1; use web model</v>
       </c>
       <c r="D13" s="24" t="str">
-        <f aca="false">IF(Engine!$B$64&lt;5,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7))</f>
-        <v>N/A — capacity exhausted yr 3.2; use web model</v>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Engine!$B$65&lt;5,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8)))</f>
+        <v>N/A — capacity exhausted yr 1.1; use web model</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">IF(ISNUMBER(B13),B12-B13,"N/A — see on-prem total")</f>
-        <v>-1133042.16233439</v>
-      </c>
-      <c r="C14" s="24" t="n">
+        <v>-2606676.92900106</v>
+      </c>
+      <c r="C14" s="24" t="str">
         <f aca="false">IF(ISNUMBER(C13),C12-C13,"N/A — see on-prem total")</f>
-        <v>1567906.71786077</v>
+        <v>N/A — see on-prem total</v>
       </c>
       <c r="D14" s="24" t="str">
         <f aca="false">IF(ISNUMBER(D13),D12-D13,"N/A — see on-prem total")</f>
@@ -5550,15 +5613,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B15" s="27" t="n">
         <f aca="false">IF(ISNUMBER(B14),B14/B12,"—")</f>
-        <v>-0.898563749127158</v>
-      </c>
-      <c r="C15" s="27" t="n">
+        <v>-2.0672358646043</v>
+      </c>
+      <c r="C15" s="27" t="str">
         <f aca="false">IF(ISNUMBER(C14),C14/C12,"—")</f>
-        <v>0.358643479120773</v>
+        <v>—</v>
       </c>
       <c r="D15" s="27" t="str">
         <f aca="false">IF(ISNUMBER(D14),D14/D12,"—")</f>
@@ -5567,32 +5630,32 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B16" s="24" t="n">
-        <f aca="false">IF(Engine!$B$65&lt;1,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:B8))</f>
-        <v>3867624.92900106</v>
-      </c>
-      <c r="C16" s="24" t="str">
-        <f aca="false">IF(Engine!$B$65&lt;3,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:D8))</f>
-        <v>N/A — capacity exhausted yr 1.1; use web model</v>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Engine!$B$64&lt;1,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:B7)))</f>
+        <v>2393990.16233439</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Engine!$B$64&lt;3,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:D7)))</f>
+        <v>2803863.04553923</v>
       </c>
       <c r="D16" s="24" t="str">
-        <f aca="false">IF(Engine!$B$65&lt;5,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$65,"0.0")&amp;"; use web model",Engine!$B$45+Engine!$B$54-Engine!$B$56+SUM($B$8:F8))</f>
-        <v>N/A — capacity exhausted yr 1.1; use web model</v>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Engine!$B$64&lt;5,"N/A — capacity exhausted yr "&amp;TEXT(Engine!$B$64,"0.0")&amp;"; use web model",Engine!$B$33+Engine!$B$54-Engine!$B$55+SUM($B$7:F7)))</f>
+        <v>N/A — capacity exhausted yr 3.2; use web model</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">IF(ISNUMBER(B16),B12-B16,"N/A — see on-prem total")</f>
-        <v>-2606676.92900106</v>
-      </c>
-      <c r="C17" s="24" t="str">
+        <v>-1133042.16233439</v>
+      </c>
+      <c r="C17" s="24" t="n">
         <f aca="false">IF(ISNUMBER(C16),C12-C16,"N/A — see on-prem total")</f>
-        <v>N/A — see on-prem total</v>
+        <v>1567906.71786077</v>
       </c>
       <c r="D17" s="24" t="str">
         <f aca="false">IF(ISNUMBER(D16),D12-D16,"N/A — see on-prem total")</f>
@@ -5601,15 +5664,15 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B18" s="27" t="n">
         <f aca="false">IF(ISNUMBER(B17),B17/B12,"—")</f>
-        <v>-2.0672358646043</v>
-      </c>
-      <c r="C18" s="27" t="str">
+        <v>-0.898563749127158</v>
+      </c>
+      <c r="C18" s="27" t="n">
         <f aca="false">IF(ISNUMBER(C17),C17/C12,"—")</f>
-        <v>—</v>
+        <v>0.358643479120773</v>
       </c>
       <c r="D18" s="27" t="str">
         <f aca="false">IF(ISNUMBER(D17),D17/D12,"—")</f>
@@ -5618,138 +5681,147 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B21" s="31" t="str">
-        <f aca="false">Engine!$B$18&amp;" / "&amp;Engine!$B$19</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",Engine!$B$18&amp;" / "&amp;Engine!$B$19)</f>
         <v>1 / 3</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B22" s="24" t="n">
-        <f aca="false">Engine!$B$33</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",Engine!$B$33)</f>
         <v>2027918.71428571</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B23" s="27" t="str">
-        <f aca="false">TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17),"0.0%")</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",TEXT(Engine!$B$20,"0.0%")&amp;" / "&amp;TEXT(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17),"0.0%"))</f>
         <v>50.8% / 21.4%</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B24" s="28" t="str">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0"))</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Inputs!$B$14=0,"n/a (no growth)",TEXT(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"0.0")&amp;" / "&amp;TEXT(LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14),"0.0")))</f>
         <v>3.2 / 1.1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B25" s="24" t="n">
-        <f aca="false">Engine!$B$25</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",Engine!$B$25)</f>
         <v>51965.3333333333</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B26" s="28" t="str">
-        <f aca="false">IF(Engine!$B$63=FALSE(),"see input guards — invalid provider or GPU class for this workbook",IF(ISNA(MATCH(1,Crossover!$D$2:$D$61,0)),"no crossover within 60 months under the modeled trajectory",IF(Inputs!$B$14=0,"Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),IF(MATCH(1,Crossover!$D$2:$D$61,0)&gt;12*LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"crossover cannot be determined in the workbook — additional capacity is required before breakeven; use the dynamic web model","Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0)))))</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"see input guards — invalid input state for this workbook",IF(ISNA(MATCH(1,Crossover!$D$2:$D$61,0)),"no crossover within 60 months under the modeled trajectory",IF(Inputs!$B$14=0,"Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0),IF(MATCH(1,Crossover!$D$2:$D$61,0)&gt;12*LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),"crossover cannot be determined in the workbook — additional capacity is required before breakeven; use the dynamic web model","Month "&amp;MATCH(1,Crossover!$D$2:$D$61,0)))))</f>
         <v>Month 25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B27" s="24" t="str">
-        <f aca="false">Engine!$B$51</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",Engine!$B$51)</f>
         <v>not entered</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B28" s="24" t="n">
-        <f aca="false">Engine!$B$54</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",Engine!$B$54)</f>
         <v>359648.793650794</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B29" s="24" t="n">
-        <f aca="false">Engine!$B$55</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",Engine!$B$55)</f>
         <v>186767.807142857</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B30" s="28" t="n">
-        <f aca="false">IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14)))</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Inputs!$B$14=0,"n/a (no growth)",MIN(LN(1/(1-Engine!$B$20))/LN(1+Inputs!$B$14),LN(1/(1-(1-Engine!$B$13/((Engine!$B$19-Inputs!$B$36)*Engine!$B$17))))/LN(1+Inputs!$B$14))))</f>
         <v>1.0780264128397</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B32" s="1" t="str">
-        <f aca="false">Engine!$B$60</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",Engine!$B$60)</f>
         <v>OK — within 2% tolerance (difference $0/mo)</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B33" s="28" t="n">
-        <f aca="false">IF(Inputs!$B$4-Engine!$B$42&lt;=0,"n/a (opex exceeds bill)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42))</f>
+        <f aca="false">IF(Engine!$B$63=FALSE(),"N/A — see input guard",IF(Inputs!$B$4-Engine!$B$42&lt;=0,"n/a (opex exceeds bill)",(Engine!$B$33+Engine!$B$54)/(Inputs!$B$4-Engine!$B$42)))</f>
         <v>26.8326928757444</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B34" s="4" t="str">
         <f aca="false">IF(Inputs!$B$5&lt;&gt;"AWS","⚠ Workbook reference implementation supports AWS only — use the web calculator for this provider","AWS — OK")</f>
         <v>AWS — OK</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B35" s="4" t="str">
         <f aca="false">IF(ISNA(MATCH(Inputs!$B$8,CloudRates!$A$3:$A$6,0)),"⚠ Unsupported GPU class in reference workbook — use A100/H100/H200/B200 or the web calculator","OK")</f>
         <v>OK</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B36" s="4" t="str">
+        <f aca="false">IF(Engine!$B$63,"OK — all inputs valid","⚠ Invalid input state (out-of-range or pasted value) — economics suppressed; see guards above")</f>
+        <v>OK — all inputs valid</v>
       </c>
     </row>
   </sheetData>
@@ -5777,31 +5849,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">8*RateCard!$B$36</f>
@@ -5817,7 +5889,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">730*(RateCard!$B$5+RateCard!$B$7)</f>
@@ -5833,7 +5905,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">0.25*1000000*RateCard!$B$8+0.75*1000000*RateCard!$B$9+1*1000000*RateCard!$B$11*RateCard!$B$10</f>
@@ -5849,7 +5921,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">RateCard!$B$13/12+RateCard!$B$14*RateCard!$B$12/12</f>
@@ -5865,7 +5937,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">B6+B7+B8</f>
@@ -5881,7 +5953,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">1*(485000+142800+54323+23443+14227+RateCard!$B$20)+RateCard!$B$19+1*RateCard!$B$21</f>
@@ -5897,7 +5969,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B11" s="24" t="n">
         <f aca="false">0.25*RateCard!$B$22+0.75*RateCard!$B$24</f>
@@ -5913,7 +5985,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">(0.25*RateCard!$B$23+0.75*RateCard!$B$25)/12</f>
@@ -5929,7 +6001,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">(1*14.4+1*RateCard!$B$26)*RateCard!$B$28</f>
@@ -5945,7 +6017,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">RateCard!$B$29+RateCard!$B$30*(1+0.75)/36</f>
@@ -5961,7 +6033,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">1/RateCard!$B$31*RateCard!$B$32/12</f>
@@ -5977,7 +6049,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">B13+B14+B15</f>
@@ -5993,7 +6065,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">1*RateCard!$B$33</f>
@@ -6009,7 +6081,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B18" s="24" t="n">
         <f aca="false">B10*0.0281</f>
@@ -6025,7 +6097,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B19" s="24" t="n">
         <f aca="false">B11*0.0281+B12</f>
@@ -6041,7 +6113,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B20" s="24" t="n">
         <f aca="false">B18+B19+B16</f>
@@ -6057,12 +6129,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
